--- a/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -483,10 +483,10 @@
         <v>-0.019</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.004</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -510,10 +510,10 @@
         <v>-0.037</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.038</v>
+        <v>-0.037</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.001000000000000001</v>
+        <v>0</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.045</v>
+        <v>0.012</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.029</v>
+        <v>-0.014</v>
       </c>
       <c r="E4" t="n">
-        <v>0.016</v>
+        <v>-0.002</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.061</v>
+        <v>0.046</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.044</v>
+        <v>0.011</v>
       </c>
       <c r="E5" t="n">
-        <v>0.017</v>
+        <v>0.035</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -591,10 +591,10 @@
         <v>0.097</v>
       </c>
       <c r="D6" t="n">
-        <v>0.025</v>
+        <v>0.021</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -645,10 +645,10 @@
         <v>0.046</v>
       </c>
       <c r="D8" t="n">
-        <v>-0</v>
+        <v>-0.002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.046</v>
+        <v>0.044</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -672,10 +672,10 @@
         <v>-0.008999999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -699,10 +699,10 @@
         <v>-0.074</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.041</v>
+        <v>-0.042</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03299999999999999</v>
+        <v>0.03199999999999999</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -726,10 +726,10 @@
         <v>0.034</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.007</v>
+        <v>-0.008</v>
       </c>
       <c r="E11" t="n">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>0.023</v>
       </c>
       <c r="D12" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.007</v>
       </c>
       <c r="D13" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.017</v>
+        <v>-0.018</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -807,10 +807,10 @@
         <v>0.041</v>
       </c>
       <c r="D14" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
       <c r="E14" t="n">
-        <v>0.002000000000000002</v>
+        <v>0.003000000000000003</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -834,10 +834,10 @@
         <v>0.005</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.012</v>
+        <v>-0.013</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.007</v>
+        <v>-0.008</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -861,10 +861,10 @@
         <v>0.032</v>
       </c>
       <c r="D16" t="n">
-        <v>0.038</v>
+        <v>0.03</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.005999999999999998</v>
+        <v>0.002000000000000002</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -888,10 +888,10 @@
         <v>-0.014</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.007</v>
+        <v>-0.003</v>
       </c>
       <c r="E17" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -915,10 +915,10 @@
         <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.01</v>
+        <v>-0.004</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.01</v>
+        <v>-0.004</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -969,10 +969,10 @@
         <v>0.077</v>
       </c>
       <c r="D20" t="n">
-        <v>0.034</v>
+        <v>0.031</v>
       </c>
       <c r="E20" t="n">
-        <v>0.043</v>
+        <v>0.046</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -996,10 +996,10 @@
         <v>-0.019</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.022</v>
+        <v>-0.023</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.002999999999999999</v>
+        <v>-0.004</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1023,10 +1023,10 @@
         <v>-0.113</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.055</v>
+        <v>-0.05</v>
       </c>
       <c r="E22" t="n">
-        <v>0.058</v>
+        <v>0.063</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -1050,10 +1050,10 @@
         <v>0.197</v>
       </c>
       <c r="D23" t="n">
-        <v>0.068</v>
+        <v>0.065</v>
       </c>
       <c r="E23" t="n">
-        <v>0.129</v>
+        <v>0.132</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -1077,10 +1077,10 @@
         <v>-0.143</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.043</v>
+        <v>-0.042</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.101</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
@@ -1104,10 +1104,10 @@
         <v>-0.054</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.028</v>
+        <v>-0.027</v>
       </c>
       <c r="E25" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1131,10 +1131,10 @@
         <v>-0.128</v>
       </c>
       <c r="D26" t="n">
-        <v>0.016</v>
+        <v>0.019</v>
       </c>
       <c r="E26" t="n">
-        <v>0.112</v>
+        <v>0.109</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
@@ -1158,10 +1158,10 @@
         <v>0.227</v>
       </c>
       <c r="D27" t="n">
-        <v>0.027</v>
+        <v>0.022</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2</v>
+        <v>0.205</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
@@ -1185,10 +1185,10 @@
         <v>0.392</v>
       </c>
       <c r="D28" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="E28" t="n">
-        <v>0.357</v>
+        <v>0.362</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -1212,10 +1212,10 @@
         <v>-0.401</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.048</v>
+        <v>-0.038</v>
       </c>
       <c r="E29" t="n">
-        <v>0.353</v>
+        <v>0.363</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
@@ -1239,10 +1239,10 @@
         <v>0.107</v>
       </c>
       <c r="D30" t="n">
-        <v>0.044</v>
+        <v>0.042</v>
       </c>
       <c r="E30" t="n">
-        <v>0.063</v>
+        <v>0.065</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
@@ -1266,10 +1266,10 @@
         <v>-0.041</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.01</v>
+        <v>-0.013</v>
       </c>
       <c r="E31" t="n">
-        <v>0.031</v>
+        <v>0.028</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1293,10 +1293,10 @@
         <v>-0.066</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.058</v>
+        <v>-0.057</v>
       </c>
       <c r="E32" t="n">
-        <v>0.008</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1388,22 +1388,22 @@
         <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>7100.892033747257</v>
+        <v>7094.386718944053</v>
       </c>
       <c r="C2" t="n">
-        <v>0.994936431681357</v>
+        <v>0.9957648995493169</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1288663006716531</v>
+        <v>0.1325095691671194</v>
       </c>
       <c r="E2" t="n">
-        <v>1.612879304103456</v>
+        <v>1.678870188120528</v>
       </c>
       <c r="F2" t="n">
-        <v>1.125850702242218</v>
+        <v>1.124267686541995</v>
       </c>
       <c r="G2" t="n">
-        <v>1.612462982328197</v>
+        <v>1.678043421071839</v>
       </c>
     </row>
   </sheetData>
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.791060487166903</v>
+        <v>1.749032162934507</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1024065793378279</v>
+        <v>0.09972330619000844</v>
       </c>
       <c r="D2" t="n">
-        <v>1.590347279884817</v>
+        <v>1.55357807438283</v>
       </c>
       <c r="E2" t="n">
-        <v>1.991773694448989</v>
+        <v>1.944486251486184</v>
       </c>
       <c r="F2" t="n">
-        <v>1.716544986494854e-68</v>
+        <v>7.237657289220074e-69</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02910371070917722</v>
+        <v>0.02962572488141941</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01880080333648078</v>
+        <v>0.01822264113750337</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.007745186710745599</v>
+        <v>-0.006089995451285201</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06595260812910003</v>
+        <v>0.06534144521412401</v>
       </c>
       <c r="F3" t="n">
-        <v>0.121621436665079</v>
+        <v>0.1039997416774884</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09528654564232103</v>
+        <v>0.09776307597911854</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05129306020858122</v>
+        <v>0.04954667549874945</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.005246005023342715</v>
+        <v>0.000653376447876497</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1958190963079848</v>
+        <v>0.1948727755103606</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06321321388535661</v>
+        <v>0.04847835276759651</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01169658806391305</v>
+        <v>-0.01287593631557941</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03158668162544244</v>
+        <v>0.03341847660338246</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.07360534644091332</v>
+        <v>-0.07837494687640348</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05021217031308722</v>
+        <v>0.05262307424524465</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7111580337120431</v>
+        <v>0.70001965532665</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04904356071030166</v>
+        <v>0.04934458162077564</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02983225311977588</v>
+        <v>0.03238690772777989</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.009426580982141733</v>
+        <v>-0.0141325910962949</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1075137024027451</v>
+        <v>0.1128217543378462</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1001807960266323</v>
+        <v>0.127609519810673</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.010699291964651</v>
+        <v>0.0104559782656533</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0323746745055699</v>
+        <v>0.0325231034746707</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05275390407747308</v>
+        <v>-0.05328813321017075</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07415248800677508</v>
+        <v>0.07420008974147736</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7410347461681495</v>
+        <v>0.7478361600842374</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06457476102363403</v>
+        <v>0.06434814183682906</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03086229477052781</v>
+        <v>0.03290386814872377</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004085774793140672</v>
+        <v>-0.0001422546867241442</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1250637472541274</v>
+        <v>0.1288385383603823</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0364071063406113</v>
+        <v>0.05050750165873744</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0281057080097931</v>
+        <v>0.02877420831517302</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03068584360502376</v>
+        <v>0.03191215009447936</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.03203744029128221</v>
+        <v>-0.033772456539243</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08824885631086841</v>
+        <v>0.09132087316958905</v>
       </c>
       <c r="F9" t="n">
-        <v>0.359710050293179</v>
+        <v>0.3672325279422076</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000792091784167985</v>
+        <v>-0.00101898420932267</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05101532078856483</v>
+        <v>0.05063846000222119</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.09919609962117658</v>
+        <v>-0.1002685420462483</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1007802831895126</v>
+        <v>0.09823057362760293</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9876121054720177</v>
+        <v>0.9839454655173256</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01953323559373495</v>
+        <v>0.01931633161945881</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05037205910693161</v>
+        <v>0.05194329107217191</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.07919418608297385</v>
+        <v>-0.08249064812047906</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1182606572704437</v>
+        <v>0.1211233113593967</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6981794568923547</v>
+        <v>0.7099870626555923</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06973691738801291</v>
+        <v>0.06772898012496648</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0541463818118339</v>
+        <v>0.05163557818882265</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.03638804085633617</v>
+        <v>-0.03347489344602787</v>
       </c>
       <c r="E12" t="n">
-        <v>0.175861875632362</v>
+        <v>0.1689328536959608</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1977692520781423</v>
+        <v>0.1896305795997605</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03936278391110773</v>
+        <v>0.03988129614662063</v>
       </c>
       <c r="C13" t="n">
-        <v>0.051086989873679</v>
+        <v>0.05171813694708185</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.06076587631986556</v>
+        <v>-0.06148438961717009</v>
       </c>
       <c r="E13" t="n">
-        <v>0.139491444142081</v>
+        <v>0.1412469819104114</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4410003579805362</v>
+        <v>0.4406311499162626</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01271712252803177</v>
+        <v>0.01333034569364385</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05062255954166076</v>
+        <v>0.0532208559389334</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.08650127097885778</v>
+        <v>-0.09098061517306025</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1119355160349213</v>
+        <v>0.117641306560348</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8016482509991349</v>
+        <v>0.8022221889070266</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05355958657493828</v>
+        <v>0.05372608150388213</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05114141086306227</v>
+        <v>0.05226717408728832</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.04667573683522924</v>
+        <v>-0.04871569728088816</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1537949099851058</v>
+        <v>0.1561678602886524</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2949685659969004</v>
+        <v>0.3039909897906232</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04052904609402274</v>
+        <v>0.04075528353732605</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05118024035105334</v>
+        <v>0.05309570953627983</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.05978238171414543</v>
+        <v>-0.06331039488738231</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1408404739021909</v>
+        <v>0.1448209619620344</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4284256664338353</v>
+        <v>0.4427358660730096</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.01180162440996717</v>
+        <v>0.01088254976687355</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04960958222303651</v>
+        <v>0.05158432471739409</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.08543137003526291</v>
+        <v>-0.09022086884603817</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1090346188551972</v>
+        <v>0.1119859683797853</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8119663977540272</v>
+        <v>0.8329136341204475</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.02881342741285663</v>
+        <v>0.02863194690982659</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0503525005874652</v>
+        <v>0.04992876705012336</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.06987566027010707</v>
+        <v>-0.06922663830090534</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1275025150958203</v>
+        <v>0.1264905321205585</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5671632599289019</v>
+        <v>0.5663360387177505</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.009313953036079899</v>
+        <v>0.00951821548181659</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0519059428114003</v>
+        <v>0.05189167694291161</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.09241982545786041</v>
+        <v>-0.09218760242367768</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1110477315300202</v>
+        <v>0.1112240333873109</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8575929719538606</v>
+        <v>0.8544647937149349</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.01379447702808756</v>
+        <v>-0.01322088667279001</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0504108287316283</v>
+        <v>0.04979291726953829</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.112597885772896</v>
+        <v>-0.1108132112062676</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08500893171672089</v>
+        <v>0.08437143786068754</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7843604092048622</v>
+        <v>0.7906108960257915</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.003092890211616492</v>
+        <v>0.004335437062310105</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04890879872800196</v>
+        <v>0.05125049584123834</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.09276659382238577</v>
+        <v>-0.09611368897633686</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09895237424561874</v>
+        <v>0.1047845631009571</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9495770573709426</v>
+        <v>0.9325849043145351</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.01034221495579915</v>
+        <v>0.01158397950368171</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05353000686324142</v>
+        <v>0.05351623953049019</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.09457467058833595</v>
+        <v>-0.0933059225640978</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1152591004999342</v>
+        <v>0.1164738815714612</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8467991548628974</v>
+        <v>0.828631323447275</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.04414151305926853</v>
+        <v>0.04490126550683204</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05200266111164537</v>
+        <v>0.05073590126058445</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.05778182981979803</v>
+        <v>-0.05453927368709382</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1460648559383351</v>
+        <v>0.1443418047007579</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3959748858831927</v>
+        <v>0.3761567069305489</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.09257469998838677</v>
+        <v>0.09277287691209139</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04013163418177873</v>
+        <v>0.0419807494514414</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0139181423513639</v>
+        <v>0.01049211994326661</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1712312576254096</v>
+        <v>0.1750536338809162</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02106729777227955</v>
+        <v>0.02711273375311733</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0359786184442716</v>
+        <v>0.03607863560750366</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02403628910003266</v>
+        <v>0.02485846017140064</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.01113164251378508</v>
+        <v>-0.01264305103956496</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08308887940232829</v>
+        <v>0.08480032225457229</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1344333852615451</v>
+        <v>0.1466789605900471</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01414455843260854</v>
+        <v>0.01448398768324709</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02847248613439088</v>
+        <v>0.02811551845289981</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.04166048894111365</v>
+        <v>-0.04062141589110784</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06994960580633072</v>
+        <v>0.06958939125760201</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6193442803784488</v>
+        <v>0.6064412877410579</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.03290296070469237</v>
+        <v>-0.03309843316687117</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02894039758226</v>
+        <v>0.02920935542237533</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.08962509766419204</v>
+        <v>-0.09034771780635655</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0238191762548073</v>
+        <v>0.02415085147261421</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2555710964827923</v>
+        <v>0.2571533936244735</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.01367876114641974</v>
+        <v>-0.0137832652788754</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02884154967954932</v>
+        <v>0.02964373700932217</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.07020715977665914</v>
+        <v>-0.07188392218432395</v>
       </c>
       <c r="E28" t="n">
-        <v>0.04284963748381965</v>
+        <v>0.04431739162657314</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6353054193228803</v>
+        <v>0.6419573641976893</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.02662459802101696</v>
+        <v>-0.0269352087796916</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02890017680347932</v>
+        <v>0.02936902969487703</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.08326790370267632</v>
+        <v>-0.08449744924253795</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0300187076606424</v>
+        <v>0.03062703168315474</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3569143176162929</v>
+        <v>0.359074690426296</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4023325834933801</v>
+        <v>0.398223309657814</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03968560193011214</v>
+        <v>0.0392698381059611</v>
       </c>
       <c r="D30" t="n">
-        <v>0.324550233005567</v>
+        <v>0.3212558412914116</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4801149339811931</v>
+        <v>0.4751907780242164</v>
       </c>
       <c r="F30" t="n">
-        <v>3.746968690837363e-24</v>
+        <v>3.645104327879786e-24</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0004359137896690168</v>
+        <v>-0.003190404661875357</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001367191147543997</v>
+        <v>0.00419190674909983</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.002243731619499205</v>
+        <v>-0.01140639091666141</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003115559198837239</v>
+        <v>0.00502558159291069</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7498486408096909</v>
+        <v>0.4466052571656733</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4977795062913186</v>
+        <v>0.001072258730903537</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0118741494776586</v>
+        <v>0.001289206013563256</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4745066009680626</v>
+        <v>-0.001454538624332901</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5210524116145745</v>
+        <v>0.003599056086139975</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.4055668752339309</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.00205718666506498</v>
+        <v>0.4975842499220142</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001363938368899229</v>
+        <v>0.01226979046800347</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.004730456745239775</v>
+        <v>0.4735359025068746</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0006160834151098154</v>
+        <v>0.5216325973371538</v>
       </c>
       <c r="F33" t="n">
-        <v>0.131485561583713</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2264,19 +2264,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.001517675541394995</v>
+        <v>-0.001517501047856205</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001631868489509199</v>
+        <v>0.001599774795501181</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.004716079008338804</v>
+        <v>-0.004653002030413449</v>
       </c>
       <c r="E34" t="n">
-        <v>0.001680727925548814</v>
+        <v>0.001617999934701039</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3523590767499664</v>
+        <v>0.3428385058225917</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.639158330392934</v>
+        <v>-0.002085975822998771</v>
       </c>
       <c r="C35" t="n">
-        <v>0.04617304703621801</v>
+        <v>0.001402357375237837</v>
       </c>
       <c r="D35" t="n">
-        <v>1.548660821145473</v>
+        <v>-0.004834545771919054</v>
       </c>
       <c r="E35" t="n">
-        <v>1.729655839640395</v>
+        <v>0.0006625941259215109</v>
       </c>
       <c r="F35" t="n">
-        <v>4.858375967378376e-276</v>
+        <v>0.1368885945885609</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2310,23 +2310,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.006838723240314424</v>
+        <v>1.638035829451044</v>
       </c>
       <c r="C36" t="n">
-        <v>0.004013340317286054</v>
+        <v>0.04812529240022992</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.01470472571989764</v>
+        <v>1.543711989601135</v>
       </c>
       <c r="E36" t="n">
-        <v>0.001027279239268795</v>
+        <v>1.732359669300954</v>
       </c>
       <c r="F36" t="n">
-        <v>0.08838149038219476</v>
+        <v>6.341968535618201e-254</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.350970771285248</v>
+        <v>-2.68060017980294</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4605522587714034</v>
+        <v>0.4771933030981267</v>
       </c>
       <c r="D2" t="n">
-        <v>3.313590542287848e-07</v>
+        <v>1.93818176827037e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2391,13 +2391,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02128055977478192</v>
+        <v>-0.02542074333516159</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09751395156308111</v>
+        <v>0.1002143663033998</v>
       </c>
       <c r="D3" t="n">
-        <v>0.827249191641336</v>
+        <v>0.7997554080121703</v>
       </c>
     </row>
     <row r="4">
@@ -2407,13 +2407,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2245966634275915</v>
+        <v>0.2244463748843408</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2329354389845562</v>
+        <v>0.2335027157442914</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3349449904957182</v>
+        <v>0.3364439424069164</v>
       </c>
     </row>
     <row r="5">
@@ -2423,13 +2423,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8167052829997485</v>
+        <v>0.8155080917228588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1617156577703267</v>
+        <v>0.173402651392118</v>
       </c>
       <c r="D5" t="n">
-        <v>4.412210487480358e-07</v>
+        <v>2.563995828054386e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2439,13 +2439,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03599538577094948</v>
+        <v>0.03527526670387294</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1898688322218615</v>
+        <v>0.1916882946919544</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8496380437366924</v>
+        <v>0.8539945454713553</v>
       </c>
     </row>
     <row r="7">
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2765708211818085</v>
+        <v>0.2773648159307716</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1824472225347018</v>
+        <v>0.1901447102133385</v>
       </c>
       <c r="D7" t="n">
-        <v>0.129545920374235</v>
+        <v>0.1446466431125523</v>
       </c>
     </row>
     <row r="8">
@@ -2471,13 +2471,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1102648615599912</v>
+        <v>0.1036811851537241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1853641405651108</v>
+        <v>0.1952515666982444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5519401263365121</v>
+        <v>0.5954095400432468</v>
       </c>
     </row>
     <row r="9">
@@ -2487,13 +2487,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8745743640527194</v>
+        <v>0.8738774480300985</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1615402513662274</v>
+        <v>0.1695280942409136</v>
       </c>
       <c r="D9" t="n">
-        <v>6.164188141358052e-08</v>
+        <v>2.539495077342719e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04349724922704642</v>
+        <v>-0.04456520772617057</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2655215602978132</v>
+        <v>0.2604021031716314</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8698743077153893</v>
+        <v>0.8641137091517844</v>
       </c>
     </row>
     <row r="11">
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2685655156863916</v>
+        <v>-0.2737623724798145</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2761865361461748</v>
+        <v>0.2787881385465063</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3308484806726052</v>
+        <v>0.3261132423877634</v>
       </c>
     </row>
     <row r="12">
@@ -2535,13 +2535,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08406558527820192</v>
+        <v>0.08100487957118158</v>
       </c>
       <c r="C12" t="n">
-        <v>0.251020166800007</v>
+        <v>0.2596429772097172</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7377037334343584</v>
+        <v>0.7550514391424689</v>
       </c>
     </row>
     <row r="13">
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04159103469582721</v>
+        <v>0.03917827337461771</v>
       </c>
       <c r="C13" t="n">
-        <v>0.255561465250315</v>
+        <v>0.2572958805743772</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8707201879025983</v>
+        <v>0.8789745077123736</v>
       </c>
     </row>
     <row r="14">
@@ -2567,13 +2567,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05097157642059893</v>
+        <v>-0.05296103812307912</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2615504699624188</v>
+        <v>0.2610089865588722</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8454850334004391</v>
+        <v>0.8392062624375538</v>
       </c>
     </row>
     <row r="15">
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1235593461635321</v>
+        <v>0.1181322726534163</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2569613848518211</v>
+        <v>0.2572294350577189</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6306245929938302</v>
+        <v>0.6460556128984085</v>
       </c>
     </row>
     <row r="16">
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.002490750131026257</v>
+        <v>-0.00400098624037939</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2457746491930773</v>
+        <v>0.2383903410311194</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9919141495524532</v>
+        <v>0.9866094604655136</v>
       </c>
     </row>
     <row r="17">
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1110262478895003</v>
+        <v>0.1057185310395308</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2594324060220158</v>
+        <v>0.2543340222421757</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6686814903924607</v>
+        <v>0.6776529122567302</v>
       </c>
     </row>
     <row r="18">
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1338440250599403</v>
+        <v>-0.1377694895733253</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2694490717592011</v>
+        <v>0.2636874203313639</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6193779257550096</v>
+        <v>0.6013412201546287</v>
       </c>
     </row>
     <row r="19">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02068301206114321</v>
+        <v>-0.0255715409422322</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2629683391871477</v>
+        <v>0.2527597901538112</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9373093461992266</v>
+        <v>0.9194160355966682</v>
       </c>
     </row>
     <row r="20">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0686991433762508</v>
+        <v>-0.07344622569376394</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2617458461247386</v>
+        <v>0.2674578609541013</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7929629071620667</v>
+        <v>0.7836169672222786</v>
       </c>
     </row>
     <row r="21">
@@ -2679,13 +2679,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2112158738988716</v>
+        <v>0.2063167170305062</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2400889859196068</v>
+        <v>0.2442896532450728</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3790001987958982</v>
+        <v>0.3983578134719856</v>
       </c>
     </row>
     <row r="22">
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.159933319308369</v>
+        <v>-0.1704634573362025</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2649283257747139</v>
+        <v>0.2696748454965907</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5460529306471213</v>
+        <v>0.5273167196806369</v>
       </c>
     </row>
     <row r="23">
@@ -2711,13 +2711,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4920005620651325</v>
+        <v>-0.5008110927334755</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2884409459397611</v>
+        <v>0.2870672180445716</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08805953197431808</v>
+        <v>0.08105838975171867</v>
       </c>
     </row>
     <row r="24">
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9425285809878476</v>
+        <v>0.9366864721074269</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1559773650465781</v>
+        <v>0.1483430409733375</v>
       </c>
       <c r="D24" t="n">
-        <v>1.515312581506736e-09</v>
+        <v>2.713396260923871e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5768512495314141</v>
+        <v>-0.5776106069409676</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1130405709043027</v>
+        <v>0.1143619392421805</v>
       </c>
       <c r="D25" t="n">
-        <v>3.342294640071132e-07</v>
+        <v>4.401383208103756e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2759,13 +2759,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2384858887162336</v>
+        <v>0.2373161448441742</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1457315480836286</v>
+        <v>0.1503781926377478</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1017404238903948</v>
+        <v>0.1145360411757809</v>
       </c>
     </row>
     <row r="27">
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04585234373593617</v>
+        <v>-0.04350476117998649</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1593109532353293</v>
+        <v>0.1611879340386415</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7734870970055308</v>
+        <v>0.7872365295400219</v>
       </c>
     </row>
     <row r="28">
@@ -2791,13 +2791,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07857740431296747</v>
+        <v>-0.07514354096975731</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1565335672967476</v>
+        <v>0.1613683918223567</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6156785148897228</v>
+        <v>0.6414556246120153</v>
       </c>
     </row>
     <row r="29">
@@ -2807,45 +2807,45 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09755305493394664</v>
+        <v>0.09749293462742098</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1499487653516257</v>
+        <v>0.1543265796290168</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5153202832397639</v>
+        <v>0.5275624553510017</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.006860378637723895</v>
+        <v>-0.004129656026475424</v>
       </c>
       <c r="C30" t="n">
-        <v>0.006945236405256705</v>
+        <v>0.02222260881033181</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3232594861617505</v>
+        <v>0.8525770672961283</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.002646425713821547</v>
+        <v>0.006335499136474501</v>
       </c>
       <c r="C31" t="n">
-        <v>0.007095424075339026</v>
+        <v>0.006871422968197188</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7091660102282209</v>
+        <v>0.3565249957666434</v>
       </c>
     </row>
     <row r="32">
@@ -2855,45 +2855,45 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.004895000819746557</v>
+        <v>-0.005012017390962181</v>
       </c>
       <c r="C32" t="n">
-        <v>0.008684655396149939</v>
+        <v>0.008304876992454852</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5730005966817302</v>
+        <v>0.5461741835341496</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2261835420647834</v>
+        <v>-0.00241813341219285</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1139281184793711</v>
+        <v>0.007135781003458538</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04710910483736543</v>
+        <v>0.7347043603418298</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.01540023496026497</v>
+        <v>0.2280638724458788</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0213723694247541</v>
+        <v>0.1146565719927948</v>
       </c>
       <c r="D34" t="n">
-        <v>0.47117565131408</v>
+        <v>0.04668969945129902</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.227</v>
+        <v>-0.008</v>
       </c>
       <c r="D7" t="n">
-        <v>0.024</v>
+        <v>-0.002</v>
       </c>
       <c r="E7" t="n">
-        <v>0.203</v>
+        <v>0.006</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.143</v>
+        <v>-0.066</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.042</v>
+        <v>-0.057</v>
       </c>
       <c r="E8" t="n">
-        <v>0.101</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.054</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.002</v>
+        <v>-0.027</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.024</v>
+        <v>0.041</v>
       </c>
       <c r="D10" t="n">
-        <v>0.027</v>
+        <v>0.037</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.002999999999999999</v>
+        <v>0.004000000000000004</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.034</v>
+        <v>0.007</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.008</v>
+        <v>0.025</v>
       </c>
       <c r="E11" t="n">
-        <v>0.026</v>
+        <v>-0.018</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.107</v>
+        <v>-0.074</v>
       </c>
       <c r="D12" t="n">
-        <v>0.042</v>
+        <v>-0.042</v>
       </c>
       <c r="E12" t="n">
-        <v>0.065</v>
+        <v>0.03199999999999999</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.007</v>
+        <v>0.034</v>
       </c>
       <c r="D13" t="n">
-        <v>0.025</v>
+        <v>-0.008</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.018</v>
+        <v>0.026</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.128</v>
+        <v>-0.041</v>
       </c>
       <c r="D14" t="n">
-        <v>0.018</v>
+        <v>-0.012</v>
       </c>
       <c r="E14" t="n">
-        <v>0.11</v>
+        <v>0.029</v>
       </c>
       <c r="F14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.005</v>
+        <v>0.032</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.012</v>
+        <v>0.032</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.007</v>
+        <v>0</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.032</v>
+        <v>0.023</v>
       </c>
       <c r="D16" t="n">
-        <v>0.032</v>
+        <v>0.011</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.046</v>
+        <v>-0.401</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.002</v>
+        <v>-0.038</v>
       </c>
       <c r="E17" t="n">
-        <v>0.044</v>
+        <v>0.363</v>
       </c>
       <c r="F17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.392</v>
+        <v>-0.014</v>
       </c>
       <c r="D18" t="n">
-        <v>0.03</v>
+        <v>-0.003</v>
       </c>
       <c r="E18" t="n">
-        <v>0.362</v>
+        <v>0.011</v>
       </c>
       <c r="F18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.008</v>
+        <v>-0.143</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.002</v>
+        <v>-0.042</v>
       </c>
       <c r="E19" t="n">
-        <v>0.006</v>
+        <v>0.101</v>
       </c>
       <c r="F19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,16 +966,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.197</v>
+        <v>-0.019</v>
       </c>
       <c r="D20" t="n">
-        <v>0.067</v>
+        <v>-0.024</v>
       </c>
       <c r="E20" t="n">
-        <v>0.13</v>
+        <v>-0.005000000000000001</v>
       </c>
       <c r="F20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.074</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.042</v>
+        <v>-0.002</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03199999999999999</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.023</v>
+        <v>-0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.011</v>
+        <v>-0.005</v>
       </c>
       <c r="E23" t="n">
-        <v>0.012</v>
+        <v>-0.005</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.401</v>
+        <v>0.022</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.038</v>
+        <v>0.015</v>
       </c>
       <c r="E24" t="n">
-        <v>0.363</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.041</v>
+        <v>-0.024</v>
       </c>
       <c r="D25" t="n">
-        <v>0.037</v>
+        <v>0.027</v>
       </c>
       <c r="E25" t="n">
-        <v>0.004000000000000004</v>
+        <v>-0.002999999999999999</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.066</v>
+        <v>0.197</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.057</v>
+        <v>0.067</v>
       </c>
       <c r="E27" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="F27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.041</v>
+        <v>0.046</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.012</v>
+        <v>-0.002</v>
       </c>
       <c r="E28" t="n">
-        <v>0.029</v>
+        <v>0.044</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.022</v>
+        <v>0.227</v>
       </c>
       <c r="D29" t="n">
-        <v>0.015</v>
+        <v>0.024</v>
       </c>
       <c r="E29" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.203</v>
       </c>
       <c r="F29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.054</v>
+        <v>0.005</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.027</v>
+        <v>-0.012</v>
       </c>
       <c r="E30" t="n">
-        <v>0.027</v>
+        <v>-0.007</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.019</v>
+        <v>0.107</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.024</v>
+        <v>0.042</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.005000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="F31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,16 +1290,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.014</v>
+        <v>-0.128</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.003</v>
+        <v>0.018</v>
       </c>
       <c r="E32" t="n">
-        <v>0.011</v>
+        <v>0.11</v>
       </c>
       <c r="F32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
@@ -1308,7 +1308,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0</v>
+        <v>0.392</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.005</v>
+        <v>0.03</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.005</v>
+        <v>0.362</v>
       </c>
       <c r="F33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="b">
         <v>1</v>
@@ -1494,16 +1494,16 @@
         <v>1.748744200678083</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0997224673554809</v>
+        <v>0.09972246735548673</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553291756211869</v>
+        <v>1.553291756211858</v>
       </c>
       <c r="E2" t="n">
-        <v>1.944196645144297</v>
+        <v>1.944196645144308</v>
       </c>
       <c r="F2" t="n">
-        <v>7.59513082977984e-69</v>
+        <v>7.595130829916493e-69</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1516,16 +1516,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0295863397441571</v>
+        <v>0.02958633974415711</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01822177522012755</v>
+        <v>0.01822177522012756</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.006127683421677316</v>
+        <v>-0.006127683421677313</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06530036290999153</v>
+        <v>0.06530036290999154</v>
       </c>
       <c r="F3" t="n">
         <v>0.1044440307699914</v>
@@ -1541,19 +1541,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0978401142418725</v>
+        <v>0.09784011424187253</v>
       </c>
       <c r="C4" t="n">
         <v>0.04951895669896678</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007847425598991736</v>
+        <v>0.0007847425598992014</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1948954859238458</v>
+        <v>0.1948954859238459</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04817615306008703</v>
+        <v>0.04817615306008694</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1566,19 +1566,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.0127379720094039</v>
+        <v>-0.01273797200940394</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03343233284250818</v>
+        <v>0.03343233284250816</v>
       </c>
       <c r="D5" t="n">
         <v>-0.07826414029987555</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05278819628106774</v>
+        <v>0.05278819628106768</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7031976288909345</v>
+        <v>0.7031976288909334</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04927628124940879</v>
+        <v>0.04927628124940884</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03239456843861483</v>
+        <v>0.03239456843861484</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.01421590618499421</v>
+        <v>-0.01421590618499418</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1127684686838118</v>
+        <v>0.1127684686838119</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1282277489991777</v>
+        <v>0.1282277489991775</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1616,19 +1616,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0104778525809015</v>
+        <v>0.01047785258090146</v>
       </c>
       <c r="C7" t="n">
         <v>0.03252233317855407</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05326474914227652</v>
+        <v>-0.05326474914227657</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07422045430407953</v>
+        <v>0.07422045430407949</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7473208240704079</v>
+        <v>0.7473208240704087</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06433271843302669</v>
+        <v>0.06433271843302668</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03291080729184542</v>
+        <v>0.03291080729184541</v>
       </c>
       <c r="D8" t="n">
         <v>-0.0001712785611285156</v>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0286514049037586</v>
+        <v>0.02865140490375856</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03191029283342593</v>
+        <v>0.03191029283342592</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.03389161978588281</v>
+        <v>-0.03389161978588283</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09119442959340002</v>
+        <v>0.09119442959339995</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3692530175492086</v>
+        <v>0.3692530175492091</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1691,19 +1691,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0009794214476963237</v>
+        <v>-0.0009794214476962462</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05063414819939274</v>
+        <v>0.05063414819939278</v>
       </c>
       <c r="D10" t="n">
         <v>-0.1002205283063697</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09826168541097707</v>
+        <v>0.09826168541097723</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9845674006463193</v>
+        <v>0.9845674006463205</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1716,19 +1716,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01946826154009435</v>
+        <v>0.01946826154009432</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05194685720438134</v>
+        <v>0.05194685720438145</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.08234570769053812</v>
+        <v>-0.08234570769053835</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1212822307707268</v>
+        <v>0.121282230770727</v>
       </c>
       <c r="F11" t="n">
-        <v>0.707829553416398</v>
+        <v>0.7078295534163992</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06785609067849589</v>
+        <v>0.06785609067849586</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05163905582747092</v>
+        <v>0.05163905582747091</v>
       </c>
       <c r="D12" t="n">
         <v>-0.03335459893900031</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1690667802959921</v>
+        <v>0.169066780295992</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1888307512048417</v>
+        <v>0.1888307512048416</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1766,19 +1766,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04035183396023317</v>
+        <v>0.04035183396023319</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05171295167094477</v>
+        <v>0.05171295167094479</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.06100368884907898</v>
+        <v>-0.061003688849079</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1417073567695453</v>
+        <v>0.1417073567695454</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4352118346691926</v>
+        <v>0.4352118346691924</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1791,19 +1791,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01360432138726268</v>
+        <v>0.01360432138726276</v>
       </c>
       <c r="C14" t="n">
         <v>0.05321733263316392</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09069973392702671</v>
+        <v>-0.09069973392702664</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1179083767015521</v>
+        <v>0.1179083767015522</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7982311147396461</v>
+        <v>0.7982311147396448</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1816,19 +1816,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05405252017528384</v>
+        <v>0.0540525201752838</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0522673518884417</v>
+        <v>0.05226735188844174</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.04838960709334347</v>
+        <v>-0.04838960709334359</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1564946474439111</v>
+        <v>0.1564946474439112</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3010639142436634</v>
+        <v>0.3010639142436642</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1841,19 +1841,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04086477158037348</v>
+        <v>0.04086477158037346</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05309945880834849</v>
+        <v>0.05309945880834852</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.06320825528255769</v>
+        <v>-0.06320825528255777</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1449377984433046</v>
+        <v>0.1449377984433047</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4415435960896876</v>
+        <v>0.4415435960896881</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1866,19 +1866,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.01102820644228603</v>
+        <v>0.01102820644228601</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05158345722977693</v>
+        <v>0.05158345722977697</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09007351192613902</v>
+        <v>-0.09007351192613912</v>
       </c>
       <c r="E17" t="n">
         <v>0.1121299248107111</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8307081155011068</v>
+        <v>0.8307081155011071</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1891,19 +1891,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.02900589471309431</v>
+        <v>0.02900589471309425</v>
       </c>
       <c r="C18" t="n">
-        <v>0.04992506750994722</v>
+        <v>0.04992506750994716</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.06884543953213304</v>
+        <v>-0.06884543953213298</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1268572289583217</v>
+        <v>0.1268572289583215</v>
       </c>
       <c r="F18" t="n">
-        <v>0.561248141734635</v>
+        <v>0.5612481417346353</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1916,19 +1916,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.009706893816720148</v>
+        <v>0.009706893816720116</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05188944681346103</v>
+        <v>0.05188944681346105</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.09199455311537015</v>
+        <v>-0.09199455311537021</v>
       </c>
       <c r="E19" t="n">
         <v>0.1114083407488104</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8516067315648226</v>
+        <v>0.851606731564823</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1941,19 +1941,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.01294184623909369</v>
+        <v>-0.0129418462390937</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04979214122466382</v>
+        <v>0.04979214122466381</v>
       </c>
       <c r="D20" t="n">
         <v>-0.1105326497525669</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08464895727437949</v>
+        <v>0.08464895727437945</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7949274527428551</v>
+        <v>0.7949274527428548</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1966,19 +1966,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.00445065451121985</v>
+        <v>0.004450654511219809</v>
       </c>
       <c r="C21" t="n">
-        <v>0.051253082847293</v>
+        <v>0.05125308284729309</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.09600354196612203</v>
+        <v>-0.09600354196612225</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1049048509885617</v>
+        <v>0.1049048509885619</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9308012234128822</v>
+        <v>0.930801223412883</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1991,19 +1991,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0117895062929274</v>
+        <v>0.01178950629292756</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05351780370106509</v>
+        <v>0.05351780370106517</v>
       </c>
       <c r="D22" t="n">
         <v>-0.09310346149284458</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1166824740786994</v>
+        <v>0.1166824740786997</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8256442990935577</v>
+        <v>0.8256442990935557</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -2016,19 +2016,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0450085309111327</v>
+        <v>0.04500853091113263</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05073676871697227</v>
+        <v>0.05073676871697232</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.05443370846607145</v>
+        <v>-0.0544337084660716</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1444507702883368</v>
+        <v>0.1444507702883369</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3750256648141884</v>
+        <v>0.3750256648141893</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2041,19 +2041,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.09317839536589106</v>
+        <v>0.09317839536589115</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04199057011256823</v>
+        <v>0.04199057011256822</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01087839025495332</v>
+        <v>0.01087839025495342</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1754784004768288</v>
+        <v>0.1754784004768289</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02648458550495973</v>
+        <v>0.02648458550495959</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2066,19 +2066,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.03623225650076144</v>
+        <v>0.03623225650076152</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02486297432359926</v>
+        <v>0.02486297432359928</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.01249827772203721</v>
+        <v>-0.01249827772203718</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0849627907235601</v>
+        <v>0.08496279072356022</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1450397569591428</v>
+        <v>0.1450397569591422</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2091,19 +2091,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01467109228439205</v>
+        <v>0.01467109228439209</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02811127962746578</v>
+        <v>0.02811127962746581</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.04042600334477542</v>
+        <v>-0.04042600334477545</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06976818791355952</v>
+        <v>0.06976818791355963</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6017445295692687</v>
+        <v>0.6017445295692684</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2116,19 +2116,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.03310111763713031</v>
+        <v>-0.03310111763713029</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02920545388089281</v>
+        <v>0.0292054538808928</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.09034275539582576</v>
+        <v>-0.09034275539582573</v>
       </c>
       <c r="E27" t="n">
         <v>0.02414052012156515</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2570512552489402</v>
+        <v>0.2570512552489403</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2141,19 +2141,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.01368596077233375</v>
+        <v>-0.0136859607723338</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02963823096954001</v>
+        <v>0.02963823096954</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.07177582603811181</v>
+        <v>-0.07177582603811183</v>
       </c>
       <c r="E28" t="n">
-        <v>0.04440390449344431</v>
+        <v>0.04440390449344424</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6442483269078476</v>
+        <v>0.6442483269078466</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2166,19 +2166,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.02682587599480334</v>
+        <v>-0.02682587599480336</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02937399338914297</v>
+        <v>0.02937399338914296</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0843978451196412</v>
+        <v>-0.08439784511964121</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03074609313003451</v>
+        <v>0.03074609313003449</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3611097025802037</v>
+        <v>0.3611097025802034</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2194,16 +2194,16 @@
         <v>0.3985398745276548</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03933933271771812</v>
+        <v>0.0393393327177181</v>
       </c>
       <c r="D30" t="n">
-        <v>0.321436199225089</v>
+        <v>0.3214361992250891</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4756435498302205</v>
+        <v>0.4756435498302204</v>
       </c>
       <c r="F30" t="n">
-        <v>4.032349524444008e-24</v>
+        <v>4.032349524443835e-24</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2212,23 +2212,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.002088076448677743</v>
+        <v>0.0010631219852765</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001402263199247396</v>
+        <v>0.001289385890041364</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.004836461816048554</v>
+        <v>-0.001464027921378697</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0006603089186930666</v>
+        <v>0.003590271891931697</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1364673619490752</v>
+        <v>0.4096452440067881</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2237,23 +2237,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.001532654351402113</v>
+        <v>-0.002088076448677744</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001599885891944229</v>
+        <v>0.001402263199247397</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.004668373078986541</v>
+        <v>-0.004836461816048556</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001603064376182316</v>
+        <v>0.0006603089186930687</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3380742102093481</v>
+        <v>0.1364673619490754</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2262,23 +2262,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.003156716305439282</v>
+        <v>1.638429102143954</v>
       </c>
       <c r="C33" t="n">
-        <v>0.00419143405202006</v>
+        <v>0.04812377374195426</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.01137177609097338</v>
+        <v>1.544108238809569</v>
       </c>
       <c r="E33" t="n">
-        <v>0.00505834348009482</v>
+        <v>1.732749965478338</v>
       </c>
       <c r="F33" t="n">
-        <v>0.451368705162151</v>
+        <v>4.628174711724608e-254</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2287,23 +2287,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4977006363722659</v>
+        <v>-0.001532654351402115</v>
       </c>
       <c r="C34" t="n">
-        <v>0.01226810100606328</v>
+        <v>0.001599885891944252</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4736556002416823</v>
+        <v>-0.00466837307898659</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5217456725028495</v>
+        <v>0.00160306437618236</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>0.3380742102093548</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2312,23 +2312,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.638429102143954</v>
+        <v>0.4977006363722659</v>
       </c>
       <c r="C35" t="n">
-        <v>0.04812377374195412</v>
+        <v>0.01226810100606316</v>
       </c>
       <c r="D35" t="n">
-        <v>1.544108238809569</v>
+        <v>0.4736556002416825</v>
       </c>
       <c r="E35" t="n">
-        <v>1.732749965478338</v>
+        <v>0.5217456725028493</v>
       </c>
       <c r="F35" t="n">
-        <v>4.628174711708808e-254</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2337,23 +2337,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.001063121985276503</v>
+        <v>-0.00315671630543928</v>
       </c>
       <c r="C36" t="n">
-        <v>0.001289385890041367</v>
+        <v>0.00419143405202007</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.001464027921378699</v>
+        <v>-0.0113717760909734</v>
       </c>
       <c r="E36" t="n">
-        <v>0.003590271891931705</v>
+        <v>0.00505834348009484</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4096452440067879</v>
+        <v>0.4513687051621523</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.774614073588889</v>
+        <v>-2.77461407358889</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5213956350107419</v>
+        <v>0.5213956350107528</v>
       </c>
       <c r="D2" t="n">
-        <v>1.029072958036885e-07</v>
+        <v>1.029072958037503e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2418,13 +2418,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02531896946916952</v>
+        <v>-0.02531896946916946</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1001870355608945</v>
+        <v>0.1001870355608946</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8004868915759106</v>
+        <v>0.8004868915759111</v>
       </c>
     </row>
     <row r="4">
@@ -2437,10 +2437,10 @@
         <v>0.2256150601556657</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2336513202417123</v>
+        <v>0.2336513202417124</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3342414930584404</v>
+        <v>0.3342414930584405</v>
       </c>
     </row>
     <row r="5">
@@ -2453,10 +2453,10 @@
         <v>0.8160827895347563</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1734116198833065</v>
+        <v>0.1734116198833069</v>
       </c>
       <c r="D5" t="n">
-        <v>2.525694832362313e-06</v>
+        <v>2.525694832362419e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2466,13 +2466,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03622598517976082</v>
+        <v>0.03622598517976072</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1914953081760685</v>
+        <v>0.1914953081760689</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8499562329133771</v>
+        <v>0.8499562329133779</v>
       </c>
     </row>
     <row r="7">
@@ -2485,10 +2485,10 @@
         <v>0.2771938342360028</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1901314810930081</v>
+        <v>0.1901314810930085</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1448664442117519</v>
+        <v>0.1448664442117525</v>
       </c>
     </row>
     <row r="8">
@@ -2498,13 +2498,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1053581304950987</v>
+        <v>0.1053581304950989</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1953442667159787</v>
+        <v>0.195344266715979</v>
       </c>
       <c r="D8" t="n">
-        <v>0.58964819891079</v>
+        <v>0.5896481989107898</v>
       </c>
     </row>
     <row r="9">
@@ -2514,13 +2514,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8758696511293144</v>
+        <v>0.8758696511293145</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1693371735726042</v>
+        <v>0.1693371735726046</v>
       </c>
       <c r="D9" t="n">
-        <v>2.31178862989609e-07</v>
+        <v>2.311788629896225e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2530,13 +2530,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04427462059794676</v>
+        <v>-0.04427462059794664</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2604040478124681</v>
+        <v>0.2604040478124685</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8649922202201142</v>
+        <v>0.8649922202201148</v>
       </c>
     </row>
     <row r="11">
@@ -2549,10 +2549,10 @@
         <v>-0.2742205061505736</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2787689544694695</v>
+        <v>0.2787689544694698</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3252710045288592</v>
+        <v>0.3252710045288596</v>
       </c>
     </row>
     <row r="12">
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08193295015444108</v>
+        <v>0.0819329501544412</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2597818841250332</v>
+        <v>0.2597818841250336</v>
       </c>
       <c r="D12" t="n">
         <v>0.752464559918951</v>
@@ -2578,13 +2578,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03769699417328217</v>
+        <v>0.03769699417328223</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2573362415649834</v>
+        <v>0.2573362415649832</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8835351721093905</v>
+        <v>0.8835351721093903</v>
       </c>
     </row>
     <row r="14">
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05102687086135054</v>
+        <v>-0.05102687086135028</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2608488036216073</v>
+        <v>0.2608488036216074</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8449087216020048</v>
+        <v>0.8449087216020057</v>
       </c>
     </row>
     <row r="15">
@@ -2610,13 +2610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1194505179052273</v>
+        <v>0.1194505179052272</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2572736242808297</v>
+        <v>0.2572736242808301</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6424373510261991</v>
+        <v>0.6424373510262</v>
       </c>
     </row>
     <row r="16">
@@ -2626,13 +2626,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.003394520999805394</v>
+        <v>-0.003394520999805274</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2383941217340661</v>
+        <v>0.2383941217340667</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9886392149415375</v>
+        <v>0.9886392149415379</v>
       </c>
     </row>
     <row r="17">
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1051737680003745</v>
+        <v>0.1051737680003746</v>
       </c>
       <c r="C17" t="n">
-        <v>0.254498915914791</v>
+        <v>0.2544989159147915</v>
       </c>
       <c r="D17" t="n">
         <v>0.6794174396292689</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1377738518166144</v>
+        <v>-0.1377738518166146</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2637734916431439</v>
+        <v>0.2637734916431445</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6014483864186183</v>
+        <v>0.6014483864186184</v>
       </c>
     </row>
     <row r="19">
@@ -2674,13 +2674,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02393490642264846</v>
+        <v>-0.02393490642264839</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2529805715426137</v>
+        <v>0.2529805715426139</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9246233049950183</v>
+        <v>0.9246233049950185</v>
       </c>
     </row>
     <row r="20">
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0730127358393004</v>
+        <v>-0.07301273583930051</v>
       </c>
       <c r="C20" t="n">
-        <v>0.267519090068655</v>
+        <v>0.2675190900686554</v>
       </c>
       <c r="D20" t="n">
         <v>0.7849106151948602</v>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2069135147918232</v>
+        <v>0.2069135147918233</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2442870989291297</v>
+        <v>0.2442870989291298</v>
       </c>
       <c r="D21" t="n">
         <v>0.396989777761073</v>
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1717092932306348</v>
+        <v>-0.1717092932306347</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2696190828094297</v>
+        <v>0.26961908280943</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5242168027309875</v>
+        <v>0.5242168027309879</v>
       </c>
     </row>
     <row r="23">
@@ -2738,13 +2738,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5023322926397006</v>
+        <v>-0.5023322926397007</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2872431741192604</v>
+        <v>0.2872431741192606</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08032473613005384</v>
+        <v>0.08032473613005404</v>
       </c>
     </row>
     <row r="24">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9363452786511912</v>
+        <v>0.9363452786511914</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1483102369545481</v>
+        <v>0.1483102369545483</v>
       </c>
       <c r="D24" t="n">
-        <v>2.72929944135022e-10</v>
+        <v>2.729299441350359e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2770,13 +2770,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5780513937211164</v>
+        <v>-0.5780513937211161</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1144316984848932</v>
+        <v>0.1144316984848934</v>
       </c>
       <c r="D25" t="n">
-        <v>4.383605797803144e-07</v>
+        <v>4.383605797803429e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2362077053959267</v>
+        <v>0.2362077053959268</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1504768607120733</v>
+        <v>0.1504768607120735</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1164784602604647</v>
+        <v>0.1164784602604649</v>
       </c>
     </row>
     <row r="27">
@@ -2802,13 +2802,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04595559996241708</v>
+        <v>-0.04595559996241703</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1616567014228947</v>
+        <v>0.1616567014228948</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7761966040079383</v>
+        <v>0.7761966040079387</v>
       </c>
     </row>
     <row r="28">
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07605967823822857</v>
+        <v>-0.07605967823822861</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1614891401822257</v>
+        <v>0.1614891401822258</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6376482824383375</v>
+        <v>0.6376482824383377</v>
       </c>
     </row>
     <row r="29">
@@ -2834,109 +2834,109 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09626986426402311</v>
+        <v>0.09626986426402316</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543844601757254</v>
+        <v>0.1543844601757255</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5329085436093797</v>
+        <v>0.5329085436093796</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.00242675524240514</v>
+        <v>0.006290302487114348</v>
       </c>
       <c r="C30" t="n">
-        <v>0.007136997489227798</v>
+        <v>0.006868867616884191</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7338379468830419</v>
+        <v>0.3597875728110753</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.005017911290030937</v>
+        <v>-0.002426755242405131</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008305443072289021</v>
+        <v>0.007136997489227782</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5457296836910623</v>
+        <v>0.7338379468830423</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.004305141260627533</v>
+        <v>0.324898498976664</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02221655124176771</v>
+        <v>0.261225524973239</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8463475148043501</v>
+        <v>0.2135926414117487</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.02937091471947223</v>
+        <v>-0.005017911290030938</v>
       </c>
       <c r="C33" t="n">
-        <v>0.06892977188933347</v>
+        <v>0.008305443072289188</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6700356258910081</v>
+        <v>0.5457296836910703</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.3248984989766633</v>
+        <v>0.02937091471947237</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2612255249732386</v>
+        <v>0.06892977188933404</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2135926414117491</v>
+        <v>0.6700356258910092</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.006290302487114358</v>
+        <v>-0.004305141260627539</v>
       </c>
       <c r="C35" t="n">
-        <v>0.006868867616884179</v>
+        <v>0.02221655124176771</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3597875728110738</v>
+        <v>0.84634751480435</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.008</v>
+        <v>0.197</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.002</v>
+        <v>0.067</v>
       </c>
       <c r="E7" t="n">
-        <v>0.006</v>
+        <v>0.13</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.066</v>
+        <v>0.046</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.057</v>
+        <v>-0.002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.044</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.054</v>
+        <v>-0.128</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.027</v>
+        <v>0.018</v>
       </c>
       <c r="E9" t="n">
-        <v>0.027</v>
+        <v>0.11</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.041</v>
+        <v>0.107</v>
       </c>
       <c r="D10" t="n">
-        <v>0.037</v>
+        <v>0.042</v>
       </c>
       <c r="E10" t="n">
-        <v>0.004000000000000004</v>
+        <v>0.065</v>
       </c>
       <c r="F10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.007</v>
+        <v>0.227</v>
       </c>
       <c r="D11" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.018</v>
+        <v>0.203</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.074</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.042</v>
+        <v>-0.005</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03199999999999999</v>
+        <v>-0.005</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.034</v>
+        <v>-0.066</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.008</v>
+        <v>-0.057</v>
       </c>
       <c r="E13" t="n">
-        <v>0.026</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.041</v>
+        <v>0.032</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.012</v>
+        <v>0.032</v>
       </c>
       <c r="E14" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.032</v>
+        <v>-0.054</v>
       </c>
       <c r="D15" t="n">
-        <v>0.032</v>
+        <v>-0.027</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.023</v>
+        <v>0.041</v>
       </c>
       <c r="D16" t="n">
-        <v>0.011</v>
+        <v>0.037</v>
       </c>
       <c r="E16" t="n">
-        <v>0.012</v>
+        <v>0.004000000000000004</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.401</v>
+        <v>0.005</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.038</v>
+        <v>-0.012</v>
       </c>
       <c r="E17" t="n">
-        <v>0.363</v>
+        <v>-0.007</v>
       </c>
       <c r="F17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.014</v>
+        <v>-0.008</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="E18" t="n">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.143</v>
+        <v>0.022</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.042</v>
+        <v>0.015</v>
       </c>
       <c r="E19" t="n">
-        <v>0.101</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.019</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.024</v>
+        <v>-0.002</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.005000000000000001</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.041</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.002</v>
+        <v>-0.012</v>
       </c>
       <c r="E21" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.029</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.113</v>
+        <v>-0.019</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.049</v>
+        <v>-0.024</v>
       </c>
       <c r="E22" t="n">
-        <v>0.064</v>
+        <v>-0.005000000000000001</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0</v>
+        <v>-0.113</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.005</v>
+        <v>-0.049</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.005</v>
+        <v>0.064</v>
       </c>
       <c r="F23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.022</v>
+        <v>-0.143</v>
       </c>
       <c r="D24" t="n">
-        <v>0.015</v>
+        <v>-0.042</v>
       </c>
       <c r="E24" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.101</v>
       </c>
       <c r="F24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.024</v>
+        <v>-0.014</v>
       </c>
       <c r="D25" t="n">
-        <v>0.027</v>
+        <v>-0.003</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.002999999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.197</v>
+        <v>0.034</v>
       </c>
       <c r="D27" t="n">
-        <v>0.067</v>
+        <v>-0.008</v>
       </c>
       <c r="E27" t="n">
-        <v>0.13</v>
+        <v>0.026</v>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.046</v>
+        <v>-0.024</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.002</v>
+        <v>0.027</v>
       </c>
       <c r="E28" t="n">
-        <v>0.044</v>
+        <v>-0.002999999999999999</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.227</v>
+        <v>0.023</v>
       </c>
       <c r="D29" t="n">
-        <v>0.024</v>
+        <v>0.011</v>
       </c>
       <c r="E29" t="n">
-        <v>0.203</v>
+        <v>0.012</v>
       </c>
       <c r="F29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.005</v>
+        <v>-0.074</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.012</v>
+        <v>-0.042</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.007</v>
+        <v>0.03199999999999999</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.107</v>
+        <v>0.392</v>
       </c>
       <c r="D31" t="n">
-        <v>0.042</v>
+        <v>0.03</v>
       </c>
       <c r="E31" t="n">
-        <v>0.065</v>
+        <v>0.362</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,16 +1290,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.128</v>
+        <v>0.007</v>
       </c>
       <c r="D32" t="n">
-        <v>0.018</v>
+        <v>0.025</v>
       </c>
       <c r="E32" t="n">
-        <v>0.11</v>
+        <v>-0.018</v>
       </c>
       <c r="F32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
@@ -1308,7 +1308,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.392</v>
+        <v>-0.401</v>
       </c>
       <c r="D33" t="n">
-        <v>0.03</v>
+        <v>-0.038</v>
       </c>
       <c r="E33" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="F33" t="b">
         <v>0</v>
@@ -1494,16 +1494,16 @@
         <v>1.748744200678083</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09972246735548673</v>
+        <v>0.09972246735548233</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553291756211858</v>
+        <v>1.553291756211866</v>
       </c>
       <c r="E2" t="n">
-        <v>1.944196645144308</v>
+        <v>1.944196645144299</v>
       </c>
       <c r="F2" t="n">
-        <v>7.595130829916493e-69</v>
+        <v>7.595130829814058e-69</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1516,19 +1516,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02958633974415711</v>
+        <v>0.02958633974415713</v>
       </c>
       <c r="C3" t="n">
         <v>0.01822177522012756</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.006127683421677313</v>
+        <v>-0.006127683421677303</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06530036290999154</v>
+        <v>0.06530036290999157</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1044440307699914</v>
+        <v>0.1044440307699912</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1541,19 +1541,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09784011424187253</v>
+        <v>0.09784011424187246</v>
       </c>
       <c r="C4" t="n">
         <v>0.04951895669896678</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007847425598992014</v>
+        <v>0.000784742559899132</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1948954859238459</v>
+        <v>0.1948954859238458</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04817615306008694</v>
+        <v>0.0481761530600871</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1566,19 +1566,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01273797200940394</v>
+        <v>-0.01273797200940386</v>
       </c>
       <c r="C5" t="n">
         <v>0.03343233284250816</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.07826414029987555</v>
+        <v>-0.07826414029987548</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05278819628106768</v>
+        <v>0.05278819628106775</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7031976288909334</v>
+        <v>0.7031976288909352</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04927628124940884</v>
+        <v>0.04927628124940894</v>
       </c>
       <c r="C6" t="n">
         <v>0.03239456843861484</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.01421590618499418</v>
+        <v>-0.01421590618499408</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1127684686838119</v>
+        <v>0.112768468683812</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1282277489991775</v>
+        <v>0.1282277489991767</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1616,19 +1616,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01047785258090146</v>
+        <v>0.01047785258090151</v>
       </c>
       <c r="C7" t="n">
         <v>0.03252233317855407</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05326474914227657</v>
+        <v>-0.05326474914227652</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07422045430407949</v>
+        <v>0.07422045430407956</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7473208240704087</v>
+        <v>0.7473208240704075</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1641,19 +1641,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06433271843302668</v>
+        <v>0.06433271843302669</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03291080729184541</v>
+        <v>0.0329108072918454</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0001712785611285156</v>
+        <v>-0.0001712785611284878</v>
       </c>
       <c r="E8" t="n">
         <v>0.1288367154271819</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05061144476357895</v>
+        <v>0.05061144476357885</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02865140490375856</v>
+        <v>0.02865140490375861</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03191029283342592</v>
+        <v>0.0319102928334259</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.03389161978588283</v>
+        <v>-0.03389161978588275</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09119442959339995</v>
+        <v>0.09119442959339998</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3692530175492091</v>
+        <v>0.3692530175492078</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1691,19 +1691,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0009794214476962462</v>
+        <v>-0.0009794214476963115</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05063414819939278</v>
+        <v>0.05063414819939272</v>
       </c>
       <c r="D10" t="n">
         <v>-0.1002205283063697</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09826168541097723</v>
+        <v>0.09826168541097706</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9845674006463205</v>
+        <v>0.9845674006463195</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1716,16 +1716,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01946826154009432</v>
+        <v>0.01946826154009427</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05194685720438145</v>
+        <v>0.05194685720438134</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.08234570769053835</v>
+        <v>-0.08234570769053819</v>
       </c>
       <c r="E11" t="n">
-        <v>0.121282230770727</v>
+        <v>0.1212822307707267</v>
       </c>
       <c r="F11" t="n">
         <v>0.7078295534163992</v>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06785609067849586</v>
+        <v>0.0678560906784958</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05163905582747091</v>
+        <v>0.05163905582747093</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.03335459893900031</v>
+        <v>-0.03335459893900042</v>
       </c>
       <c r="E12" t="n">
         <v>0.169066780295992</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1888307512048416</v>
+        <v>0.1888307512048424</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1766,19 +1766,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04035183396023319</v>
+        <v>0.04035183396023308</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05171295167094479</v>
+        <v>0.05171295167094481</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.061003688849079</v>
+        <v>-0.06100368884907915</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1417073567695454</v>
+        <v>0.1417073567695453</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4352118346691924</v>
+        <v>0.4352118346691939</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1791,19 +1791,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01360432138726276</v>
+        <v>0.01360432138726278</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05321733263316392</v>
+        <v>0.05321733263316383</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09069973392702664</v>
+        <v>-0.09069973392702643</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1179083767015522</v>
+        <v>0.117908376701552</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7982311147396448</v>
+        <v>0.7982311147396444</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1816,19 +1816,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0540525201752838</v>
+        <v>0.05405252017528376</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05226735188844174</v>
+        <v>0.05226735188844175</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.04838960709334359</v>
+        <v>-0.04838960709334365</v>
       </c>
       <c r="E15" t="n">
         <v>0.1564946474439112</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3010639142436642</v>
+        <v>0.3010639142436645</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1841,19 +1841,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04086477158037346</v>
+        <v>0.04086477158037339</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05309945880834852</v>
+        <v>0.05309945880834849</v>
       </c>
       <c r="D16" t="n">
         <v>-0.06320825528255777</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1449377984433047</v>
+        <v>0.1449377984433046</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4415435960896881</v>
+        <v>0.4415435960896885</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1869,10 +1869,10 @@
         <v>0.01102820644228601</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05158345722977697</v>
+        <v>0.05158345722977693</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09007351192613912</v>
+        <v>-0.09007351192613905</v>
       </c>
       <c r="E17" t="n">
         <v>0.1121299248107111</v>
@@ -1894,16 +1894,16 @@
         <v>0.02900589471309425</v>
       </c>
       <c r="C18" t="n">
-        <v>0.04992506750994716</v>
+        <v>0.04992506750994719</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.06884543953213298</v>
+        <v>-0.06884543953213303</v>
       </c>
       <c r="E18" t="n">
         <v>0.1268572289583215</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5612481417346353</v>
+        <v>0.5612481417346354</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1916,19 +1916,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.009706893816720116</v>
+        <v>0.009706893816720033</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05188944681346105</v>
+        <v>0.05188944681346103</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.09199455311537021</v>
+        <v>-0.09199455311537025</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1114083407488104</v>
+        <v>0.1114083407488103</v>
       </c>
       <c r="F19" t="n">
-        <v>0.851606731564823</v>
+        <v>0.8516067315648244</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1941,19 +1941,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0129418462390937</v>
+        <v>-0.01294184623909374</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04979214122466381</v>
+        <v>0.04979214122466374</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1105326497525669</v>
+        <v>-0.1105326497525668</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08464895727437945</v>
+        <v>0.08464895727437929</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7949274527428548</v>
+        <v>0.794927452742854</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1966,19 +1966,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.004450654511219809</v>
+        <v>0.004450654511219815</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05125308284729309</v>
+        <v>0.05125308284729304</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.09600354196612225</v>
+        <v>-0.09600354196612215</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1049048509885619</v>
+        <v>0.1049048509885618</v>
       </c>
       <c r="F21" t="n">
-        <v>0.930801223412883</v>
+        <v>0.9308012234128827</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1991,19 +1991,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.01178950629292756</v>
+        <v>0.01178950629292737</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05351780370106517</v>
+        <v>0.05351780370106515</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.09310346149284458</v>
+        <v>-0.09310346149284472</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1166824740786997</v>
+        <v>0.1166824740786995</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8256442990935557</v>
+        <v>0.8256442990935584</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -2016,19 +2016,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.04500853091113263</v>
+        <v>0.0450085309111326</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05073676871697232</v>
+        <v>0.05073676871697231</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0544337084660716</v>
+        <v>-0.05443370846607161</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1444507702883369</v>
+        <v>0.1444507702883368</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3750256648141893</v>
+        <v>0.3750256648141898</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2041,19 +2041,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.09317839536589115</v>
+        <v>0.09317839536589112</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04199057011256822</v>
+        <v>0.04199057011256824</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01087839025495342</v>
+        <v>0.01087839025495335</v>
       </c>
       <c r="E24" t="n">
         <v>0.1754784004768289</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02648458550495959</v>
+        <v>0.0264845855049597</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2066,19 +2066,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.03623225650076152</v>
+        <v>0.03623225650076144</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02486297432359928</v>
+        <v>0.0248629743235993</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.01249827772203718</v>
+        <v>-0.01249827772203729</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08496279072356022</v>
+        <v>0.08496279072356018</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1450397569591422</v>
+        <v>0.1450397569591435</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2091,19 +2091,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01467109228439209</v>
+        <v>0.01467109228439208</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02811127962746581</v>
+        <v>0.02811127962746579</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.04042600334477545</v>
+        <v>-0.04042600334477541</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06976818791355963</v>
+        <v>0.06976818791355957</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6017445295692684</v>
+        <v>0.601744529569268</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2116,19 +2116,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.03310111763713029</v>
+        <v>-0.03310111763713031</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0292054538808928</v>
+        <v>0.02920545388089282</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.09034275539582573</v>
+        <v>-0.09034275539582579</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02414052012156515</v>
+        <v>0.02414052012156517</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2570512552489403</v>
+        <v>0.2570512552489407</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2141,19 +2141,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0136859607723338</v>
+        <v>-0.01368596077233376</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02963823096954</v>
+        <v>0.02963823096954001</v>
       </c>
       <c r="D28" t="n">
         <v>-0.07177582603811183</v>
       </c>
       <c r="E28" t="n">
-        <v>0.04440390449344424</v>
+        <v>0.04440390449344431</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6442483269078466</v>
+        <v>0.6442483269078475</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2166,16 +2166,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.02682587599480336</v>
+        <v>-0.02682587599480338</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02937399338914296</v>
+        <v>0.02937399338914299</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.08439784511964121</v>
+        <v>-0.08439784511964127</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03074609313003449</v>
+        <v>0.03074609313003451</v>
       </c>
       <c r="F29" t="n">
         <v>0.3611097025802034</v>
@@ -2194,16 +2194,16 @@
         <v>0.3985398745276548</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0393393327177181</v>
+        <v>0.03933933271771813</v>
       </c>
       <c r="D30" t="n">
         <v>0.3214361992250891</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4756435498302204</v>
+        <v>0.4756435498302206</v>
       </c>
       <c r="F30" t="n">
-        <v>4.032349524443835e-24</v>
+        <v>4.032349524444008e-24</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2212,23 +2212,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0010631219852765</v>
+        <v>0.4977006363722659</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001289385890041364</v>
+        <v>0.01226810100606312</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.001464027921378697</v>
+        <v>0.4736556002416826</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003590271891931697</v>
+        <v>0.5217456725028492</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4096452440067881</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2237,23 +2237,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.002088076448677744</v>
+        <v>0.001063121985276499</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001402263199247397</v>
+        <v>0.001289385890041361</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.004836461816048556</v>
+        <v>-0.001464027921378692</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0006603089186930687</v>
+        <v>0.003590271891931689</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1364673619490754</v>
+        <v>0.4096452440067876</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2269,16 +2269,16 @@
         <v>1.638429102143954</v>
       </c>
       <c r="C33" t="n">
-        <v>0.04812377374195426</v>
+        <v>0.04812377374195378</v>
       </c>
       <c r="D33" t="n">
-        <v>1.544108238809569</v>
+        <v>1.54410823880957</v>
       </c>
       <c r="E33" t="n">
         <v>1.732749965478338</v>
       </c>
       <c r="F33" t="n">
-        <v>4.628174711724608e-254</v>
+        <v>4.628174711670365e-254</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2291,19 +2291,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.001532654351402115</v>
+        <v>-0.001532654351402105</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001599885891944252</v>
+        <v>0.001599885891944241</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.00466837307898659</v>
+        <v>-0.004668373078986557</v>
       </c>
       <c r="E34" t="n">
-        <v>0.00160306437618236</v>
+        <v>0.001603064376182347</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3380742102093548</v>
+        <v>0.3380742102093544</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2312,23 +2312,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4977006363722659</v>
+        <v>-0.002088076448677741</v>
       </c>
       <c r="C35" t="n">
-        <v>0.01226810100606316</v>
+        <v>0.001402263199247397</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4736556002416825</v>
+        <v>-0.004836461816048554</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5217456725028493</v>
+        <v>0.0006603089186930713</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.1364673619490759</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2341,19 +2341,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.00315671630543928</v>
+        <v>-0.003156716305439279</v>
       </c>
       <c r="C36" t="n">
-        <v>0.00419143405202007</v>
+        <v>0.004191434052020087</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0113717760909734</v>
+        <v>-0.01137177609097343</v>
       </c>
       <c r="E36" t="n">
-        <v>0.00505834348009484</v>
+        <v>0.005058343480094874</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4513687051621523</v>
+        <v>0.4513687051621542</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.77461407358889</v>
+        <v>-2.774614073588889</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5213956350107528</v>
+        <v>0.5213956350107549</v>
       </c>
       <c r="D2" t="n">
-        <v>1.029072958037503e-07</v>
+        <v>1.029072958037635e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2418,13 +2418,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02531896946916946</v>
+        <v>-0.02531896946916956</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1001870355608946</v>
+        <v>0.1001870355608945</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8004868915759111</v>
+        <v>0.8004868915759102</v>
       </c>
     </row>
     <row r="4">
@@ -2456,7 +2456,7 @@
         <v>0.1734116198833069</v>
       </c>
       <c r="D5" t="n">
-        <v>2.525694832362419e-06</v>
+        <v>2.525694832362434e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2466,13 +2466,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03622598517976072</v>
+        <v>0.03622598517976073</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1914953081760689</v>
+        <v>0.1914953081760688</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8499562329133779</v>
+        <v>0.8499562329133776</v>
       </c>
     </row>
     <row r="7">
@@ -2482,13 +2482,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2771938342360028</v>
+        <v>0.2771938342360027</v>
       </c>
       <c r="C7" t="n">
         <v>0.1901314810930085</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1448664442117525</v>
+        <v>0.1448664442117526</v>
       </c>
     </row>
     <row r="8">
@@ -2498,13 +2498,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1053581304950989</v>
+        <v>0.1053581304950987</v>
       </c>
       <c r="C8" t="n">
-        <v>0.195344266715979</v>
+        <v>0.1953442667159791</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5896481989107898</v>
+        <v>0.5896481989107905</v>
       </c>
     </row>
     <row r="9">
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8758696511293145</v>
+        <v>0.8758696511293144</v>
       </c>
       <c r="C9" t="n">
         <v>0.1693371735726046</v>
@@ -2530,13 +2530,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04427462059794664</v>
+        <v>-0.04427462059794719</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2604040478124685</v>
+        <v>0.2604040478124692</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8649922202201148</v>
+        <v>0.8649922202201135</v>
       </c>
     </row>
     <row r="11">
@@ -2546,13 +2546,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2742205061505736</v>
+        <v>-0.274220506150574</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2787689544694698</v>
+        <v>0.2787689544694702</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3252710045288596</v>
+        <v>0.3252710045288597</v>
       </c>
     </row>
     <row r="12">
@@ -2562,13 +2562,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0819329501544412</v>
+        <v>0.08193295015444103</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2597818841250336</v>
+        <v>0.2597818841250338</v>
       </c>
       <c r="D12" t="n">
-        <v>0.752464559918951</v>
+        <v>0.7524645599189518</v>
       </c>
     </row>
     <row r="13">
@@ -2578,13 +2578,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03769699417328223</v>
+        <v>0.03769699417328207</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2573362415649832</v>
+        <v>0.2573362415649835</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8835351721093903</v>
+        <v>0.8835351721093908</v>
       </c>
     </row>
     <row r="14">
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05102687086135028</v>
+        <v>-0.05102687086135054</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2608488036216074</v>
+        <v>0.2608488036216079</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8449087216020057</v>
+        <v>0.8449087216020053</v>
       </c>
     </row>
     <row r="15">
@@ -2610,13 +2610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1194505179052272</v>
+        <v>0.1194505179052271</v>
       </c>
       <c r="C15" t="n">
         <v>0.2572736242808301</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6424373510262</v>
+        <v>0.6424373510262004</v>
       </c>
     </row>
     <row r="16">
@@ -2626,13 +2626,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.003394520999805274</v>
+        <v>-0.003394520999805412</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2383941217340667</v>
+        <v>0.2383941217340666</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9886392149415379</v>
+        <v>0.9886392149415375</v>
       </c>
     </row>
     <row r="17">
@@ -2642,13 +2642,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1051737680003746</v>
+        <v>0.1051737680003743</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2544989159147915</v>
+        <v>0.2544989159147921</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6794174396292689</v>
+        <v>0.6794174396292707</v>
       </c>
     </row>
     <row r="18">
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1377738518166146</v>
+        <v>-0.1377738518166148</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2637734916431445</v>
+        <v>0.2637734916431448</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6014483864186184</v>
+        <v>0.6014483864186186</v>
       </c>
     </row>
     <row r="19">
@@ -2674,13 +2674,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02393490642264839</v>
+        <v>-0.02393490642264861</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2529805715426139</v>
+        <v>0.2529805715426145</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9246233049950185</v>
+        <v>0.924623304995018</v>
       </c>
     </row>
     <row r="20">
@@ -2690,13 +2690,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.07301273583930051</v>
+        <v>-0.07301273583930061</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2675190900686554</v>
+        <v>0.2675190900686556</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7849106151948602</v>
+        <v>0.7849106151948601</v>
       </c>
     </row>
     <row r="21">
@@ -2706,13 +2706,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2069135147918233</v>
+        <v>0.2069135147918231</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2442870989291298</v>
+        <v>0.2442870989291301</v>
       </c>
       <c r="D21" t="n">
-        <v>0.396989777761073</v>
+        <v>0.3969897777610738</v>
       </c>
     </row>
     <row r="22">
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1717092932306347</v>
+        <v>-0.1717092932306346</v>
       </c>
       <c r="C22" t="n">
-        <v>0.26961908280943</v>
+        <v>0.2696190828094302</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5242168027309879</v>
+        <v>0.5242168027309888</v>
       </c>
     </row>
     <row r="23">
@@ -2738,13 +2738,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5023322926397007</v>
+        <v>-0.502332292639701</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2872431741192606</v>
+        <v>0.2872431741192609</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08032473613005404</v>
+        <v>0.08032473613005409</v>
       </c>
     </row>
     <row r="24">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9363452786511914</v>
+        <v>0.9363452786511915</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1483102369545483</v>
+        <v>0.1483102369545484</v>
       </c>
       <c r="D24" t="n">
-        <v>2.729299441350359e-10</v>
+        <v>2.729299441350379e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2773,10 +2773,10 @@
         <v>-0.5780513937211161</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1144316984848934</v>
+        <v>0.1144316984848936</v>
       </c>
       <c r="D25" t="n">
-        <v>4.383605797803429e-07</v>
+        <v>4.383605797803591e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2362077053959268</v>
+        <v>0.2362077053959266</v>
       </c>
       <c r="C26" t="n">
         <v>0.1504768607120735</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1164784602604649</v>
+        <v>0.1164784602604652</v>
       </c>
     </row>
     <row r="27">
@@ -2802,13 +2802,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04595559996241703</v>
+        <v>-0.0459555999624169</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1616567014228948</v>
+        <v>0.1616567014228946</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7761966040079387</v>
+        <v>0.7761966040079391</v>
       </c>
     </row>
     <row r="28">
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07605967823822861</v>
+        <v>-0.07605967823822846</v>
       </c>
       <c r="C28" t="n">
         <v>0.1614891401822258</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6376482824383377</v>
+        <v>0.6376482824383383</v>
       </c>
     </row>
     <row r="29">
@@ -2834,45 +2834,45 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09626986426402316</v>
+        <v>0.09626986426402322</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543844601757255</v>
+        <v>0.1543844601757254</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5329085436093796</v>
+        <v>0.5329085436093792</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.006290302487114348</v>
+        <v>0.02937091471947224</v>
       </c>
       <c r="C30" t="n">
-        <v>0.006868867616884191</v>
+        <v>0.06892977188933404</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3597875728110753</v>
+        <v>0.6700356258910105</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.002426755242405131</v>
+        <v>0.006290302487114353</v>
       </c>
       <c r="C31" t="n">
-        <v>0.007136997489227782</v>
+        <v>0.006868867616884182</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7338379468830423</v>
+        <v>0.3597875728110742</v>
       </c>
     </row>
     <row r="32">
@@ -2882,13 +2882,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.324898498976664</v>
+        <v>0.3248984989766634</v>
       </c>
       <c r="C32" t="n">
-        <v>0.261225524973239</v>
+        <v>0.2612255249732404</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2135926414117487</v>
+        <v>0.2135926414117519</v>
       </c>
     </row>
     <row r="33">
@@ -2898,29 +2898,29 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.005017911290030938</v>
+        <v>-0.005017911290030934</v>
       </c>
       <c r="C33" t="n">
-        <v>0.008305443072289188</v>
+        <v>0.008305443072289176</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5457296836910703</v>
+        <v>0.54572968369107</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.02937091471947237</v>
+        <v>-0.002426755242405132</v>
       </c>
       <c r="C34" t="n">
-        <v>0.06892977188933404</v>
+        <v>0.007136997489227781</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6700356258910092</v>
+        <v>0.7338379468830423</v>
       </c>
     </row>
     <row r="35">
@@ -2930,13 +2930,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.004305141260627539</v>
+        <v>-0.004305141260627556</v>
       </c>
       <c r="C35" t="n">
-        <v>0.02221655124176771</v>
+        <v>0.02221655124176754</v>
       </c>
       <c r="D35" t="n">
-        <v>0.84634751480435</v>
+        <v>0.8463475148043482</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.215</v>
+        <v>0.351</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.058</v>
+        <v>0.016</v>
       </c>
       <c r="E6" t="n">
-        <v>0.157</v>
+        <v>0.335</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.392</v>
+        <v>-0.215</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.027</v>
+        <v>-0.058</v>
       </c>
       <c r="E7" t="n">
-        <v>0.365</v>
+        <v>0.157</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.095</v>
+        <v>-0.001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005</v>
+        <v>-0.001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.054</v>
+        <v>0.044</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.023</v>
+        <v>0.027</v>
       </c>
       <c r="E9" t="n">
-        <v>0.031</v>
+        <v>0.017</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.036</v>
+        <v>0.033</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.001</v>
+        <v>0.025</v>
       </c>
       <c r="E10" t="n">
-        <v>0.035</v>
+        <v>0.008</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.044</v>
+        <v>0.013</v>
       </c>
       <c r="D11" t="n">
-        <v>0.027</v>
+        <v>0.007</v>
       </c>
       <c r="E11" t="n">
-        <v>0.017</v>
+        <v>0.005999999999999999</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.033</v>
+        <v>0.368</v>
       </c>
       <c r="D13" t="n">
-        <v>0.025</v>
+        <v>0.004</v>
       </c>
       <c r="E13" t="n">
-        <v>0.008</v>
+        <v>0.364</v>
       </c>
       <c r="F13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.351</v>
+        <v>-0.012</v>
       </c>
       <c r="D14" t="n">
-        <v>0.016</v>
+        <v>0.006</v>
       </c>
       <c r="E14" t="n">
-        <v>0.335</v>
+        <v>0.006</v>
       </c>
       <c r="F14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.019</v>
+        <v>0.036</v>
       </c>
       <c r="D15" t="n">
-        <v>0.007</v>
+        <v>-0.001</v>
       </c>
       <c r="E15" t="n">
-        <v>0.012</v>
+        <v>0.035</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.185</v>
+        <v>-0.181</v>
       </c>
       <c r="D16" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="E16" t="n">
-        <v>0.172</v>
+        <v>0.167</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.096</v>
+        <v>0.01</v>
       </c>
       <c r="D17" t="n">
-        <v>0.017</v>
+        <v>0.004</v>
       </c>
       <c r="E17" t="n">
-        <v>0.079</v>
+        <v>0.006</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.09</v>
+        <v>-0.019</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.029</v>
+        <v>0.007</v>
       </c>
       <c r="E18" t="n">
-        <v>0.061</v>
+        <v>0.012</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.181</v>
+        <v>0.007</v>
       </c>
       <c r="D19" t="n">
-        <v>0.014</v>
+        <v>-0.006</v>
       </c>
       <c r="E19" t="n">
-        <v>0.167</v>
+        <v>0.001</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.007</v>
+        <v>0.014</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.006</v>
+        <v>0.017</v>
       </c>
       <c r="E20" t="n">
-        <v>0.001</v>
+        <v>-0.003000000000000001</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.001</v>
+        <v>0.059</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.001</v>
+        <v>0.021</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.03799999999999999</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.013</v>
+        <v>-0.054</v>
       </c>
       <c r="D23" t="n">
-        <v>0.007</v>
+        <v>-0.023</v>
       </c>
       <c r="E23" t="n">
-        <v>0.005999999999999999</v>
+        <v>0.031</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.059</v>
+        <v>0.075</v>
       </c>
       <c r="D24" t="n">
-        <v>0.021</v>
+        <v>0.004</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03799999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.008</v>
+        <v>-0.015</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.007</v>
+        <v>-0.03</v>
       </c>
       <c r="E25" t="n">
-        <v>0.001</v>
+        <v>-0.015</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.014</v>
+        <v>-0.095</v>
       </c>
       <c r="D26" t="n">
-        <v>0.017</v>
+        <v>0.005</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.003000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.012</v>
+        <v>0.076</v>
       </c>
       <c r="D27" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.006</v>
+        <v>0.076</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.368</v>
+        <v>-0.096</v>
       </c>
       <c r="D28" t="n">
-        <v>0.004</v>
+        <v>0.017</v>
       </c>
       <c r="E28" t="n">
-        <v>0.364</v>
+        <v>0.079</v>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.015</v>
+        <v>-0.008</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.03</v>
+        <v>-0.007</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.015</v>
+        <v>0.001</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.076</v>
+        <v>0.185</v>
       </c>
       <c r="D30" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="F30" t="b">
         <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="F30" t="b">
-        <v>1</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01</v>
+        <v>-0.392</v>
       </c>
       <c r="D31" t="n">
-        <v>0.004</v>
+        <v>-0.027</v>
       </c>
       <c r="E31" t="n">
-        <v>0.006</v>
+        <v>0.365</v>
       </c>
       <c r="F31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.075</v>
+        <v>-0.09</v>
       </c>
       <c r="D32" t="n">
-        <v>0.004</v>
+        <v>-0.029</v>
       </c>
       <c r="E32" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.061</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1394,16 +1394,16 @@
         <v>0.9955799696542841</v>
       </c>
       <c r="D2" t="n">
-        <v>0.162954385760132</v>
+        <v>0.1629543857601319</v>
       </c>
       <c r="E2" t="n">
-        <v>1.864929480836646</v>
+        <v>1.864929480836645</v>
       </c>
       <c r="F2" t="n">
         <v>1.150690388380934</v>
       </c>
       <c r="G2" t="n">
-        <v>1.864005612713848</v>
+        <v>1.864005612713847</v>
       </c>
     </row>
   </sheetData>
@@ -1467,16 +1467,16 @@
         <v>1.493998113457369</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09154176342090883</v>
+        <v>0.09154176342090374</v>
       </c>
       <c r="D2" t="n">
-        <v>1.314579554071102</v>
+        <v>1.314579554071111</v>
       </c>
       <c r="E2" t="n">
-        <v>1.673416672843637</v>
+        <v>1.673416672843626</v>
       </c>
       <c r="F2" t="n">
-        <v>7.067206153169928e-60</v>
+        <v>7.067206153065696e-60</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01139734884641806</v>
+        <v>0.01139734884641807</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01836912354870617</v>
+        <v>0.01836912354870615</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02460547173661261</v>
+        <v>-0.02460547173661256</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04740016942944874</v>
+        <v>0.04740016942944871</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5349534598931436</v>
+        <v>0.5349534598931428</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.09369904833157616</v>
+        <v>-0.09369904833157612</v>
       </c>
       <c r="C4" t="n">
         <v>0.04522288491293568</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1823342740379299</v>
+        <v>-0.1823342740379298</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.005063822625222439</v>
+        <v>-0.005063822625222411</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03827115219154165</v>
+        <v>0.03827115219154168</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01066467357152958</v>
+        <v>-0.01066467357152956</v>
       </c>
       <c r="C5" t="n">
         <v>0.02981982333274043</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.069110453329048</v>
+        <v>-0.06911045332904799</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04778110618598884</v>
+        <v>0.04778110618598886</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7206149497742431</v>
+        <v>0.7206149497742436</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.0430149299782906</v>
+        <v>-0.04301492997829071</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03066350771200719</v>
+        <v>0.03066350771200718</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1031143007334909</v>
+        <v>-0.103114300733491</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01708444077690968</v>
+        <v>0.01708444077690955</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1606749173778492</v>
+        <v>0.160674917377848</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.000958159133144368</v>
+        <v>0.0009581591331443899</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02954143714616892</v>
+        <v>0.02954143714616891</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05694199372490043</v>
+        <v>-0.05694199372490039</v>
       </c>
       <c r="E7" t="n">
         <v>0.05885831199118918</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9741256203875792</v>
+        <v>0.9741256203875787</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.01499471859888911</v>
+        <v>-0.01499471859888913</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03011722069603005</v>
+        <v>0.03011722069603003</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.07402338647755236</v>
+        <v>-0.07402338647755233</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04403394927977412</v>
+        <v>0.04403394927977407</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6185696367956144</v>
+        <v>0.6185696367956137</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009760945713619089</v>
+        <v>0.009760945713619056</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02969887927955249</v>
+        <v>0.02969887927955247</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.04844778805550667</v>
+        <v>-0.04844778805550665</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06796967948274485</v>
+        <v>0.06796967948274475</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7424098394948964</v>
+        <v>0.742409839494897</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.008945036718057835</v>
+        <v>0.008945036718057981</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05227344659369313</v>
+        <v>0.05227344659369305</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.09350903595335866</v>
+        <v>-0.09350903595335837</v>
       </c>
       <c r="E10" t="n">
         <v>0.1113991093894743</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8641293418452056</v>
+        <v>0.8641293418452032</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.07294946240716801</v>
+        <v>-0.07294946240716796</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04956147246244856</v>
+        <v>0.04956147246244858</v>
       </c>
       <c r="D11" t="n">
         <v>-0.1700881634543409</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02418923864000483</v>
+        <v>0.02418923864000493</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1410482591329775</v>
+        <v>0.141048259132978</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.0866234227437129</v>
+        <v>-0.08662342274371281</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05089844563154311</v>
+        <v>0.05089844563154302</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1863825430506074</v>
+        <v>-0.1863825430506072</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01313569756318164</v>
+        <v>0.01313569756318156</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08877648025963143</v>
+        <v>0.0887764802596312</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.008024749836483989</v>
+        <v>-0.00802474983648396</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0511329505696971</v>
+        <v>0.05113295056969708</v>
       </c>
       <c r="D13" t="n">
         <v>-0.1082434913763571</v>
       </c>
       <c r="E13" t="n">
-        <v>0.09219399170338916</v>
+        <v>0.09219399170338914</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8752929892942484</v>
+        <v>0.8752929892942487</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.0434055775908031</v>
+        <v>-0.04340557759080323</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05045929460802636</v>
+        <v>0.05045929460802622</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1423039777078309</v>
+        <v>-0.1423039777078308</v>
       </c>
       <c r="E14" t="n">
-        <v>0.05549282252622471</v>
+        <v>0.0554928225262243</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3896734268082872</v>
+        <v>0.3896734268082844</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.04574671530427657</v>
+        <v>-0.04574671530427653</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04961392181428283</v>
+        <v>0.04961392181428274</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1429882151920571</v>
+        <v>-0.1429882151920568</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05149478458350391</v>
+        <v>0.05149478458350377</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3565004068554812</v>
+        <v>0.3565004068554808</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.03713592023139942</v>
+        <v>-0.03713592023139934</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0501047234776117</v>
+        <v>0.05010472347761165</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1353393737028568</v>
+        <v>-0.1353393737028566</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06106753324005801</v>
+        <v>0.06106753324005797</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4585927625445326</v>
+        <v>0.4585927625445331</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.01948239245873595</v>
+        <v>-0.01948239245873583</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05062347938805212</v>
+        <v>0.05062347938805207</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1187025888314239</v>
+        <v>-0.1187025888314237</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07973780391395199</v>
+        <v>0.07973780391395201</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7003493364163532</v>
+        <v>0.7003493364163547</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.0289754764427335</v>
+        <v>-0.02897547644273349</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05100630816200045</v>
+        <v>0.05100630816200025</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1289460034246058</v>
+        <v>-0.1289460034246054</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07099505053913879</v>
+        <v>0.07099505053913839</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5699831381275162</v>
+        <v>0.5699831381275147</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.04008864287509659</v>
+        <v>-0.0400886428750965</v>
       </c>
       <c r="C19" t="n">
-        <v>0.049962567227668</v>
+        <v>0.04996256722766793</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1380134752164871</v>
+        <v>-0.1380134752164869</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05783618946629392</v>
+        <v>0.05783618946629386</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4223369033872226</v>
+        <v>0.4223369033872229</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,13 +1914,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.08980962914662674</v>
+        <v>-0.08980962914662666</v>
       </c>
       <c r="C20" t="n">
-        <v>0.049560306065848</v>
+        <v>0.04956030606584796</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1869460440984708</v>
+        <v>-0.1869460440984706</v>
       </c>
       <c r="E20" t="n">
         <v>0.007326785805217312</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.003397924751943089</v>
+        <v>0.003397924751943129</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04891083189773254</v>
+        <v>0.04891083189773243</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.09246554422150555</v>
+        <v>-0.0924655442215053</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09926139372539172</v>
+        <v>0.09926139372539156</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9446140588838081</v>
+        <v>0.9446140588838075</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.005820590202436503</v>
+        <v>-0.005820590202436421</v>
       </c>
       <c r="C22" t="n">
-        <v>0.04992222605418426</v>
+        <v>0.0499222260541841</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1036663552967048</v>
+        <v>-0.1036663552967044</v>
       </c>
       <c r="E22" t="n">
-        <v>0.09202517489183179</v>
+        <v>0.09202517489183155</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9071824564981807</v>
+        <v>0.9071824564981817</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,16 +1989,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.060918825403517</v>
+        <v>-0.06091882540351694</v>
       </c>
       <c r="C23" t="n">
-        <v>0.04983273321557469</v>
+        <v>0.04983273321557465</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1585891877572363</v>
+        <v>-0.1585891877572361</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03675153695020227</v>
+        <v>0.03675153695020223</v>
       </c>
       <c r="F23" t="n">
         <v>0.2215314283124583</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.04546552218884722</v>
+        <v>-0.04546552218884721</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04088368473780888</v>
+        <v>0.04088368473780889</v>
       </c>
       <c r="D24" t="n">
         <v>-0.1255960718302425</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03466502745254807</v>
+        <v>0.03466502745254811</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2661080237958383</v>
+        <v>0.2661080237958385</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.005855003749821483</v>
+        <v>0.0058550037498215</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02357096913273561</v>
+        <v>0.02357096913273558</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.04034324683104563</v>
+        <v>-0.04034324683104555</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05205325433068859</v>
+        <v>0.05205325433068855</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8038257535625446</v>
+        <v>0.8038257535625438</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.02022035479316614</v>
+        <v>0.0202203547931663</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02847209635064421</v>
+        <v>0.0284720963506442</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03558392861845081</v>
+        <v>-0.03558392861845063</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07602463820478308</v>
+        <v>0.07602463820478322</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4775916198870095</v>
+        <v>0.4775916198870058</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.01017504924390034</v>
+        <v>0.01017504924390035</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02920817082181944</v>
+        <v>0.02920817082181942</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.04707191362115943</v>
+        <v>-0.04707191362115939</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06742201210896011</v>
+        <v>0.06742201210896009</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7275675029194186</v>
+        <v>0.7275675029194182</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.03075274291213686</v>
+        <v>0.03075274291213688</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02852520938942749</v>
+        <v>0.02852520938942745</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.02515564014260479</v>
+        <v>-0.02515564014260472</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08666112596687851</v>
+        <v>0.08666112596687847</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2809935950997039</v>
+        <v>0.280993595099703</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0143177518740259</v>
+        <v>-0.01431775187402591</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02757795020140895</v>
+        <v>0.02757795020140894</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.06836954103622657</v>
+        <v>-0.06836954103622656</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03973403728817478</v>
+        <v>0.03973403728817473</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6036394802206333</v>
+        <v>0.6036394802206331</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3642249454799705</v>
+        <v>0.3642249454799706</v>
       </c>
       <c r="C30" t="n">
         <v>0.03859338896492542</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2885832930673711</v>
+        <v>0.2885832930673712</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4398665978925699</v>
+        <v>0.43986659789257</v>
       </c>
       <c r="F30" t="n">
-        <v>3.817947647451507e-21</v>
+        <v>3.817947647451479e-21</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0002855410455972139</v>
+        <v>0.5808547372361993</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001532410754135861</v>
+        <v>0.01060596000933938</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.002717928842030937</v>
+        <v>0.560067437596422</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003289010933225364</v>
+        <v>0.6016420368759766</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8521824265148036</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5808547372361993</v>
+        <v>0.0002855410455972268</v>
       </c>
       <c r="C32" t="n">
-        <v>0.01060596000933946</v>
+        <v>0.001532410754135844</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5600674375964219</v>
+        <v>-0.002717928842030891</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6016420368759767</v>
+        <v>0.003289010933225345</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.8521824265147955</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.002242891807688964</v>
+        <v>0.002242891807688963</v>
       </c>
       <c r="C33" t="n">
         <v>0.001173661517189242</v>
       </c>
       <c r="D33" t="n">
-        <v>-5.744249604258764e-05</v>
+        <v>-5.744249604258938e-05</v>
       </c>
       <c r="E33" t="n">
         <v>0.004543226111420515</v>
       </c>
       <c r="F33" t="n">
-        <v>0.05600188208985725</v>
+        <v>0.05600188208985742</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.001854532319157673</v>
+        <v>0.003217439514964093</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0012435949802524</v>
+        <v>0.003983890433832253</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.004291933691807177</v>
+        <v>-0.004590842253700773</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0005828690534918314</v>
+        <v>0.01102572128362896</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1358913747251274</v>
+        <v>0.4193137172191305</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.003217439514964078</v>
+        <v>-0.001854532319157672</v>
       </c>
       <c r="C35" t="n">
-        <v>0.003983890433832237</v>
+        <v>0.001243594980252398</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.004590842253700758</v>
+        <v>-0.004291933691807172</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01102572128362891</v>
+        <v>0.0005828690534918283</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4193137172191307</v>
+        <v>0.135891374725127</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.427664644175296</v>
+        <v>-2.427664644175297</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5181657220038096</v>
+        <v>0.518165722003795</v>
       </c>
       <c r="D2" t="n">
-        <v>2.798063509202437e-06</v>
+        <v>2.798063509200602e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04283704187763173</v>
+        <v>0.04283704187763186</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1065056610557123</v>
+        <v>0.1065056610557124</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6875336293530993</v>
+        <v>0.6875336293530986</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3420089197228885</v>
+        <v>0.3420089197228886</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2258273108558931</v>
+        <v>0.2258273108558932</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1299064164023923</v>
+        <v>0.1299064164023925</v>
       </c>
     </row>
     <row r="5">
@@ -2401,10 +2401,10 @@
         <v>0.7568550919253108</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1749116140278904</v>
+        <v>0.1749116140278903</v>
       </c>
       <c r="D5" t="n">
-        <v>1.511047971683326e-05</v>
+        <v>1.511047971683322e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2420,7 +2420,7 @@
         <v>0.2139666880119049</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3950624226561795</v>
+        <v>0.3950624226561794</v>
       </c>
     </row>
     <row r="7">
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1330552971690139</v>
+        <v>0.1330552971690138</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1953952819476561</v>
+        <v>0.195395281947656</v>
       </c>
       <c r="D7" t="n">
         <v>0.495900279135249</v>
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09728047689820782</v>
+        <v>-0.09728047689820798</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2107853049245228</v>
+        <v>0.210785304924523</v>
       </c>
       <c r="D8" t="n">
-        <v>0.644429513016221</v>
+        <v>0.6444295130162208</v>
       </c>
     </row>
     <row r="9">
@@ -2465,7 +2465,7 @@
         <v>1.068702246714659</v>
       </c>
       <c r="C9" t="n">
-        <v>0.170416507653911</v>
+        <v>0.1704165076539109</v>
       </c>
       <c r="D9" t="n">
         <v>3.584618716992764e-10</v>
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09164285114131059</v>
+        <v>0.09164285114131063</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2821462910028383</v>
+        <v>0.2821462910028389</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7453277880093383</v>
+        <v>0.7453277880093387</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2093667135385762</v>
+        <v>0.2093667135385763</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2718908402685894</v>
+        <v>0.2718908402685901</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4412764034926273</v>
+        <v>0.4412764034926281</v>
       </c>
     </row>
     <row r="12">
@@ -2513,10 +2513,10 @@
         <v>-0.2458167359844366</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3060864204610708</v>
+        <v>0.3060864204610709</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4219193324752599</v>
+        <v>0.4219193324752601</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2480605146834356</v>
+        <v>0.2480605146834357</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2698784026653985</v>
+        <v>0.2698784026653989</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3580136685717247</v>
+        <v>0.3580136685717253</v>
       </c>
     </row>
     <row r="14">
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2887265920666393</v>
+        <v>0.2887265920666394</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2797122646585146</v>
+        <v>0.2797122646585147</v>
       </c>
       <c r="D14" t="n">
         <v>0.3019657220075026</v>
@@ -2561,10 +2561,10 @@
         <v>0.336456969341774</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2683702941076246</v>
+        <v>0.2683702941076241</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2099495347382759</v>
+        <v>0.209949534738275</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1212332819747692</v>
+        <v>0.1212332819747694</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2679493505870749</v>
+        <v>0.2679493505870756</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6509459134758502</v>
+        <v>0.6509459134758506</v>
       </c>
     </row>
     <row r="17">
@@ -2593,10 +2593,10 @@
         <v>0.1766572982617266</v>
       </c>
       <c r="C17" t="n">
-        <v>0.27523508908112</v>
+        <v>0.2752350890811207</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5209761107851423</v>
+        <v>0.5209761107851434</v>
       </c>
     </row>
     <row r="18">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3813830960578523</v>
+        <v>0.3813830960578521</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2677517444468908</v>
+        <v>0.2677517444468906</v>
       </c>
       <c r="D18" t="n">
         <v>0.1543334033865622</v>
@@ -2625,10 +2625,10 @@
         <v>0.1210111614869998</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2775843004204008</v>
+        <v>0.2775843004204014</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6628774877860033</v>
+        <v>0.6628774877860041</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2255181952666772</v>
+        <v>0.2255181952666774</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2783783956071244</v>
+        <v>0.2783783956071254</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4178747418803487</v>
+        <v>0.4178747418803501</v>
       </c>
     </row>
     <row r="21">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.04646654583854209</v>
+        <v>0.04646654583854215</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2845286078456555</v>
+        <v>0.2845286078456557</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8702738657351099</v>
+        <v>0.8702738657351098</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.02162756752909087</v>
+        <v>-0.02162756752909093</v>
       </c>
       <c r="C23" t="n">
-        <v>0.292590547588469</v>
+        <v>0.2925905475884682</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9410760153784373</v>
+        <v>0.941076015378437</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8764973807420282</v>
+        <v>0.8764973807420283</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1598667289796822</v>
+        <v>0.1598667289796823</v>
       </c>
       <c r="D24" t="n">
-        <v>4.189413124540363e-08</v>
+        <v>4.189413124540437e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5923085897232844</v>
+        <v>-0.5923085897232843</v>
       </c>
       <c r="C25" t="n">
         <v>0.1169262828732782</v>
       </c>
       <c r="D25" t="n">
-        <v>4.069915021574037e-07</v>
+        <v>4.069915021574112e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2740,7 +2740,7 @@
         <v>0.1507698258117117</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3579479313928083</v>
+        <v>0.3579479313928081</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08444119781568341</v>
+        <v>-0.08444119781568352</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1574438589059062</v>
+        <v>0.157443858905906</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5917334279738693</v>
+        <v>0.5917334279738683</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.111408531619885</v>
+        <v>-0.1114085316198852</v>
       </c>
       <c r="C28" t="n">
         <v>0.1483441008175727</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4526440879579785</v>
+        <v>0.4526440879579775</v>
       </c>
     </row>
     <row r="29">
@@ -2782,45 +2782,45 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3220151818496276</v>
+        <v>-0.3220151818496279</v>
       </c>
       <c r="C29" t="n">
         <v>0.1549982402231347</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03775166539448383</v>
+        <v>0.03775166539448364</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.01293860122823145</v>
+        <v>-0.03120747680900953</v>
       </c>
       <c r="C30" t="n">
-        <v>0.008183645815534294</v>
+        <v>0.05994942728922986</v>
       </c>
       <c r="D30" t="n">
-        <v>0.113870852015484</v>
+        <v>0.6026709615967232</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.03120747680900968</v>
+        <v>-0.01293860122823144</v>
       </c>
       <c r="C31" t="n">
-        <v>0.05994942728923026</v>
+        <v>0.008183645815534315</v>
       </c>
       <c r="D31" t="n">
-        <v>0.602670961596724</v>
+        <v>0.1138708520154851</v>
       </c>
     </row>
     <row r="32">
@@ -2833,42 +2833,42 @@
         <v>0.01489842147412547</v>
       </c>
       <c r="C32" t="n">
-        <v>0.007094501199577943</v>
+        <v>0.00709450119957797</v>
       </c>
       <c r="D32" t="n">
-        <v>0.03572922606502613</v>
+        <v>0.03572922606502685</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.00258063803607496</v>
+        <v>0.01847772081409662</v>
       </c>
       <c r="C33" t="n">
-        <v>0.007292353686099011</v>
+        <v>0.02286223089800336</v>
       </c>
       <c r="D33" t="n">
-        <v>0.723426769534945</v>
+        <v>0.4189637308910251</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0184777208140966</v>
+        <v>0.002580638036074957</v>
       </c>
       <c r="C34" t="n">
-        <v>0.02286223089800328</v>
+        <v>0.007292353686099036</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4189637308910242</v>
+        <v>0.7234267695349461</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.351</v>
+        <v>-0.001</v>
       </c>
       <c r="D6" t="n">
-        <v>0.016</v>
+        <v>-0.001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.335</v>
+        <v>0</v>
       </c>
       <c r="F6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.215</v>
+        <v>-0.096</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.058</v>
+        <v>0.017</v>
       </c>
       <c r="E7" t="n">
-        <v>0.157</v>
+        <v>0.079</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.001</v>
+        <v>0.059</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.001</v>
+        <v>0.021</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.03799999999999999</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.044</v>
+        <v>-0.007</v>
       </c>
       <c r="D9" t="n">
-        <v>0.027</v>
+        <v>-0.028</v>
       </c>
       <c r="E9" t="n">
-        <v>0.017</v>
+        <v>-0.021</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.013</v>
+        <v>0.368</v>
       </c>
       <c r="D11" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="E11" t="n">
-        <v>0.005999999999999999</v>
+        <v>0.364</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.001</v>
+        <v>0.014</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.007</v>
+        <v>0.017</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.006</v>
+        <v>-0.003000000000000001</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.368</v>
+        <v>0.044</v>
       </c>
       <c r="D13" t="n">
-        <v>0.004</v>
+        <v>0.027</v>
       </c>
       <c r="E13" t="n">
-        <v>0.364</v>
+        <v>0.017</v>
       </c>
       <c r="F13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.012</v>
+        <v>-0.181</v>
       </c>
       <c r="D14" t="n">
-        <v>0.006</v>
+        <v>0.014</v>
       </c>
       <c r="E14" t="n">
-        <v>0.006</v>
+        <v>0.167</v>
       </c>
       <c r="F14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.036</v>
+        <v>0.076</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.035</v>
+        <v>0.076</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.181</v>
+        <v>0.01</v>
       </c>
       <c r="D16" t="n">
-        <v>0.014</v>
+        <v>0.004</v>
       </c>
       <c r="E16" t="n">
-        <v>0.167</v>
+        <v>0.006</v>
       </c>
       <c r="F16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01</v>
+        <v>-0.008</v>
       </c>
       <c r="D17" t="n">
-        <v>0.004</v>
+        <v>-0.007</v>
       </c>
       <c r="E17" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.019</v>
+        <v>0.351</v>
       </c>
       <c r="D18" t="n">
-        <v>0.007</v>
+        <v>0.016</v>
       </c>
       <c r="E18" t="n">
-        <v>0.012</v>
+        <v>0.335</v>
       </c>
       <c r="F18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.007</v>
+        <v>-0.012</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.006</v>
+        <v>0.006</v>
       </c>
       <c r="E19" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.014</v>
+        <v>-0.054</v>
       </c>
       <c r="D20" t="n">
-        <v>0.017</v>
+        <v>-0.023</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.003000000000000001</v>
+        <v>0.031</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.059</v>
+        <v>0.185</v>
       </c>
       <c r="D21" t="n">
-        <v>0.021</v>
+        <v>0.013</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03799999999999999</v>
+        <v>0.172</v>
       </c>
       <c r="F21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.007</v>
+        <v>-0.215</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.028</v>
+        <v>-0.058</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.021</v>
+        <v>0.157</v>
       </c>
       <c r="F22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.054</v>
+        <v>-0.001</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.023</v>
+        <v>-0.007</v>
       </c>
       <c r="E23" t="n">
-        <v>0.031</v>
+        <v>-0.006</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.075</v>
+        <v>-0.095</v>
       </c>
       <c r="D24" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="E24" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.015</v>
+        <v>0.013</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.03</v>
+        <v>0.007</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.015</v>
+        <v>0.005999999999999999</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.095</v>
+        <v>0.036</v>
       </c>
       <c r="D26" t="n">
-        <v>0.005</v>
+        <v>-0.001</v>
       </c>
       <c r="E26" t="n">
-        <v>0.09</v>
+        <v>0.035</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.076</v>
+        <v>0.075</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="E27" t="n">
-        <v>0.076</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.096</v>
+        <v>-0.019</v>
       </c>
       <c r="D28" t="n">
-        <v>0.017</v>
+        <v>0.007</v>
       </c>
       <c r="E28" t="n">
-        <v>0.079</v>
+        <v>0.012</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.008</v>
+        <v>-0.392</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.007</v>
+        <v>-0.027</v>
       </c>
       <c r="E29" t="n">
-        <v>0.001</v>
+        <v>0.365</v>
       </c>
       <c r="F29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.185</v>
+        <v>-0.015</v>
       </c>
       <c r="D30" t="n">
-        <v>0.013</v>
+        <v>-0.03</v>
       </c>
       <c r="E30" t="n">
-        <v>0.172</v>
+        <v>-0.015</v>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.392</v>
+        <v>0.007</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.027</v>
+        <v>-0.006</v>
       </c>
       <c r="E31" t="n">
-        <v>0.365</v>
+        <v>0.001</v>
       </c>
       <c r="F31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1397,13 +1397,13 @@
         <v>0.1629543857601319</v>
       </c>
       <c r="E2" t="n">
-        <v>1.864929480836645</v>
+        <v>1.864929480836644</v>
       </c>
       <c r="F2" t="n">
         <v>1.150690388380934</v>
       </c>
       <c r="G2" t="n">
-        <v>1.864005612713847</v>
+        <v>1.864005612713846</v>
       </c>
     </row>
   </sheetData>
@@ -1467,16 +1467,16 @@
         <v>1.493998113457369</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09154176342090374</v>
+        <v>0.091541763420905</v>
       </c>
       <c r="D2" t="n">
-        <v>1.314579554071111</v>
+        <v>1.314579554071109</v>
       </c>
       <c r="E2" t="n">
-        <v>1.673416672843626</v>
+        <v>1.673416672843629</v>
       </c>
       <c r="F2" t="n">
-        <v>7.067206153065696e-60</v>
+        <v>7.0672061530913e-60</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01139734884641807</v>
+        <v>0.01139734884641808</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01836912354870615</v>
+        <v>0.01836912354870616</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02460547173661256</v>
+        <v>-0.02460547173661258</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04740016942944871</v>
+        <v>0.04740016942944873</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5349534598931428</v>
+        <v>0.5349534598931429</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.09369904833157612</v>
+        <v>-0.09369904833157605</v>
       </c>
       <c r="C4" t="n">
         <v>0.04522288491293568</v>
@@ -1523,10 +1523,10 @@
         <v>-0.1823342740379298</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.005063822625222411</v>
+        <v>-0.005063822625222328</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03827115219154168</v>
+        <v>0.03827115219154187</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01066467357152956</v>
+        <v>-0.01066467357152957</v>
       </c>
       <c r="C5" t="n">
         <v>0.02981982333274043</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06911045332904799</v>
+        <v>-0.06911045332904797</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04778110618598886</v>
+        <v>0.04778110618598883</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7206149497742436</v>
+        <v>0.7206149497742433</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.04301492997829071</v>
+        <v>-0.04301492997829064</v>
       </c>
       <c r="C6" t="n">
         <v>0.03066350771200718</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.103114300733491</v>
+        <v>-0.1031143007334909</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01708444077690955</v>
+        <v>0.01708444077690961</v>
       </c>
       <c r="F6" t="n">
-        <v>0.160674917377848</v>
+        <v>0.1606749173778486</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0009581591331443899</v>
+        <v>0.000958159133144383</v>
       </c>
       <c r="C7" t="n">
         <v>0.02954143714616891</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05694199372490039</v>
+        <v>-0.0569419937249004</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05885831199118918</v>
+        <v>0.05885831199118917</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9741256203875787</v>
+        <v>0.9741256203875788</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.01499471859888913</v>
+        <v>-0.0149947185988891</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03011722069603003</v>
+        <v>0.03011722069603004</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.07402338647755233</v>
+        <v>-0.07402338647755231</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04403394927977407</v>
+        <v>0.04403394927977411</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6185696367956137</v>
+        <v>0.6185696367956146</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009760945713619056</v>
+        <v>0.009760945713619061</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02969887927955247</v>
+        <v>0.02969887927955248</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.04844778805550665</v>
+        <v>-0.04844778805550666</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06796967948274475</v>
+        <v>0.06796967948274478</v>
       </c>
       <c r="F9" t="n">
-        <v>0.742409839494897</v>
+        <v>0.7424098394948969</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.008945036718057981</v>
+        <v>0.008945036718057868</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05227344659369305</v>
+        <v>0.05227344659369303</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.09350903595335837</v>
+        <v>-0.09350903595335844</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1113991093894743</v>
+        <v>0.1113991093894742</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8641293418452032</v>
+        <v>0.8641293418452048</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.07294946240716796</v>
+        <v>-0.07294946240716804</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04956147246244858</v>
+        <v>0.04956147246244856</v>
       </c>
       <c r="D11" t="n">
         <v>-0.1700881634543409</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02418923864000493</v>
+        <v>0.0241892386400048</v>
       </c>
       <c r="F11" t="n">
-        <v>0.141048259132978</v>
+        <v>0.1410482591329774</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.08662342274371281</v>
+        <v>-0.0866234227437129</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05089844563154302</v>
+        <v>0.05089844563154299</v>
       </c>
       <c r="D12" t="n">
         <v>-0.1863825430506072</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01313569756318156</v>
+        <v>0.01313569756318141</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0887764802596312</v>
+        <v>0.08877648025963067</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.00802474983648396</v>
+        <v>-0.008024749836484031</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05113295056969708</v>
+        <v>0.05113295056969707</v>
       </c>
       <c r="D13" t="n">
         <v>-0.1082434913763571</v>
       </c>
       <c r="E13" t="n">
-        <v>0.09219399170338914</v>
+        <v>0.09219399170338906</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8752929892942487</v>
+        <v>0.8752929892942476</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04340557759080323</v>
+        <v>-0.04340557759080313</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05045929460802622</v>
+        <v>0.0504592946080262</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1423039777078308</v>
+        <v>-0.1423039777078306</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0554928225262243</v>
+        <v>0.05549282252622437</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3896734268082844</v>
+        <v>0.3896734268082854</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.04574671530427653</v>
+        <v>-0.0457467153042766</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04961392181428274</v>
+        <v>0.04961392181428279</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1429882151920568</v>
+        <v>-0.142988215192057</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05149478458350377</v>
+        <v>0.05149478458350382</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3565004068554808</v>
+        <v>0.3565004068554806</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.03713592023139934</v>
+        <v>-0.03713592023139941</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05010472347761165</v>
+        <v>0.05010472347761164</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1353393737028566</v>
+        <v>-0.1353393737028567</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06106753324005797</v>
+        <v>0.06106753324005789</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4585927625445331</v>
+        <v>0.4585927625445322</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.01948239245873583</v>
+        <v>-0.01948239245873594</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05062347938805207</v>
+        <v>0.05062347938805204</v>
       </c>
       <c r="D17" t="n">
         <v>-0.1187025888314237</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07973780391395201</v>
+        <v>0.07973780391395184</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7003493364163547</v>
+        <v>0.7003493364163529</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.02897547644273349</v>
+        <v>-0.02897547644273368</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05100630816200025</v>
+        <v>0.05100630816200024</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1289460034246054</v>
+        <v>-0.1289460034246055</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07099505053913839</v>
+        <v>0.07099505053913818</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5699831381275147</v>
+        <v>0.569983138127512</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.0400886428750965</v>
+        <v>-0.04008864287509659</v>
       </c>
       <c r="C19" t="n">
-        <v>0.04996256722766793</v>
+        <v>0.04996256722766795</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1380134752164869</v>
+        <v>-0.138013475216487</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05783618946629386</v>
+        <v>0.0578361894662938</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4223369033872229</v>
+        <v>0.422336903387222</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.08980962914662666</v>
+        <v>-0.08980962914662678</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04956030606584796</v>
+        <v>0.04956030606584794</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1869460440984706</v>
+        <v>-0.1869460440984707</v>
       </c>
       <c r="E20" t="n">
-        <v>0.007326785805217312</v>
+        <v>0.007326785805217145</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0699663870864066</v>
+        <v>0.06996638708640614</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.003397924751943129</v>
+        <v>0.003397924751943027</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04891083189773243</v>
+        <v>0.04891083189773242</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0924655442215053</v>
+        <v>-0.09246554422150538</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09926139372539156</v>
+        <v>0.09926139372539144</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9446140588838075</v>
+        <v>0.9446140588838091</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.005820590202436421</v>
+        <v>-0.005820590202436488</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0499222260541841</v>
+        <v>0.04992222605418412</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1036663552967044</v>
+        <v>-0.1036663552967045</v>
       </c>
       <c r="E22" t="n">
-        <v>0.09202517489183155</v>
+        <v>0.09202517489183151</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9071824564981817</v>
+        <v>0.9071824564981807</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06091882540351694</v>
+        <v>-0.06091882540351704</v>
       </c>
       <c r="C23" t="n">
-        <v>0.04983273321557465</v>
+        <v>0.04983273321557466</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1585891877572361</v>
+        <v>-0.1585891877572362</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03675153695020223</v>
+        <v>0.03675153695020217</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2215314283124583</v>
+        <v>0.2215314283124578</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.04546552218884721</v>
+        <v>-0.04546552218884725</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04088368473780889</v>
+        <v>0.04088368473780891</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1255960718302425</v>
+        <v>-0.1255960718302426</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03466502745254811</v>
+        <v>0.0346650274525481</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2661080237958385</v>
+        <v>0.2661080237958384</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0058550037498215</v>
+        <v>0.00585500374982147</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02357096913273558</v>
+        <v>0.02357096913273563</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.04034324683104555</v>
+        <v>-0.04034324683104566</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05205325433068855</v>
+        <v>0.05205325433068861</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8038257535625438</v>
+        <v>0.8038257535625452</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0202203547931663</v>
+        <v>0.02022035479316629</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0284720963506442</v>
+        <v>0.02847209635064419</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03558392861845063</v>
+        <v>-0.03558392861845062</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07602463820478322</v>
+        <v>0.0760246382047832</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4775916198870058</v>
+        <v>0.477591619887006</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.01017504924390035</v>
+        <v>0.01017504924390033</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02920817082181942</v>
+        <v>0.0292081708218194</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.04707191362115939</v>
+        <v>-0.04707191362115936</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06742201210896009</v>
+        <v>0.06742201210896001</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7275675029194182</v>
+        <v>0.7275675029194186</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.03075274291213688</v>
+        <v>0.0307527429121369</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02852520938942745</v>
+        <v>0.02852520938942747</v>
       </c>
       <c r="D28" t="n">
         <v>-0.02515564014260472</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08666112596687847</v>
+        <v>0.08666112596687853</v>
       </c>
       <c r="F28" t="n">
-        <v>0.280993595099703</v>
+        <v>0.2809935950997029</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.01431775187402591</v>
+        <v>-0.01431775187402592</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02757795020140894</v>
+        <v>0.02757795020140895</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.06836954103622656</v>
+        <v>-0.06836954103622658</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03973403728817473</v>
+        <v>0.03973403728817475</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6036394802206331</v>
+        <v>0.6036394802206329</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3642249454799706</v>
+        <v>0.3642249454799705</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03859338896492542</v>
+        <v>0.03859338896492541</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2885832930673712</v>
+        <v>0.2885832930673711</v>
       </c>
       <c r="E30" t="n">
-        <v>0.43986659789257</v>
+        <v>0.4398665978925698</v>
       </c>
       <c r="F30" t="n">
-        <v>3.817947647451479e-21</v>
+        <v>3.817947647451369e-21</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5808547372361993</v>
+        <v>-0.001854532319157671</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01060596000933938</v>
+        <v>0.001243594980252397</v>
       </c>
       <c r="D31" t="n">
-        <v>0.560067437596422</v>
+        <v>-0.004291933691807168</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6016420368759766</v>
+        <v>0.0005828690534918262</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.1358913747251266</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0002855410455972268</v>
+        <v>0.00321743951496409</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001532410754135844</v>
+        <v>0.00398389043383224</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.002717928842030891</v>
+        <v>-0.004590842253700753</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003289010933225345</v>
+        <v>0.01102572128362893</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8521824265147955</v>
+        <v>0.4193137172191295</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.002242891807688963</v>
+        <v>0.0002855410455972181</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001173661517189242</v>
+        <v>0.001532410754135847</v>
       </c>
       <c r="D33" t="n">
-        <v>-5.744249604258938e-05</v>
+        <v>-0.002717928842030906</v>
       </c>
       <c r="E33" t="n">
-        <v>0.004543226111420515</v>
+        <v>0.003289010933225342</v>
       </c>
       <c r="F33" t="n">
-        <v>0.05600188208985742</v>
+        <v>0.8521824265148001</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.003217439514964093</v>
+        <v>0.5808547372361993</v>
       </c>
       <c r="C34" t="n">
-        <v>0.003983890433832253</v>
+        <v>0.01060596000933933</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.004590842253700773</v>
+        <v>0.5600674375964221</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01102572128362896</v>
+        <v>0.6016420368759765</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4193137172191305</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.001854532319157672</v>
+        <v>0.002242891807688962</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001243594980252398</v>
+        <v>0.001173661517189244</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.004291933691807172</v>
+        <v>-5.744249604259285e-05</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0005828690534918283</v>
+        <v>0.004543226111420517</v>
       </c>
       <c r="F35" t="n">
-        <v>0.135891374725127</v>
+        <v>0.05600188208985778</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2353,10 +2353,10 @@
         <v>-2.427664644175297</v>
       </c>
       <c r="C2" t="n">
-        <v>0.518165722003795</v>
+        <v>0.5181657220037946</v>
       </c>
       <c r="D2" t="n">
-        <v>2.798063509200602e-06</v>
+        <v>2.798063509200555e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04283704187763186</v>
+        <v>0.04283704187763187</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1065056610557124</v>
+        <v>0.1065056610557123</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6875336293530986</v>
+        <v>0.687533629353098</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3420089197228886</v>
+        <v>0.3420089197228887</v>
       </c>
       <c r="C4" t="n">
         <v>0.2258273108558932</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1299064164023925</v>
+        <v>0.1299064164023923</v>
       </c>
     </row>
     <row r="5">
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7568550919253108</v>
+        <v>0.7568550919253106</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1749116140278903</v>
+        <v>0.1749116140278904</v>
       </c>
       <c r="D5" t="n">
-        <v>1.511047971683322e-05</v>
+        <v>1.511047971683338e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2417,10 +2417,10 @@
         <v>-0.1819727920118001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2139666880119049</v>
+        <v>0.2139666880119048</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3950624226561794</v>
+        <v>0.3950624226561792</v>
       </c>
     </row>
     <row r="7">
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09728047689820798</v>
+        <v>-0.09728047689820801</v>
       </c>
       <c r="C8" t="n">
-        <v>0.210785304924523</v>
+        <v>0.2107853049245229</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6444295130162208</v>
+        <v>0.6444295130162203</v>
       </c>
     </row>
     <row r="9">
@@ -2465,10 +2465,10 @@
         <v>1.068702246714659</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1704165076539109</v>
+        <v>0.1704165076539108</v>
       </c>
       <c r="D9" t="n">
-        <v>3.584618716992764e-10</v>
+        <v>3.584618716992673e-10</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09164285114131063</v>
+        <v>0.09164285114131118</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2821462910028389</v>
+        <v>0.2821462910028381</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7453277880093387</v>
+        <v>0.7453277880093366</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2093667135385763</v>
+        <v>0.2093667135385769</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2718908402685901</v>
+        <v>0.2718908402685892</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4412764034926281</v>
+        <v>0.4412764034926253</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.2458167359844366</v>
+        <v>-0.2458167359844359</v>
       </c>
       <c r="C12" t="n">
         <v>0.3060864204610709</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4219193324752601</v>
+        <v>0.4219193324752615</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2480605146834357</v>
+        <v>0.2480605146834365</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2698784026653989</v>
+        <v>0.2698784026653986</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3580136685717253</v>
+        <v>0.358013668571723</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2887265920666394</v>
+        <v>0.2887265920666402</v>
       </c>
       <c r="C14" t="n">
         <v>0.2797122646585147</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3019657220075026</v>
+        <v>0.3019657220075013</v>
       </c>
     </row>
     <row r="15">
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.336456969341774</v>
+        <v>0.3364569693417747</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2683702941076241</v>
+        <v>0.2683702941076246</v>
       </c>
       <c r="D15" t="n">
         <v>0.209949534738275</v>
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1212332819747694</v>
+        <v>0.12123328197477</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2679493505870756</v>
+        <v>0.267949350587075</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6509459134758506</v>
+        <v>0.6509459134758482</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1766572982617266</v>
+        <v>0.1766572982617274</v>
       </c>
       <c r="C17" t="n">
         <v>0.2752350890811207</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5209761107851434</v>
+        <v>0.5209761107851416</v>
       </c>
     </row>
     <row r="18">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3813830960578521</v>
+        <v>0.3813830960578531</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2677517444468906</v>
+        <v>0.2677517444468913</v>
       </c>
       <c r="D18" t="n">
         <v>0.1543334033865622</v>
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1210111614869998</v>
+        <v>0.1210111614870004</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2775843004204014</v>
+        <v>0.2775843004204017</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6628774877860041</v>
+        <v>0.6628774877860026</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2255181952666774</v>
+        <v>0.2255181952666781</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2783783956071254</v>
+        <v>0.2783783956071247</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4178747418803501</v>
+        <v>0.4178747418803473</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2301319673853003</v>
+        <v>0.2301319673853011</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2673309630216587</v>
+        <v>0.2673309630216589</v>
       </c>
       <c r="D21" t="n">
-        <v>0.389320440492121</v>
+        <v>0.3893204404921197</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.04646654583854215</v>
+        <v>0.04646654583854266</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2845286078456557</v>
+        <v>0.2845286078456553</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8702738657351098</v>
+        <v>0.8702738657351081</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.02162756752909093</v>
+        <v>-0.02162756752909017</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2925905475884682</v>
+        <v>0.2925905475884684</v>
       </c>
       <c r="D23" t="n">
-        <v>0.941076015378437</v>
+        <v>0.9410760153784391</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8764973807420283</v>
+        <v>0.8764973807420282</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1598667289796823</v>
+        <v>0.1598667289796821</v>
       </c>
       <c r="D24" t="n">
-        <v>4.189413124540437e-08</v>
+        <v>4.189413124540285e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2721,10 +2721,10 @@
         <v>-0.5923085897232843</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1169262828732782</v>
+        <v>0.116926282873278</v>
       </c>
       <c r="D25" t="n">
-        <v>4.069915021574112e-07</v>
+        <v>4.069915021573901e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1386000328216487</v>
+        <v>-0.1386000328216486</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1507698258117117</v>
+        <v>0.1507698258117116</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3579479313928081</v>
+        <v>0.357947931392808</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08444119781568352</v>
+        <v>-0.08444119781568343</v>
       </c>
       <c r="C27" t="n">
         <v>0.157443858905906</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5917334279738683</v>
+        <v>0.5917334279738686</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1114085316198852</v>
+        <v>-0.1114085316198851</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1483441008175727</v>
+        <v>0.1483441008175725</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4526440879579775</v>
+        <v>0.4526440879579774</v>
       </c>
     </row>
     <row r="29">
@@ -2782,93 +2782,93 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3220151818496279</v>
+        <v>-0.3220151818496276</v>
       </c>
       <c r="C29" t="n">
         <v>0.1549982402231347</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03775166539448364</v>
+        <v>0.03775166539448375</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.03120747680900953</v>
+        <v>0.002580638036074957</v>
       </c>
       <c r="C30" t="n">
-        <v>0.05994942728922986</v>
+        <v>0.007292353686099048</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6026709615967232</v>
+        <v>0.7234267695349467</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.01293860122823144</v>
+        <v>0.01847772081409666</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008183645815534315</v>
+        <v>0.0228622308980033</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1138708520154851</v>
+        <v>0.418963730891023</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.01489842147412547</v>
+        <v>-0.01293860122823144</v>
       </c>
       <c r="C32" t="n">
-        <v>0.00709450119957797</v>
+        <v>0.00818364581553413</v>
       </c>
       <c r="D32" t="n">
-        <v>0.03572922606502685</v>
+        <v>0.1138708520154768</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.01847772081409662</v>
+        <v>-0.03120747680900959</v>
       </c>
       <c r="C33" t="n">
-        <v>0.02286223089800336</v>
+        <v>0.0599494272892295</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4189637308910251</v>
+        <v>0.6026709615967203</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.002580638036074957</v>
+        <v>0.01489842147412546</v>
       </c>
       <c r="C34" t="n">
-        <v>0.007292353686099036</v>
+        <v>0.007094501199577954</v>
       </c>
       <c r="D34" t="n">
-        <v>0.7234267695349461</v>
+        <v>0.03572922606502647</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.059</v>
+        <v>-0.015</v>
       </c>
       <c r="D6" t="n">
-        <v>0.021</v>
+        <v>-0.03</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03799999999999999</v>
+        <v>-0.015</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.095</v>
+        <v>-0.001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005</v>
+        <v>-0.007</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09</v>
+        <v>-0.006</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.033</v>
+        <v>0.013</v>
       </c>
       <c r="D8" t="n">
-        <v>0.025</v>
+        <v>0.007</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008</v>
+        <v>0.005999999999999999</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.012</v>
+        <v>0.351</v>
       </c>
       <c r="D9" t="n">
-        <v>0.006</v>
+        <v>0.016</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006</v>
+        <v>0.335</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.054</v>
+        <v>0.185</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.023</v>
+        <v>0.013</v>
       </c>
       <c r="E10" t="n">
-        <v>0.031</v>
+        <v>0.172</v>
       </c>
       <c r="F10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.368</v>
+        <v>-0.007</v>
       </c>
       <c r="D11" t="n">
-        <v>0.004</v>
+        <v>-0.028</v>
       </c>
       <c r="E11" t="n">
-        <v>0.364</v>
+        <v>-0.021</v>
       </c>
       <c r="F11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.007</v>
+        <v>-0.181</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.006</v>
+        <v>0.014</v>
       </c>
       <c r="E12" t="n">
-        <v>0.001</v>
+        <v>0.167</v>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.185</v>
+        <v>-0.054</v>
       </c>
       <c r="D13" t="n">
-        <v>0.013</v>
+        <v>-0.023</v>
       </c>
       <c r="E13" t="n">
-        <v>0.172</v>
+        <v>0.031</v>
       </c>
       <c r="F13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.007</v>
+        <v>-0.392</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.028</v>
+        <v>-0.027</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.021</v>
+        <v>0.365</v>
       </c>
       <c r="F14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.09</v>
+        <v>0.007</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.029</v>
+        <v>-0.006</v>
       </c>
       <c r="E15" t="n">
-        <v>0.061</v>
+        <v>0.001</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.014</v>
+        <v>0.036</v>
       </c>
       <c r="D16" t="n">
-        <v>0.017</v>
+        <v>-0.001</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.003000000000000001</v>
+        <v>0.035</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.096</v>
+        <v>0.368</v>
       </c>
       <c r="D17" t="n">
-        <v>0.017</v>
+        <v>0.004</v>
       </c>
       <c r="E17" t="n">
-        <v>0.079</v>
+        <v>0.364</v>
       </c>
       <c r="F17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.351</v>
+        <v>0.059</v>
       </c>
       <c r="D18" t="n">
-        <v>0.016</v>
+        <v>0.021</v>
       </c>
       <c r="E18" t="n">
-        <v>0.335</v>
+        <v>0.03799999999999999</v>
       </c>
       <c r="F18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.036</v>
+        <v>-0.215</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.001</v>
+        <v>-0.058</v>
       </c>
       <c r="E19" t="n">
-        <v>0.035</v>
+        <v>0.157</v>
       </c>
       <c r="F19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.008</v>
+        <v>0.044</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.007</v>
+        <v>0.027</v>
       </c>
       <c r="E20" t="n">
-        <v>0.001</v>
+        <v>0.017</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.076</v>
+        <v>-0.008</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-0.007</v>
       </c>
       <c r="E21" t="n">
-        <v>0.076</v>
+        <v>0.001</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="D22" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.076</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.001</v>
+        <v>-0.095</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.007</v>
+        <v>0.005</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.006</v>
+        <v>0.09</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.044</v>
+        <v>-0.019</v>
       </c>
       <c r="D24" t="n">
-        <v>0.027</v>
+        <v>0.007</v>
       </c>
       <c r="E24" t="n">
-        <v>0.017</v>
+        <v>0.012</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.013</v>
+        <v>-0.096</v>
       </c>
       <c r="D25" t="n">
-        <v>0.007</v>
+        <v>0.017</v>
       </c>
       <c r="E25" t="n">
-        <v>0.005999999999999999</v>
+        <v>0.079</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03</v>
+        <v>0.004</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.015</v>
+        <v>0.006</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.181</v>
+        <v>-0.001</v>
       </c>
       <c r="D27" t="n">
-        <v>0.014</v>
+        <v>-0.001</v>
       </c>
       <c r="E27" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.019</v>
+        <v>0.075</v>
       </c>
       <c r="D28" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="E28" t="n">
-        <v>0.012</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.215</v>
+        <v>0.014</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.058</v>
+        <v>0.017</v>
       </c>
       <c r="E29" t="n">
-        <v>0.157</v>
+        <v>-0.003000000000000001</v>
       </c>
       <c r="F29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.001</v>
+        <v>0.033</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.001</v>
+        <v>0.025</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01</v>
+        <v>-0.012</v>
       </c>
       <c r="D31" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="E31" t="n">
         <v>0.006</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,16 +1290,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.392</v>
+        <v>-0.09</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.027</v>
+        <v>-0.029</v>
       </c>
       <c r="E32" t="n">
-        <v>0.365</v>
+        <v>0.061</v>
       </c>
       <c r="F32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
@@ -1397,13 +1397,13 @@
         <v>0.1629543857601319</v>
       </c>
       <c r="E2" t="n">
-        <v>1.864929480836645</v>
+        <v>1.864929480836644</v>
       </c>
       <c r="F2" t="n">
         <v>1.150690388380934</v>
       </c>
       <c r="G2" t="n">
-        <v>1.864005612713847</v>
+        <v>1.864005612713846</v>
       </c>
     </row>
   </sheetData>
@@ -1467,16 +1467,16 @@
         <v>1.493998113457369</v>
       </c>
       <c r="C2" t="n">
-        <v>0.091541763420904</v>
+        <v>0.09154176342090867</v>
       </c>
       <c r="D2" t="n">
-        <v>1.314579554071111</v>
+        <v>1.314579554071102</v>
       </c>
       <c r="E2" t="n">
-        <v>1.673416672843627</v>
+        <v>1.673416672843636</v>
       </c>
       <c r="F2" t="n">
-        <v>7.067206153070735e-60</v>
+        <v>7.067206153166901e-60</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1492,16 +1492,16 @@
         <v>0.01139734884641808</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01836912354870614</v>
+        <v>0.01836912354870615</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02460547173661254</v>
+        <v>-0.02460547173661257</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0474001694294487</v>
+        <v>0.04740016942944872</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5349534598931425</v>
+        <v>0.5349534598931427</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.09369904833157608</v>
+        <v>-0.09369904833157609</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04522288491293567</v>
+        <v>0.04522288491293568</v>
       </c>
       <c r="D4" t="n">
         <v>-0.1823342740379298</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01066467357152959</v>
+        <v>-0.01066467357152958</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02981982333274041</v>
+        <v>0.02981982333274044</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06911045332904796</v>
+        <v>-0.06911045332904801</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04778110618598878</v>
+        <v>0.04778110618598885</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7206149497742427</v>
+        <v>0.7206149497742431</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.04301492997829066</v>
+        <v>-0.04301492997829062</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03066350771200715</v>
+        <v>0.03066350771200717</v>
       </c>
       <c r="D6" t="n">
         <v>-0.1031143007334909</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01708444077690956</v>
+        <v>0.01708444077690963</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1606749173778481</v>
+        <v>0.1606749173778487</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.000958159133144392</v>
+        <v>0.0009581591331443436</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0295414371461689</v>
+        <v>0.02954143714616892</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05694199372490037</v>
+        <v>-0.05694199372490046</v>
       </c>
       <c r="E7" t="n">
         <v>0.05885831199118915</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9741256203875786</v>
+        <v>0.9741256203875799</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1617,16 +1617,16 @@
         <v>-0.01499471859888912</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03011722069603003</v>
+        <v>0.03011722069603005</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.07402338647755233</v>
+        <v>-0.07402338647755236</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04403394927977407</v>
+        <v>0.04403394927977411</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6185696367956139</v>
+        <v>0.6185696367956141</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009760945713619051</v>
+        <v>0.009760945713619037</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02969887927955246</v>
+        <v>0.02969887927955249</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.04844778805550663</v>
+        <v>-0.0484477880555067</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06796967948274474</v>
+        <v>0.06796967948274478</v>
       </c>
       <c r="F9" t="n">
-        <v>0.742409839494897</v>
+        <v>0.7424098394948977</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.008945036718057971</v>
+        <v>0.008945036718057974</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05227344659369308</v>
+        <v>0.05227344659369309</v>
       </c>
       <c r="D10" t="n">
         <v>-0.09350903595335844</v>
@@ -1689,13 +1689,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.07294946240716803</v>
+        <v>-0.07294946240716806</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04956147246244859</v>
+        <v>0.0495614724624486</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1700881634543409</v>
+        <v>-0.170088163454341</v>
       </c>
       <c r="E11" t="n">
         <v>0.02418923864000487</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.08662342274371293</v>
+        <v>-0.08662342274371289</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05089844563154299</v>
+        <v>0.05089844563154306</v>
       </c>
       <c r="D12" t="n">
         <v>-0.1863825430506073</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01313569756318138</v>
+        <v>0.01313569756318156</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08877648025963054</v>
+        <v>0.08877648025963114</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.008024749836484038</v>
+        <v>-0.008024749836484041</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05113295056969714</v>
+        <v>0.0511329505696972</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1082434913763573</v>
+        <v>-0.1082434913763574</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0921939917033892</v>
+        <v>0.09219399170338931</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8752929892942477</v>
+        <v>0.8752929892942478</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04340557759080326</v>
+        <v>-0.04340557759080336</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0504592946080263</v>
+        <v>0.05045929460802629</v>
       </c>
       <c r="D14" t="n">
         <v>-0.142303977707831</v>
       </c>
       <c r="E14" t="n">
-        <v>0.05549282252622444</v>
+        <v>0.05549282252622432</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3896734268082849</v>
+        <v>0.3896734268082839</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1792,16 +1792,16 @@
         <v>-0.04574671530427658</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04961392181428277</v>
+        <v>0.04961392181428281</v>
       </c>
       <c r="D15" t="n">
         <v>-0.142988215192057</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05149478458350379</v>
+        <v>0.05149478458350387</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3565004068554806</v>
+        <v>0.3565004068554809</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.0371359202313994</v>
+        <v>-0.03713592023139944</v>
       </c>
       <c r="C16" t="n">
         <v>0.05010472347761168</v>
@@ -1823,10 +1823,10 @@
         <v>-0.1353393737028568</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06106753324005798</v>
+        <v>0.06106753324005793</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4585927625445326</v>
+        <v>0.4585927625445322</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.0194823924587359</v>
+        <v>-0.01948239245873591</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0506234793880521</v>
+        <v>0.05062347938805218</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1187025888314238</v>
+        <v>-0.118702588831424</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07973780391395199</v>
+        <v>0.07973780391395213</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7003493364163539</v>
+        <v>0.700349336416354</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.02897547644273366</v>
+        <v>-0.02897547644273362</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05100630816200025</v>
+        <v>0.0510063081620003</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1289460034246055</v>
+        <v>-0.1289460034246056</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07099505053913824</v>
+        <v>0.07099505053913838</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5699831381275126</v>
+        <v>0.5699831381275133</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,16 +1889,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.04008864287509657</v>
+        <v>-0.04008864287509658</v>
       </c>
       <c r="C19" t="n">
-        <v>0.04996256722766797</v>
+        <v>0.04996256722766799</v>
       </c>
       <c r="D19" t="n">
         <v>-0.138013475216487</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05783618946629387</v>
+        <v>0.0578361894662939</v>
       </c>
       <c r="F19" t="n">
         <v>0.4223369033872225</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.08980962914662673</v>
+        <v>-0.08980962914662674</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04956030606584794</v>
+        <v>0.04956030606584797</v>
       </c>
       <c r="D20" t="n">
         <v>-0.1869460440984707</v>
       </c>
       <c r="E20" t="n">
-        <v>0.007326785805217215</v>
+        <v>0.007326785805217256</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06996638708640632</v>
+        <v>0.0699663870864064</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.003397924751943067</v>
+        <v>0.003397924751943052</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04891083189773249</v>
+        <v>0.04891083189773255</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.09246554422150546</v>
+        <v>-0.09246554422150562</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09926139372539161</v>
+        <v>0.09926139372539171</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9446140588838084</v>
+        <v>0.9446140588838088</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.005820590202436582</v>
+        <v>-0.005820590202436491</v>
       </c>
       <c r="C22" t="n">
-        <v>0.04992222605418418</v>
+        <v>0.04992222605418416</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1036663552967047</v>
+        <v>-0.1036663552967046</v>
       </c>
       <c r="E22" t="n">
-        <v>0.09202517489183154</v>
+        <v>0.0920251748918316</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9071824564981794</v>
+        <v>0.9071824564981807</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06091882540351704</v>
+        <v>-0.06091882540351701</v>
       </c>
       <c r="C23" t="n">
         <v>0.04983273321557469</v>
@@ -1998,10 +1998,10 @@
         <v>-0.1585891877572363</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03675153695020222</v>
+        <v>0.03675153695020227</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2215314283124579</v>
+        <v>0.2215314283124583</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.04546552218884724</v>
+        <v>-0.04546552218884725</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04088368473780889</v>
+        <v>0.04088368473780891</v>
       </c>
       <c r="D24" t="n">
         <v>-0.1255960718302426</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03466502745254808</v>
+        <v>0.0346650274525481</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2661080237958383</v>
+        <v>0.2661080237958384</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.005855003749821498</v>
+        <v>0.005855003749821487</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02357096913273561</v>
+        <v>0.02357096913273565</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.04034324683104561</v>
+        <v>-0.0403432468310457</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05205325433068861</v>
+        <v>0.05205325433068868</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8038257535625442</v>
+        <v>0.8038257535625448</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0202203547931664</v>
+        <v>0.02022035479316629</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02847209635064421</v>
+        <v>0.02847209635064418</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03558392861845055</v>
+        <v>-0.03558392861845061</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07602463820478336</v>
+        <v>0.07602463820478318</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4775916198870037</v>
+        <v>0.4775916198870058</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.01017504924390039</v>
+        <v>0.01017504924390033</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02920817082181943</v>
+        <v>0.02920817082181941</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.04707191362115938</v>
+        <v>-0.04707191362115939</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06742201210896015</v>
+        <v>0.06742201210896005</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7275675029194174</v>
+        <v>0.7275675029194186</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.03075274291213697</v>
+        <v>0.0307527429121369</v>
       </c>
       <c r="C28" t="n">
         <v>0.02852520938942747</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.02515564014260466</v>
+        <v>-0.02515564014260473</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08666112596687861</v>
+        <v>0.08666112596687854</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2809935950997019</v>
+        <v>0.2809935950997029</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.01431775187402586</v>
+        <v>-0.0143177518740259</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02757795020140896</v>
+        <v>0.02757795020140895</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.06836954103622656</v>
+        <v>-0.06836954103622657</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03973403728817484</v>
+        <v>0.03973403728817476</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6036394802206344</v>
+        <v>0.6036394802206333</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,16 +2164,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3642249454799706</v>
+        <v>0.3642249454799705</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03859338896492542</v>
+        <v>0.03859338896492541</v>
       </c>
       <c r="D30" t="n">
         <v>0.2885832930673712</v>
       </c>
       <c r="E30" t="n">
-        <v>0.43986659789257</v>
+        <v>0.4398665978925699</v>
       </c>
       <c r="F30" t="n">
         <v>3.817947647451369e-21</v>
@@ -2192,13 +2192,13 @@
         <v>0.5808547372361993</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01060596000933934</v>
+        <v>0.01060596000933939</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5600674375964221</v>
+        <v>0.560067437596422</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6016420368759765</v>
+        <v>0.6016420368759766</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.002242891807688964</v>
+        <v>-0.001854532319157671</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001173661517189244</v>
+        <v>0.001243594980252397</v>
       </c>
       <c r="D32" t="n">
-        <v>-5.744249604259155e-05</v>
+        <v>-0.004291933691807169</v>
       </c>
       <c r="E32" t="n">
-        <v>0.00454322611142052</v>
+        <v>0.0005828690534918264</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0560018820898576</v>
+        <v>0.1358913747251267</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.001854532319157671</v>
+        <v>0.0002855410455972195</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001243594980252399</v>
+        <v>0.001532410754135868</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.004291933691807172</v>
+        <v>-0.002717928842030945</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0005828690534918303</v>
+        <v>0.003289010933225384</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1358913747251274</v>
+        <v>0.8521824265148015</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2264,19 +2264,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.003217439514964088</v>
+        <v>0.003217439514964092</v>
       </c>
       <c r="C34" t="n">
-        <v>0.003983890433832258</v>
+        <v>0.003983890433832266</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.004590842253700789</v>
+        <v>-0.004590842253700801</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01102572128362896</v>
+        <v>0.01102572128362899</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4193137172191319</v>
+        <v>0.4193137172191322</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0002855410455972202</v>
+        <v>0.002242891807688964</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001532410754135811</v>
+        <v>0.001173661517189242</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.002717928842030832</v>
+        <v>-5.744249604258808e-05</v>
       </c>
       <c r="E35" t="n">
-        <v>0.003289010933225272</v>
+        <v>0.004543226111420516</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8521824265147957</v>
+        <v>0.05600188208985725</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.427664644175294</v>
+        <v>-2.427664644175297</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5181657220038094</v>
+        <v>0.5181657220038028</v>
       </c>
       <c r="D2" t="n">
-        <v>2.798063509202462e-06</v>
+        <v>2.798063509201582e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04283704187763178</v>
+        <v>0.04283704187763192</v>
       </c>
       <c r="C3" t="n">
         <v>0.1065056610557123</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6875336293530989</v>
+        <v>0.6875336293530978</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3420089197228885</v>
+        <v>0.3420089197228887</v>
       </c>
       <c r="C4" t="n">
-        <v>0.225827310855893</v>
+        <v>0.2258273108558931</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1299064164023921</v>
+        <v>0.1299064164023923</v>
       </c>
     </row>
     <row r="5">
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7568550919253108</v>
+        <v>0.7568550919253106</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1749116140278903</v>
+        <v>0.1749116140278902</v>
       </c>
       <c r="D5" t="n">
-        <v>1.511047971683312e-05</v>
+        <v>1.511047971683288e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1819727920118001</v>
+        <v>-0.1819727920118004</v>
       </c>
       <c r="C6" t="n">
         <v>0.2139666880119048</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3950624226561794</v>
+        <v>0.3950624226561785</v>
       </c>
     </row>
     <row r="7">
@@ -2433,10 +2433,10 @@
         <v>0.1330552971690138</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1953952819476558</v>
+        <v>0.1953952819476561</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4959002791352487</v>
+        <v>0.4959002791352496</v>
       </c>
     </row>
     <row r="8">
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09728047689820793</v>
+        <v>-0.09728047689820803</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2107853049245227</v>
+        <v>0.2107853049245229</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6444295130162204</v>
+        <v>0.6444295130162205</v>
       </c>
     </row>
     <row r="9">
@@ -2465,10 +2465,10 @@
         <v>1.068702246714659</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1704165076539108</v>
+        <v>0.1704165076539109</v>
       </c>
       <c r="D9" t="n">
-        <v>3.584618716992648e-10</v>
+        <v>3.584618716992699e-10</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09164285114131061</v>
+        <v>0.09164285114131082</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2821462910028378</v>
+        <v>0.2821462910028381</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7453277880093379</v>
+        <v>0.7453277880093375</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2093667135385762</v>
+        <v>0.2093667135385765</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2718908402685897</v>
+        <v>0.2718908402685894</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4412764034926278</v>
+        <v>0.4412764034926265</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.2458167359844365</v>
+        <v>-0.2458167359844362</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3060864204610706</v>
+        <v>0.3060864204610709</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4219193324752599</v>
+        <v>0.4219193324752608</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2480605146834356</v>
+        <v>0.2480605146834359</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2698784026653987</v>
+        <v>0.2698784026653986</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3580136685717249</v>
+        <v>0.3580136685717242</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2887265920666393</v>
+        <v>0.2887265920666398</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2797122646585141</v>
+        <v>0.2797122646585147</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3019657220075017</v>
+        <v>0.3019657220075019</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.336456969341774</v>
+        <v>0.3364569693417743</v>
       </c>
       <c r="C15" t="n">
         <v>0.268370294107624</v>
       </c>
       <c r="D15" t="n">
-        <v>0.209949534738275</v>
+        <v>0.2099495347382745</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1212332819747693</v>
+        <v>0.1212332819747696</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2679493505870751</v>
+        <v>0.2679493505870748</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6509459134758502</v>
+        <v>0.6509459134758488</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1766572982617266</v>
+        <v>0.1766572982617269</v>
       </c>
       <c r="C17" t="n">
-        <v>0.27523508908112</v>
+        <v>0.2752350890811202</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5209761107851423</v>
+        <v>0.5209761107851418</v>
       </c>
     </row>
     <row r="18">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3813830960578522</v>
+        <v>0.3813830960578525</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2677517444468914</v>
+        <v>0.2677517444468916</v>
       </c>
       <c r="D18" t="n">
         <v>0.1543334033865632</v>
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1210111614869997</v>
+        <v>0.1210111614870001</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2775843004204014</v>
+        <v>0.2775843004204012</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6628774877860042</v>
+        <v>0.662877487786003</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2255181952666772</v>
+        <v>0.2255181952666776</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2783783956071252</v>
+        <v>0.2783783956071247</v>
       </c>
       <c r="D20" t="n">
-        <v>0.41787474188035</v>
+        <v>0.4178747418803483</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2301319673853003</v>
+        <v>0.2301319673853007</v>
       </c>
       <c r="C21" t="n">
         <v>0.2673309630216584</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3893204404921206</v>
+        <v>0.3893204404921196</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.04646654583854196</v>
+        <v>0.04646654583854237</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2845286078456555</v>
+        <v>0.2845286078456554</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8702738657351102</v>
+        <v>0.870273865735109</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.0216275675290909</v>
+        <v>-0.02162756752909064</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2925905475884689</v>
+        <v>0.292590547588468</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9410760153784372</v>
+        <v>0.9410760153784377</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8764973807420284</v>
+        <v>0.8764973807420283</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1598667289796821</v>
+        <v>0.1598667289796822</v>
       </c>
       <c r="D24" t="n">
-        <v>4.189413124540276e-08</v>
+        <v>4.189413124540331e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5923085897232842</v>
+        <v>-0.5923085897232843</v>
       </c>
       <c r="C25" t="n">
-        <v>0.116926282873278</v>
+        <v>0.1169262828732779</v>
       </c>
       <c r="D25" t="n">
-        <v>4.06991502157394e-07</v>
+        <v>4.069915021573848e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1386000328216488</v>
+        <v>-0.138600032821649</v>
       </c>
       <c r="C26" t="n">
         <v>0.1507698258117116</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3579479313928077</v>
+        <v>0.357947931392807</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08444119781568343</v>
+        <v>-0.08444119781568341</v>
       </c>
       <c r="C27" t="n">
-        <v>0.157443858905906</v>
+        <v>0.1574438589059061</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5917334279738685</v>
+        <v>0.5917334279738689</v>
       </c>
     </row>
     <row r="28">
@@ -2769,7 +2769,7 @@
         <v>-0.1114085316198851</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1483441008175723</v>
+        <v>0.1483441008175724</v>
       </c>
       <c r="D28" t="n">
         <v>0.4526440879579769</v>
@@ -2785,10 +2785,10 @@
         <v>-0.3220151818496277</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1549982402231347</v>
+        <v>0.1549982402231345</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03775166539448364</v>
+        <v>0.0377516653944835</v>
       </c>
     </row>
     <row r="30">
@@ -2798,45 +2798,45 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0312074768090097</v>
+        <v>-0.03120747680900965</v>
       </c>
       <c r="C30" t="n">
-        <v>0.05994942728923066</v>
+        <v>0.0599494272892301</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6026709615967261</v>
+        <v>0.6026709615967234</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.01489842147412547</v>
+        <v>0.002580638036074952</v>
       </c>
       <c r="C31" t="n">
-        <v>0.007094501199577966</v>
+        <v>0.007292353686099041</v>
       </c>
       <c r="D31" t="n">
-        <v>0.03572922606502668</v>
+        <v>0.7234267695349469</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.002580638036074951</v>
+        <v>-0.01293860122823144</v>
       </c>
       <c r="C32" t="n">
-        <v>0.007292353686099037</v>
+        <v>0.008183645815534393</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7234267695349468</v>
+        <v>0.1138708520154885</v>
       </c>
     </row>
     <row r="33">
@@ -2846,29 +2846,29 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.01847772081409665</v>
+        <v>0.01847772081409668</v>
       </c>
       <c r="C33" t="n">
-        <v>0.02286223089800339</v>
+        <v>0.02286223089800329</v>
       </c>
       <c r="D33" t="n">
-        <v>0.418963730891025</v>
+        <v>0.4189637308910223</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.01293860122823149</v>
+        <v>0.01489842147412546</v>
       </c>
       <c r="C34" t="n">
-        <v>0.008183645815534041</v>
+        <v>0.007094501199577965</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1138708520154716</v>
+        <v>0.03572922606502674</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -483,10 +483,10 @@
         <v>-0.058</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.028</v>
+        <v>-0.029</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -537,10 +537,10 @@
         <v>0.063</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="E4" t="n">
-        <v>0.061</v>
+        <v>0.057</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -552,7 +552,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>big_span</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.036</v>
+        <v>-0.025</v>
       </c>
       <c r="D5" t="n">
-        <v>0.029</v>
+        <v>0.015</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006999999999999996</v>
+        <v>0.01</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.392</v>
+        <v>-0.181</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.027</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.365</v>
+        <v>0.172</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.181</v>
+        <v>0.01</v>
       </c>
       <c r="D7" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="E7" t="n">
-        <v>0.167</v>
+        <v>0.005</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.059</v>
+        <v>0.076</v>
       </c>
       <c r="D8" t="n">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03799999999999999</v>
+        <v>0.076</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.007</v>
+        <v>-0.095</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.028</v>
+        <v>0.002</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.021</v>
+        <v>0.093</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.215</v>
+        <v>-0.008</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.058</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>0.157</v>
+        <v>-0.0009999999999999992</v>
       </c>
       <c r="F10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.015</v>
+        <v>-0.392</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.03</v>
+        <v>-0.031</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.015</v>
+        <v>0.361</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.054</v>
+        <v>-0.001</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.023</v>
+        <v>0.003</v>
       </c>
       <c r="E12" t="n">
-        <v>0.031</v>
+        <v>-0.002</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.036</v>
+        <v>0.014</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.001</v>
+        <v>0.021</v>
       </c>
       <c r="E13" t="n">
-        <v>0.035</v>
+        <v>-0.007000000000000001</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.001</v>
+        <v>0.059</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.007</v>
+        <v>0.014</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.006</v>
+        <v>0.045</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -834,10 +834,10 @@
         <v>0.033</v>
       </c>
       <c r="D15" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="E15" t="n">
-        <v>0.008</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.001</v>
+        <v>0.007</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.013</v>
+        <v>0.036</v>
       </c>
       <c r="D17" t="n">
-        <v>0.007</v>
+        <v>-0.004</v>
       </c>
       <c r="E17" t="n">
-        <v>0.005999999999999999</v>
+        <v>0.032</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01</v>
+        <v>-0.015</v>
       </c>
       <c r="D18" t="n">
-        <v>0.004</v>
+        <v>-0.028</v>
       </c>
       <c r="E18" t="n">
-        <v>0.006</v>
+        <v>-0.013</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.014</v>
+        <v>-0.096</v>
       </c>
       <c r="D19" t="n">
-        <v>0.017</v>
+        <v>0.021</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.003000000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.095</v>
+        <v>-0.001</v>
       </c>
       <c r="D20" t="n">
-        <v>0.005</v>
+        <v>-0.004</v>
       </c>
       <c r="E20" t="n">
-        <v>0.09</v>
+        <v>-0.003</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.368</v>
+        <v>-0.007</v>
       </c>
       <c r="D21" t="n">
-        <v>0.004</v>
+        <v>-0.028</v>
       </c>
       <c r="E21" t="n">
-        <v>0.364</v>
+        <v>-0.021</v>
       </c>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.096</v>
+        <v>0.075</v>
       </c>
       <c r="D22" t="n">
-        <v>0.017</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>0.079</v>
+        <v>0.066</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.012</v>
+        <v>-0.019</v>
       </c>
       <c r="D23" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="E23" t="n">
-        <v>0.006</v>
+        <v>0.014</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.09</v>
+        <v>0.351</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.029</v>
+        <v>0.016</v>
       </c>
       <c r="E24" t="n">
-        <v>0.061</v>
+        <v>0.335</v>
       </c>
       <c r="F24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.008</v>
+        <v>-0.054</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.007</v>
+        <v>-0.02</v>
       </c>
       <c r="E25" t="n">
-        <v>0.001</v>
+        <v>0.034</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.019</v>
+        <v>-0.09</v>
       </c>
       <c r="D26" t="n">
-        <v>0.007</v>
+        <v>-0.029</v>
       </c>
       <c r="E26" t="n">
-        <v>0.012</v>
+        <v>0.061</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.007</v>
+        <v>-0.012</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.006</v>
+        <v>0.006</v>
       </c>
       <c r="E27" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.351</v>
+        <v>0.368</v>
       </c>
       <c r="D28" t="n">
-        <v>0.016</v>
+        <v>0.005</v>
       </c>
       <c r="E28" t="n">
-        <v>0.335</v>
+        <v>0.363</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.075</v>
+        <v>0.013</v>
       </c>
       <c r="D29" t="n">
         <v>0.004</v>
       </c>
       <c r="E29" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.044</v>
+        <v>-0.215</v>
       </c>
       <c r="D30" t="n">
-        <v>0.027</v>
+        <v>-0.063</v>
       </c>
       <c r="E30" t="n">
-        <v>0.017</v>
+        <v>0.152</v>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1266,10 +1266,10 @@
         <v>0.185</v>
       </c>
       <c r="D31" t="n">
-        <v>0.013</v>
+        <v>0.018</v>
       </c>
       <c r="E31" t="n">
-        <v>0.172</v>
+        <v>0.167</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.076</v>
+        <v>0.044</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="E32" t="n">
-        <v>0.076</v>
+        <v>0.018</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1320,10 +1320,10 @@
         <v>-0.021</v>
       </c>
       <c r="D33" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="E33" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
@@ -1388,22 +1388,22 @@
         <v>6217</v>
       </c>
       <c r="B2" t="n">
-        <v>6054.814949838281</v>
+        <v>6058.441997574593</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9955799696542841</v>
+        <v>0.9950246761341104</v>
       </c>
       <c r="D2" t="n">
-        <v>0.162954385760132</v>
+        <v>0.1609838789597045</v>
       </c>
       <c r="E2" t="n">
-        <v>1.864929480836646</v>
+        <v>1.82043870212157</v>
       </c>
       <c r="F2" t="n">
-        <v>1.150690388380934</v>
+        <v>1.151957513402452</v>
       </c>
       <c r="G2" t="n">
-        <v>1.864005612713848</v>
+        <v>1.820173420053883</v>
       </c>
     </row>
   </sheetData>
@@ -1417,7 +1417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.493998113457369</v>
+        <v>1.480396945623569</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09154176342090348</v>
+        <v>0.0923135560579946</v>
       </c>
       <c r="D2" t="n">
-        <v>1.314579554071112</v>
+        <v>1.29946570046508</v>
       </c>
       <c r="E2" t="n">
-        <v>1.673416672843626</v>
+        <v>1.661328190782057</v>
       </c>
       <c r="F2" t="n">
-        <v>7.067206153060451e-60</v>
+        <v>7.091592649192629e-58</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01139734884641803</v>
+        <v>0.01014980283236199</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01836912354870616</v>
+        <v>0.01836499278683017</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02460547173661264</v>
+        <v>-0.02584492160616302</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0474001694294487</v>
+        <v>0.04614452727088701</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5349534598931449</v>
+        <v>0.5804885690891299</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.09369904833157609</v>
+        <v>-0.09487871714183246</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04522288491293567</v>
+        <v>0.04520079875316899</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1823342740379298</v>
+        <v>-0.1834706547704867</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.005063822625222397</v>
+        <v>-0.00628677951317827</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03827115219154174</v>
+        <v>0.03581253134930478</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01066467357152956</v>
+        <v>-0.01205799529998014</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02981982333274043</v>
+        <v>0.02981223863521451</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06911045332904797</v>
+        <v>-0.07048890932351411</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04778110618598885</v>
+        <v>0.04637291872355383</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7206149497742436</v>
+        <v>0.6858711013557706</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.04301492997829071</v>
+        <v>-0.04304972157863009</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03066350771200716</v>
+        <v>0.03059882979701846</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.103114300733491</v>
+        <v>-0.1030223259498573</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01708444077690954</v>
+        <v>0.01692288279259715</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1606749173778477</v>
+        <v>0.1594548344009052</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0009581591331443962</v>
+        <v>0.001240700728441063</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0295414371461689</v>
+        <v>0.0294679635986441</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05694199372490036</v>
+        <v>-0.05651544662263869</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05885831199118916</v>
+        <v>0.05899684807952081</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9741256203875784</v>
+        <v>0.9664162895200011</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.01499471859888913</v>
+        <v>-0.01496662172759922</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03011722069603001</v>
+        <v>0.03016435277694362</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.07402338647755229</v>
+        <v>-0.07408766678736949</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04403394927977403</v>
+        <v>0.04415442333217104</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6185696367956136</v>
+        <v>0.6197750642373498</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009760945713619091</v>
+        <v>0.01054368268372455</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02969887927955247</v>
+        <v>0.02965183417955851</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.04844778805550662</v>
+        <v>-0.04757284438376392</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06796967948274481</v>
+        <v>0.06866020975121301</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7424098394948961</v>
+        <v>0.7221530148300351</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.008945036718057849</v>
+        <v>0.008469138305614014</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05227344659369305</v>
+        <v>0.05226807550480057</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.09350903595335849</v>
+        <v>-0.09397440722501532</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1113991093894742</v>
+        <v>0.1109126838362433</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8641293418452052</v>
+        <v>0.8712800895636489</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.072949462407168</v>
+        <v>-0.07442515093376462</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04956147246244858</v>
+        <v>0.04961328479180979</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1700881634543409</v>
+        <v>-0.1716654022804406</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02418923864000488</v>
+        <v>0.02281510041291136</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1410482591329778</v>
+        <v>0.1335871310677167</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.08662342274371286</v>
+        <v>-0.08771751346518671</v>
       </c>
       <c r="C12" t="n">
-        <v>0.050898445631543</v>
+        <v>0.05098868776485559</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1863825430506072</v>
+        <v>-0.1876535051032618</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01313569756318146</v>
+        <v>0.01221847817288835</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08877648025963082</v>
+        <v>0.08537195926819326</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.008024749836483986</v>
+        <v>-0.01112220983087749</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05113295056969706</v>
+        <v>0.05102736916981043</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1082434913763571</v>
+        <v>-0.1111340156295354</v>
       </c>
       <c r="E13" t="n">
-        <v>0.09219399170338909</v>
+        <v>0.08888959596778047</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8752929892942483</v>
+        <v>0.827455934193412</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04340557759080318</v>
+        <v>-0.04293550244653974</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05045929460802626</v>
+        <v>0.05055059599645621</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1423039777078308</v>
+        <v>-0.1420128499966286</v>
       </c>
       <c r="E14" t="n">
-        <v>0.05549282252622443</v>
+        <v>0.05614184510354906</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3896734268082854</v>
+        <v>0.3956826737847416</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.04574671530427654</v>
+        <v>-0.044376478746274</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04961392181428279</v>
+        <v>0.04933346508523263</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.142988215192057</v>
+        <v>-0.1410682935458942</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05149478458350386</v>
+        <v>0.05231533605334619</v>
       </c>
       <c r="F15" t="n">
-        <v>0.356500406855481</v>
+        <v>0.3683753135199095</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.03713592023139937</v>
+        <v>-0.03724912566851705</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05010472347761162</v>
+        <v>0.0501333524597545</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1353393737028566</v>
+        <v>-0.1355086909138884</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0610675332400579</v>
+        <v>0.06101043957685429</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4585927625445324</v>
+        <v>0.4574811395184715</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.01948239245873586</v>
+        <v>-0.02013564391904809</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0506234793880521</v>
+        <v>0.05067591738089412</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1187025888314237</v>
+        <v>-0.1194586168691279</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07973780391395204</v>
+        <v>0.07918732903103175</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7003493364163544</v>
+        <v>0.6911156643997002</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.02897547644273353</v>
+        <v>-0.02951065520775305</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05100630816200019</v>
+        <v>0.05110457249157436</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1289460034246053</v>
+        <v>-0.1296737767365552</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07099505053913825</v>
+        <v>0.07065246632104907</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5699831381275138</v>
+        <v>0.5636312794271754</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.04008864287509655</v>
+        <v>-0.04054326933592469</v>
       </c>
       <c r="C19" t="n">
-        <v>0.04996256722766799</v>
+        <v>0.05001967309932245</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.138013475216487</v>
+        <v>-0.1385800271290637</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05783618946629392</v>
+        <v>0.05749348845721428</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4223369033872229</v>
+        <v>0.4176261697368353</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.08980962914662668</v>
+        <v>-0.09100057242621593</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04956030606584801</v>
+        <v>0.04944530324025027</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1869460440984708</v>
+        <v>-0.1879115859817681</v>
       </c>
       <c r="E20" t="n">
-        <v>0.007326785805217395</v>
+        <v>0.005910441129336239</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06996638708640684</v>
+        <v>0.06570527191995243</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.003397924751943098</v>
+        <v>0.00369568530611819</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04891083189773248</v>
+        <v>0.04898316444458103</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.09246554422150542</v>
+        <v>-0.09230955285406356</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09926139372539163</v>
+        <v>0.09970092346629994</v>
       </c>
       <c r="F21" t="n">
-        <v>0.944614058883808</v>
+        <v>0.9398582124386513</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.00582059020243632</v>
+        <v>-0.006269093317233029</v>
       </c>
       <c r="C22" t="n">
-        <v>0.04992222605418412</v>
+        <v>0.05001575119043809</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1036663552967043</v>
+        <v>-0.104298164310208</v>
       </c>
       <c r="E22" t="n">
-        <v>0.09202517489183169</v>
+        <v>0.09175997767574195</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9071824564981834</v>
+        <v>0.9002525019265126</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06091882540351698</v>
+        <v>-0.06082558774950664</v>
       </c>
       <c r="C23" t="n">
-        <v>0.04983273321557472</v>
+        <v>0.04992592593427266</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1585891877572363</v>
+        <v>-0.1586786044754953</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03675153695020235</v>
+        <v>0.03702742897648204</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2215314283124588</v>
+        <v>0.2231036582797601</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.04546552218884722</v>
+        <v>-0.04566521685749294</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04088368473780891</v>
+        <v>0.0409915365619473</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1255960718302426</v>
+        <v>-0.1260071521898665</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03466502745254811</v>
+        <v>0.03467671847488061</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2661080237958385</v>
+        <v>0.2652724350207529</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0058550037498215</v>
+        <v>0.005875090878894528</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02357096913273562</v>
+        <v>0.02360333061262573</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.04034324683104562</v>
+        <v>-0.04038658703704364</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05205325433068862</v>
+        <v>0.05213676879483269</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8038257535625442</v>
+        <v>0.8034308633569947</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.02022035479316614</v>
+        <v>0.01971342777812012</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02847209635064417</v>
+        <v>0.02844465885270394</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03558392861845072</v>
+        <v>-0.03603707912570801</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07602463820478302</v>
+        <v>0.07546393468194826</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4775916198870087</v>
+        <v>0.48828132975465</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.01017504924390034</v>
+        <v>0.009295584463230852</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02920817082181939</v>
+        <v>0.02918964367861766</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.04707191362115933</v>
+        <v>-0.04791506586841703</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06742201210896001</v>
+        <v>0.06650623479487873</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7275675029194182</v>
+        <v>0.7501399152983234</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.03075274291213691</v>
+        <v>0.02910093430210231</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02852520938942743</v>
+        <v>0.02854626163111396</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.02515564014260465</v>
+        <v>-0.02684871038813868</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08666112596687847</v>
+        <v>0.08505057899234329</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2809935950997021</v>
+        <v>0.3079985571095429</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0143177518740259</v>
+        <v>-0.01455084235275102</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02757795020140893</v>
+        <v>0.02750445917332441</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.06836954103622653</v>
+        <v>-0.06845859174671917</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03973403728817473</v>
+        <v>0.03935690704121713</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6036394802206331</v>
+        <v>0.5967806460697769</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3642249454799705</v>
+        <v>0.2472871475932631</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03859338896492542</v>
+        <v>0.120490624298827</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2885832930673711</v>
+        <v>0.01112986349281544</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4398665978925699</v>
+        <v>0.4834444316937109</v>
       </c>
       <c r="F30" t="n">
-        <v>3.817947647451479e-21</v>
+        <v>0.04013709890141712</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.001854532319157672</v>
+        <v>0.002290121492346934</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001243594980252395</v>
+        <v>0.001172016575419001</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.004291933691807166</v>
+        <v>-6.988784758279066e-06</v>
       </c>
       <c r="E31" t="n">
-        <v>0.000582869053491822</v>
+        <v>0.004587231769452147</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1358913747251261</v>
+        <v>0.0507011057916955</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5808547372361993</v>
+        <v>0.000295941259900692</v>
       </c>
       <c r="C32" t="n">
-        <v>0.01060596000933936</v>
+        <v>0.001533727514455641</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5600674375964221</v>
+        <v>-0.002710109430530498</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6016420368759765</v>
+        <v>0.003301991950331883</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.846993767631772</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0002855410455972233</v>
+        <v>0.58046395480427</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001532410754135825</v>
+        <v>0.0105920644318845</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.002717928842030857</v>
+        <v>0.5597038899958487</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003289010933225304</v>
+        <v>0.6012240196126913</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8521824265147955</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>big_span_treatment</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.003217439514964091</v>
+        <v>0.1348384925790881</v>
       </c>
       <c r="C34" t="n">
-        <v>0.003983890433832272</v>
+        <v>0.1244165069175249</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.004590842253700812</v>
+        <v>-0.1090133800615393</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01102572128362899</v>
+        <v>0.3786903652197154</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4193137172191329</v>
+        <v>0.2784681626532741</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,25 +2285,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>big_span</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.002242891807688965</v>
+        <v>0.002980661163500418</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001173661517189241</v>
+        <v>0.03141225726931016</v>
       </c>
       <c r="D35" t="n">
-        <v>-5.744249604258504e-05</v>
+        <v>-0.058586231757454</v>
       </c>
       <c r="E35" t="n">
-        <v>0.004543226111420514</v>
+        <v>0.06454755408445484</v>
       </c>
       <c r="F35" t="n">
-        <v>0.05600188208985693</v>
+        <v>0.9244034114648544</v>
       </c>
       <c r="G35" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>num_direct_reports</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.0007527623898864668</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.004069278319009156</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-0.007222876558441172</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.008728401338214106</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.8532394631073704</v>
+      </c>
+      <c r="G36" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -2350,13 +2375,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.427664644175294</v>
+        <v>-2.305476704343799</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5181657220038156</v>
+        <v>0.5231558886398957</v>
       </c>
       <c r="D2" t="n">
-        <v>2.798063509203218e-06</v>
+        <v>1.048781286690859e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2391,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04283704187763185</v>
+        <v>0.04353420434069191</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1065056610557124</v>
+        <v>0.106409056742103</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6875336293530986</v>
+        <v>0.6824506959222996</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2407,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3420089197228885</v>
+        <v>0.3432925190833495</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2258273108558932</v>
+        <v>0.2255266975590037</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1299064164023925</v>
+        <v>0.1279636622422186</v>
       </c>
     </row>
     <row r="5">
@@ -2398,13 +2423,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7568550919253106</v>
+        <v>0.7605144812869579</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1749116140278904</v>
+        <v>0.1749746302893661</v>
       </c>
       <c r="D5" t="n">
-        <v>1.511047971683326e-05</v>
+        <v>1.383729881436048e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2414,13 +2439,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1819727920118002</v>
+        <v>-0.1847253344570327</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2139666880119049</v>
+        <v>0.2137839199842164</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3950624226561791</v>
+        <v>0.3875467073943133</v>
       </c>
     </row>
     <row r="7">
@@ -2430,13 +2455,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1330552971690139</v>
+        <v>0.1315557084716397</v>
       </c>
       <c r="C7" t="n">
-        <v>0.195395281947656</v>
+        <v>0.1954900602479314</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4959002791352488</v>
+        <v>0.5009769126453631</v>
       </c>
     </row>
     <row r="8">
@@ -2446,13 +2471,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.097280476898208</v>
+        <v>-0.09701217403726656</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2107853049245229</v>
+        <v>0.2106651209791175</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6444295130162205</v>
+        <v>0.6451543539935694</v>
       </c>
     </row>
     <row r="9">
@@ -2462,13 +2487,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.068702246714659</v>
+        <v>1.06836372423693</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1704165076539107</v>
+        <v>0.17039906365261</v>
       </c>
       <c r="D9" t="n">
-        <v>3.584618716992556e-10</v>
+        <v>3.615710772054429e-10</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2503,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09164285114131052</v>
+        <v>0.08689152366058274</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2821462910028385</v>
+        <v>0.2814998287132306</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7453277880093387</v>
+        <v>0.7575699410849728</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2519,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.209366713538576</v>
+        <v>0.201795137724893</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2718908402685897</v>
+        <v>0.2720725433902599</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4412764034926281</v>
+        <v>0.4582714980348429</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2535,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.2458167359844367</v>
+        <v>-0.254717913624369</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3060864204610716</v>
+        <v>0.3064456171059297</v>
       </c>
       <c r="D12" t="n">
-        <v>0.421919332475261</v>
+        <v>0.4058600711263241</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2551,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2480605146834355</v>
+        <v>0.2464230505728121</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2698784026653991</v>
+        <v>0.2698278039491651</v>
       </c>
       <c r="D13" t="n">
-        <v>0.358013668571726</v>
+        <v>0.3611055994101838</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2567,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2887265920666393</v>
+        <v>0.2748558804119319</v>
       </c>
       <c r="C14" t="n">
-        <v>0.279712264658515</v>
+        <v>0.2804187360263206</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3019657220075033</v>
+        <v>0.3270059980902326</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2583,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.336456969341774</v>
+        <v>0.332378742824722</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2683702941076243</v>
+        <v>0.2680469343907508</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2099495347382754</v>
+        <v>0.2149746432427817</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2599,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1212332819747691</v>
+        <v>0.1140118957648396</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2679493505870756</v>
+        <v>0.2676707923199497</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6509459134758514</v>
+        <v>0.6701510266435819</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2615,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1766572982617265</v>
+        <v>0.1677017081805965</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2752350890811209</v>
+        <v>0.2756856221796299</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5209761107851441</v>
+        <v>0.5429833635124652</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2631,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3813830960578519</v>
+        <v>0.3735057320986759</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2677517444468921</v>
+        <v>0.2682143805306411</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1543334033865648</v>
+        <v>0.163751628838233</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2647,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1210111614869995</v>
+        <v>0.113216954125305</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2775843004204018</v>
+        <v>0.2774495710571204</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6628774877860051</v>
+        <v>0.6832272913858297</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2663,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.225518195266677</v>
+        <v>0.2221611794684661</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2783783956071257</v>
+        <v>0.2786852004816445</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4178747418803513</v>
+        <v>0.4253487681357134</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2679,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2301319673853001</v>
+        <v>0.2186935943615167</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2673309630216597</v>
+        <v>0.2670399544657338</v>
       </c>
       <c r="D21" t="n">
-        <v>0.389320440492123</v>
+        <v>0.4128123266990043</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2695,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.04646654583854187</v>
+        <v>0.03623470789752637</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2845286078456556</v>
+        <v>0.2843907115968459</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8702738657351106</v>
+        <v>0.8986145456843156</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2711,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.0216275675290911</v>
+        <v>-0.02820713606357468</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2925905475884691</v>
+        <v>0.2921362658986943</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9410760153784367</v>
+        <v>0.9230800146895277</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2727,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8764973807420283</v>
+        <v>0.87713009663581</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1598667289796821</v>
+        <v>0.159855830901508</v>
       </c>
       <c r="D24" t="n">
-        <v>4.189413124540285e-08</v>
+        <v>4.088004552582568e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2718,13 +2743,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5923085897232843</v>
+        <v>-0.5917569512165407</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1169262828732781</v>
+        <v>0.1170694015370462</v>
       </c>
       <c r="D25" t="n">
-        <v>4.069915021574022e-07</v>
+        <v>4.309473117540662e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2759,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.138600032821649</v>
+        <v>-0.1379347416692539</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1507698258117116</v>
+        <v>0.150758529596044</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3579479313928068</v>
+        <v>0.3602240607133723</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2775,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08444119781568356</v>
+        <v>-0.08351770317020622</v>
       </c>
       <c r="C27" t="n">
-        <v>0.157443858905906</v>
+        <v>0.1575153679928091</v>
       </c>
       <c r="D27" t="n">
-        <v>0.591733427973868</v>
+        <v>0.5959598250856347</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2791,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1114085316198852</v>
+        <v>-0.1104442107318848</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1483441008175725</v>
+        <v>0.1485662159865757</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4526440879579768</v>
+        <v>0.4572391948936894</v>
       </c>
     </row>
     <row r="29">
@@ -2782,93 +2807,93 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3220151818496279</v>
+        <v>-0.3186105264926382</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1549982402231347</v>
+        <v>0.1550508799957422</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03775166539448363</v>
+        <v>0.03989086197612763</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.002580638036074954</v>
+        <v>0.01482976190572093</v>
       </c>
       <c r="C30" t="n">
-        <v>0.007292353686099036</v>
+        <v>0.007101299600452754</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7234267695349466</v>
+        <v>0.03676928414705771</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.03120747680900965</v>
+        <v>-0.01307736032002064</v>
       </c>
       <c r="C31" t="n">
-        <v>0.05994942728923073</v>
+        <v>0.008192979711924422</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6026709615967271</v>
+        <v>0.1104516092929849</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.01293860122823147</v>
+        <v>-0.03170385269830843</v>
       </c>
       <c r="C32" t="n">
-        <v>0.008183645815534327</v>
+        <v>0.06006853305094961</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1138708520154848</v>
+        <v>0.5976418440010105</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>big_span</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.01847772081409663</v>
+        <v>-0.181689871304995</v>
       </c>
       <c r="C33" t="n">
-        <v>0.02286223089800341</v>
+        <v>0.1675437923427971</v>
       </c>
       <c r="D33" t="n">
-        <v>0.418963730891026</v>
+        <v>0.2781732450178442</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.01489842147412546</v>
+        <v>0.03008506166450894</v>
       </c>
       <c r="C34" t="n">
-        <v>0.007094501199577966</v>
+        <v>0.02331722086972509</v>
       </c>
       <c r="D34" t="n">
-        <v>0.03572922606502676</v>
+        <v>0.1969636114055594</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -483,10 +483,10 @@
         <v>-0.058</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.029</v>
+        <v>-0.028</v>
       </c>
       <c r="E2" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -537,10 +537,10 @@
         <v>0.063</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="E4" t="n">
-        <v>0.057</v>
+        <v>0.061</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -552,7 +552,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>big_span</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.025</v>
+        <v>0.036</v>
       </c>
       <c r="D5" t="n">
-        <v>0.015</v>
+        <v>0.029</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01</v>
+        <v>0.006999999999999996</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.392</v>
+        <v>-0.09</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.031</v>
+        <v>-0.029</v>
       </c>
       <c r="E6" t="n">
-        <v>0.361</v>
+        <v>0.061</v>
       </c>
       <c r="F6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.181</v>
+        <v>0.014</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.017</v>
       </c>
       <c r="E7" t="n">
-        <v>0.172</v>
+        <v>-0.003000000000000001</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.044</v>
+        <v>0.185</v>
       </c>
       <c r="D8" t="n">
-        <v>0.026</v>
+        <v>0.013</v>
       </c>
       <c r="E8" t="n">
-        <v>0.018</v>
+        <v>0.172</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.351</v>
+        <v>-0.019</v>
       </c>
       <c r="D9" t="n">
-        <v>0.016</v>
+        <v>0.007</v>
       </c>
       <c r="E9" t="n">
-        <v>0.335</v>
+        <v>0.012</v>
       </c>
       <c r="F9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>-0.181</v>
+      </c>
+      <c r="D10" t="n">
         <v>0.014</v>
       </c>
-      <c r="D10" t="n">
-        <v>0.021</v>
-      </c>
       <c r="E10" t="n">
-        <v>-0.007000000000000001</v>
+        <v>0.167</v>
       </c>
       <c r="F10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.095</v>
+        <v>0.013</v>
       </c>
       <c r="D11" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="E11" t="n">
-        <v>0.093</v>
+        <v>0.005999999999999999</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.215</v>
+        <v>-0.054</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.063</v>
+        <v>-0.023</v>
       </c>
       <c r="E12" t="n">
-        <v>0.152</v>
+        <v>0.031</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.01</v>
+        <v>-0.012</v>
       </c>
       <c r="D13" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="E13" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.076</v>
+        <v>0.351</v>
       </c>
       <c r="D14" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="F14" t="b">
         <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="F14" t="b">
-        <v>1</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.368</v>
+        <v>-0.015</v>
       </c>
       <c r="D15" t="n">
-        <v>0.005</v>
+        <v>-0.03</v>
       </c>
       <c r="E15" t="n">
-        <v>0.363</v>
+        <v>-0.015</v>
       </c>
       <c r="F15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -861,10 +861,10 @@
         <v>-0.001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.001</v>
+        <v>-0.008</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.004</v>
+        <v>-0.007</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.003</v>
+        <v>0.001</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="D18" t="n">
         <v>0.004</v>
       </c>
       <c r="E18" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.007</v>
+        <v>-0.392</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.002</v>
+        <v>-0.027</v>
       </c>
       <c r="E19" t="n">
-        <v>0.005</v>
+        <v>0.365</v>
       </c>
       <c r="F19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.054</v>
+        <v>-0.095</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.02</v>
+        <v>0.005</v>
       </c>
       <c r="E20" t="n">
-        <v>0.034</v>
+        <v>0.09</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.008</v>
+        <v>0.036</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.001</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0009999999999999992</v>
+        <v>0.035</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.185</v>
+        <v>0.007</v>
       </c>
       <c r="D22" t="n">
-        <v>0.018</v>
+        <v>-0.006</v>
       </c>
       <c r="E22" t="n">
-        <v>0.167</v>
+        <v>0.001</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.059</v>
+        <v>-0.001</v>
       </c>
       <c r="D23" t="n">
-        <v>0.014</v>
+        <v>-0.007</v>
       </c>
       <c r="E23" t="n">
-        <v>0.045</v>
+        <v>-0.006</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.09</v>
+        <v>-0.096</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.029</v>
+        <v>0.017</v>
       </c>
       <c r="E24" t="n">
-        <v>0.061</v>
+        <v>0.079</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.033</v>
+        <v>-0.007</v>
       </c>
       <c r="D25" t="n">
-        <v>0.024</v>
+        <v>-0.028</v>
       </c>
       <c r="E25" t="n">
-        <v>0.009000000000000001</v>
+        <v>-0.021</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.036</v>
+        <v>0.076</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.004</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.032</v>
+        <v>0.076</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.012</v>
+        <v>0.368</v>
       </c>
       <c r="D27" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="E27" t="n">
-        <v>0.006</v>
+        <v>0.364</v>
       </c>
       <c r="F27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.075</v>
+        <v>-0.215</v>
       </c>
       <c r="D28" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.058</v>
       </c>
       <c r="E28" t="n">
-        <v>0.066</v>
+        <v>0.157</v>
       </c>
       <c r="F28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.019</v>
+        <v>0.075</v>
       </c>
       <c r="D29" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="E29" t="n">
-        <v>0.014</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.015</v>
+        <v>0.059</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.028</v>
+        <v>0.021</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.013</v>
+        <v>0.03799999999999999</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.096</v>
+        <v>0.033</v>
       </c>
       <c r="D31" t="n">
-        <v>0.021</v>
+        <v>0.025</v>
       </c>
       <c r="E31" t="n">
-        <v>0.075</v>
+        <v>0.008</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.007</v>
+        <v>0.044</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.028</v>
+        <v>0.027</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.021</v>
+        <v>0.017</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1320,10 +1320,10 @@
         <v>-0.021</v>
       </c>
       <c r="D33" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="E33" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
@@ -1388,22 +1388,22 @@
         <v>6217</v>
       </c>
       <c r="B2" t="n">
-        <v>6058.441997574593</v>
+        <v>6054.814949838281</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9950246761341104</v>
+        <v>0.9955799696542841</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1609838789597046</v>
+        <v>0.1629543857601319</v>
       </c>
       <c r="E2" t="n">
-        <v>1.82043870212157</v>
+        <v>1.864929480836644</v>
       </c>
       <c r="F2" t="n">
-        <v>1.151957513402452</v>
+        <v>1.150690388380934</v>
       </c>
       <c r="G2" t="n">
-        <v>1.820173420053884</v>
+        <v>1.864005612713846</v>
       </c>
     </row>
   </sheetData>
@@ -1417,7 +1417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.480396945623569</v>
+        <v>1.493998113457369</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09231355605799561</v>
+        <v>0.0915417634209051</v>
       </c>
       <c r="D2" t="n">
-        <v>1.299465700465078</v>
+        <v>1.314579554071109</v>
       </c>
       <c r="E2" t="n">
-        <v>1.66132819078206</v>
+        <v>1.673416672843629</v>
       </c>
       <c r="F2" t="n">
-        <v>7.091592649212459e-58</v>
+        <v>7.067206153092709e-60</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01014980283236199</v>
+        <v>0.01139734884641806</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01836499278683015</v>
+        <v>0.01836912354870617</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02584492160616299</v>
+        <v>-0.02460547173661262</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04614452727088696</v>
+        <v>0.04740016942944873</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5804885690891299</v>
+        <v>0.5349534598931439</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.09487871714183245</v>
+        <v>-0.09369904833157609</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04520079875316899</v>
+        <v>0.04522288491293567</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1834706547704867</v>
+        <v>-0.1823342740379298</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.006286779513178242</v>
+        <v>-0.005063822625222397</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03581253134930484</v>
+        <v>0.03827115219154174</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01205799529998015</v>
+        <v>-0.01066467357152956</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02981223863521449</v>
+        <v>0.02981982333274044</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.07048890932351409</v>
+        <v>-0.06911045332904799</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04637291872355379</v>
+        <v>0.04778110618598887</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6858711013557701</v>
+        <v>0.7206149497742436</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.04304972157863009</v>
+        <v>-0.04301492997829071</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03059882979701848</v>
+        <v>0.03066350771200715</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1030223259498574</v>
+        <v>-0.1031143007334909</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01692288279259718</v>
+        <v>0.01708444077690951</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1594548344009056</v>
+        <v>0.1606749173778477</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001240700728441044</v>
+        <v>0.0009581591331443549</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02946796359864412</v>
+        <v>0.0295414371461689</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05651544662263876</v>
+        <v>-0.05694199372490041</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05899684807952085</v>
+        <v>0.05885831199118913</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9664162895200017</v>
+        <v>0.9741256203875795</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.01496662172759925</v>
+        <v>-0.01499471859888909</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03016435277694363</v>
+        <v>0.03011722069603003</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.07408766678736953</v>
+        <v>-0.0740233864775523</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04415442333217102</v>
+        <v>0.04403394927977411</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6197750642373493</v>
+        <v>0.6185696367956148</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01054368268372452</v>
+        <v>0.009760945713619042</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02965183417955853</v>
+        <v>0.02969887927955248</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.04757284438376398</v>
+        <v>-0.04844778805550669</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06866020975121304</v>
+        <v>0.06796967948274478</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7221530148300359</v>
+        <v>0.7424098394948975</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.008469138305613943</v>
+        <v>0.008945036718057832</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0522680755048006</v>
+        <v>0.05227344659369296</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.09397440722501545</v>
+        <v>-0.09350903595335835</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1109126838362433</v>
+        <v>0.111399109389474</v>
       </c>
       <c r="F10" t="n">
-        <v>0.87128008956365</v>
+        <v>0.8641293418452052</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.07442515093376466</v>
+        <v>-0.07294946240716814</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04961328479180981</v>
+        <v>0.04956147246244857</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1716654022804407</v>
+        <v>-0.170088163454341</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02281510041291135</v>
+        <v>0.02418923864000472</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1335871310677165</v>
+        <v>0.1410482591329769</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.08771751346518676</v>
+        <v>-0.086623422743713</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05098868776485564</v>
+        <v>0.05089844563154296</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1876535051032619</v>
+        <v>-0.1863825430506073</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0122184781728884</v>
+        <v>0.01313569756318125</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08537195926819338</v>
+        <v>0.08877648025963013</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.0111222098308775</v>
+        <v>-0.008024749836484072</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0510273691698105</v>
+        <v>0.05113295056969706</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1111340156295356</v>
+        <v>-0.1082434913763572</v>
       </c>
       <c r="E13" t="n">
-        <v>0.08888959596778061</v>
+        <v>0.092193991703389</v>
       </c>
       <c r="F13" t="n">
-        <v>0.827455934193412</v>
+        <v>0.8752929892942469</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.0429355024465398</v>
+        <v>-0.04340557759080335</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05055059599645623</v>
+        <v>0.05045929460802627</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1420128499966287</v>
+        <v>-0.142303977707831</v>
       </c>
       <c r="E14" t="n">
-        <v>0.05614184510354906</v>
+        <v>0.05549282252622428</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3956826737847413</v>
+        <v>0.3896734268082835</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.04437647874627407</v>
+        <v>-0.04574671530427665</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0493334650852327</v>
+        <v>0.04961392181428276</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1410682935458944</v>
+        <v>-0.142988215192057</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05231533605334626</v>
+        <v>0.05149478458350369</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3683753135199094</v>
+        <v>0.3565004068554797</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.03724912566851709</v>
+        <v>-0.03713592023139946</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05013335245975453</v>
+        <v>0.05010472347761161</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1355086909138885</v>
+        <v>-0.1353393737028567</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06101043957685431</v>
+        <v>0.06106753324005778</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4574811395184714</v>
+        <v>0.4585927625445312</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.02013564391904812</v>
+        <v>-0.01948239245873596</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05067591738089416</v>
+        <v>0.05062347938805209</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.119458616869128</v>
+        <v>-0.1187025888314238</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07918732903103178</v>
+        <v>0.07973780391395191</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6911156643996998</v>
+        <v>0.7003493364163528</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.02951065520775304</v>
+        <v>-0.02897547644273375</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05110457249157446</v>
+        <v>0.05100630816200021</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1296737767365553</v>
+        <v>-0.1289460034246055</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07065246632104925</v>
+        <v>0.07099505053913804</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5636312794271764</v>
+        <v>0.5699831381275109</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.04054326933592471</v>
+        <v>-0.04008864287509666</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05001967309932249</v>
+        <v>0.04996256722766794</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1385800271290638</v>
+        <v>-0.138013475216487</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05749348845721435</v>
+        <v>0.05783618946629372</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4176261697368354</v>
+        <v>0.4223369033872212</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.09100057242621594</v>
+        <v>-0.08980962914662681</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04944530324025028</v>
+        <v>0.04956030606584796</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1879115859817681</v>
+        <v>-0.1869460440984708</v>
       </c>
       <c r="E20" t="n">
-        <v>0.005910441129336252</v>
+        <v>0.007326785805217173</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06570527191995246</v>
+        <v>0.06996638708640618</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.00369568530611814</v>
+        <v>0.003397924751943016</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04898316444458103</v>
+        <v>0.04891083189773241</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.09230955285406361</v>
+        <v>-0.09246554422150537</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09970092346629988</v>
+        <v>0.0992613937253914</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9398582124386522</v>
+        <v>0.9446140588838092</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.006269093317233094</v>
+        <v>-0.005820590202436597</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05001575119043807</v>
+        <v>0.04992222605418412</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1042981643102081</v>
+        <v>-0.1036663552967046</v>
       </c>
       <c r="E22" t="n">
-        <v>0.09175997767574187</v>
+        <v>0.0920251748918314</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9002525019265116</v>
+        <v>0.907182456498179</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06082558774950667</v>
+        <v>-0.06091882540351709</v>
       </c>
       <c r="C23" t="n">
-        <v>0.04992592593427267</v>
+        <v>0.04983273321557467</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1586786044754954</v>
+        <v>-0.1585891877572363</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03702742897648202</v>
+        <v>0.03675153695020213</v>
       </c>
       <c r="F23" t="n">
-        <v>0.22310365827976</v>
+        <v>0.2215314283124573</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.0456652168574929</v>
+        <v>-0.04546552218884722</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0409915365619473</v>
+        <v>0.04088368473780886</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1260071521898664</v>
+        <v>-0.1255960718302425</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03467671847488064</v>
+        <v>0.03466502745254803</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2652724350207532</v>
+        <v>0.2661080237958381</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.00587509087889457</v>
+        <v>0.005855003749821474</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02360333061262574</v>
+        <v>0.02357096913273556</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.04038658703704361</v>
+        <v>-0.04034324683104553</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05213676879483275</v>
+        <v>0.05205325433068848</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8034308633569933</v>
+        <v>0.8038257535625445</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01971342777812008</v>
+        <v>0.02022035479316613</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02844465885270396</v>
+        <v>0.02847209635064418</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03603707912570811</v>
+        <v>-0.03558392861845076</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07546393468194826</v>
+        <v>0.07602463820478303</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4882813297546514</v>
+        <v>0.4775916198870094</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.009295584463230843</v>
+        <v>0.01017504924390031</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02918964367861768</v>
+        <v>0.02920817082181938</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.04791506586841706</v>
+        <v>-0.04707191362115934</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06650623479487874</v>
+        <v>0.06742201210895997</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7501399152983237</v>
+        <v>0.7275675029194189</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0291009343021023</v>
+        <v>0.03075274291213687</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02854626163111398</v>
+        <v>0.02852520938942744</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.02684871038813871</v>
+        <v>-0.02515564014260471</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08505057899234331</v>
+        <v>0.08666112596687844</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3079985571095434</v>
+        <v>0.2809935950997029</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.01455084235275106</v>
+        <v>-0.01431775187402593</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02750445917332445</v>
+        <v>0.02757795020140893</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.06845859174671928</v>
+        <v>-0.06836954103622657</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03935690704121717</v>
+        <v>0.03973403728817471</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5967806460697764</v>
+        <v>0.6036394802206324</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2472871475932633</v>
+        <v>0.3642249454799705</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1204906242988269</v>
+        <v>0.03859338896492541</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01112986349281583</v>
+        <v>0.2885832930673712</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4834444316937108</v>
+        <v>0.4398665978925699</v>
       </c>
       <c r="F30" t="n">
-        <v>0.04013709890141682</v>
+        <v>3.817947647451369e-21</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>big_span</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.002980661163500458</v>
+        <v>0.0002855410455972163</v>
       </c>
       <c r="C31" t="n">
-        <v>0.03141225726931023</v>
+        <v>0.001532410754135807</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0585862317574541</v>
+        <v>-0.002717928842030828</v>
       </c>
       <c r="E31" t="n">
-        <v>0.06454755408445502</v>
+        <v>0.003289010933225261</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9244034114648536</v>
+        <v>0.8521824265147973</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2214,16 +2214,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.58046395480427</v>
+        <v>0.5808547372361993</v>
       </c>
       <c r="C32" t="n">
-        <v>0.01059206443188444</v>
+        <v>0.01060596000933943</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5597038899958489</v>
+        <v>0.5600674375964219</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6012240196126912</v>
+        <v>0.6016420368759767</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.002290121492346935</v>
+        <v>0.003217439514964089</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001172016575419001</v>
+        <v>0.003983890433832242</v>
       </c>
       <c r="D33" t="n">
-        <v>-6.988784758278632e-06</v>
+        <v>-0.004590842253700756</v>
       </c>
       <c r="E33" t="n">
-        <v>0.004587231769452148</v>
+        <v>0.01102572128362894</v>
       </c>
       <c r="F33" t="n">
-        <v>0.05070110579169546</v>
+        <v>0.4193137172191297</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0002959412599006877</v>
+        <v>-0.001854532319157675</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001533727514455618</v>
+        <v>0.001243594980252404</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.002710109430530459</v>
+        <v>-0.004291933691807186</v>
       </c>
       <c r="E34" t="n">
-        <v>0.003301991950331835</v>
+        <v>0.0005828690534918361</v>
       </c>
       <c r="F34" t="n">
-        <v>0.846993767631772</v>
+        <v>0.1358913747251281</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,50 +2285,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>big_span_treatment</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.134838492579088</v>
+        <v>0.002242891807688961</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1244165069175251</v>
+        <v>0.001173661517189244</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1090133800615397</v>
+        <v>-5.744249604259458e-05</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3786903652197156</v>
+        <v>0.004543226111420517</v>
       </c>
       <c r="F35" t="n">
-        <v>0.278468162653275</v>
+        <v>0.05600188208985798</v>
       </c>
       <c r="G35" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>num_direct_reports</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>0.0007527623898864515</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0.004069278319009195</v>
-      </c>
-      <c r="D36" t="n">
-        <v>-0.007222876558441263</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.008728401338214167</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.8532394631073748</v>
-      </c>
-      <c r="G36" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -2375,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.305476704343799</v>
+        <v>-2.427664644175298</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5231558886399189</v>
+        <v>0.5181657220038092</v>
       </c>
       <c r="D2" t="n">
-        <v>1.048781286691801e-05</v>
+        <v>2.798063509202317e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2391,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04353420434069196</v>
+        <v>0.04283704187763188</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1064090567421032</v>
+        <v>0.1065056610557124</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6824506959222996</v>
+        <v>0.6875336293530983</v>
       </c>
     </row>
     <row r="4">
@@ -2407,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3432925190833494</v>
+        <v>0.3420089197228887</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2255266975590038</v>
+        <v>0.2258273108558932</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1279636622422188</v>
+        <v>0.1299064164023922</v>
       </c>
     </row>
     <row r="5">
@@ -2423,13 +2398,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7605144812869579</v>
+        <v>0.7568550919253108</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1749746302893667</v>
+        <v>0.1749116140278904</v>
       </c>
       <c r="D5" t="n">
-        <v>1.383729881436144e-05</v>
+        <v>1.51104797168333e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2439,13 +2414,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1847253344570327</v>
+        <v>-0.1819727920118003</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2137839199842169</v>
+        <v>0.2139666880119049</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3875467073943144</v>
+        <v>0.395062422656179</v>
       </c>
     </row>
     <row r="7">
@@ -2455,13 +2430,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1315557084716396</v>
+        <v>0.1330552971690139</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1954900602479319</v>
+        <v>0.195395281947656</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5009769126453645</v>
+        <v>0.4959002791352489</v>
       </c>
     </row>
     <row r="8">
@@ -2471,13 +2446,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09701217403726664</v>
+        <v>-0.0972804768982078</v>
       </c>
       <c r="C8" t="n">
-        <v>0.210665120979118</v>
+        <v>0.210785304924523</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6451543539935698</v>
+        <v>0.6444295130162212</v>
       </c>
     </row>
     <row r="9">
@@ -2487,13 +2462,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.06836372423693</v>
+        <v>1.068702246714659</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1703990636526104</v>
+        <v>0.1704165076539109</v>
       </c>
       <c r="D9" t="n">
-        <v>3.615710772054783e-10</v>
+        <v>3.584618716992699e-10</v>
       </c>
     </row>
     <row r="10">
@@ -2503,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08689152366058303</v>
+        <v>0.09164285114131125</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2814998287132319</v>
+        <v>0.2821462910028381</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7575699410849731</v>
+        <v>0.7453277880093364</v>
       </c>
     </row>
     <row r="11">
@@ -2519,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2017951377248935</v>
+        <v>0.2093667135385768</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2720725433902608</v>
+        <v>0.2718908402685904</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4582714980348432</v>
+        <v>0.4412764034926278</v>
       </c>
     </row>
     <row r="12">
@@ -2535,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.2547179136243685</v>
+        <v>-0.245816735984436</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3064456171059304</v>
+        <v>0.3060864204610717</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4058600711263259</v>
+        <v>0.4219193324752625</v>
       </c>
     </row>
     <row r="13">
@@ -2551,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2464230505728126</v>
+        <v>0.2480605146834362</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2698278039491653</v>
+        <v>0.2698784026653988</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3611055994101833</v>
+        <v>0.3580136685717242</v>
       </c>
     </row>
     <row r="14">
@@ -2567,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2748558804119323</v>
+        <v>0.2887265920666398</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2804187360263232</v>
+        <v>0.2797122646585152</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3270059980902364</v>
+        <v>0.3019657220075027</v>
       </c>
     </row>
     <row r="15">
@@ -2583,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3323787428247227</v>
+        <v>0.3364569693417747</v>
       </c>
       <c r="C15" t="n">
-        <v>0.268046934390752</v>
+        <v>0.2683702941076248</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2149746432427828</v>
+        <v>0.2099495347382754</v>
       </c>
     </row>
     <row r="16">
@@ -2599,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1140118957648401</v>
+        <v>0.1212332819747698</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2676707923199509</v>
+        <v>0.267949350587076</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6701510266435817</v>
+        <v>0.6509459134758498</v>
       </c>
     </row>
     <row r="17">
@@ -2615,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1677017081805971</v>
+        <v>0.1766572982617271</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2756856221796307</v>
+        <v>0.2752350890811211</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5429833635124649</v>
+        <v>0.5209761107851427</v>
       </c>
     </row>
     <row r="18">
@@ -2631,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3735057320986765</v>
+        <v>0.3813830960578529</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2682143805306412</v>
+        <v>0.267751744446892</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1637516288382325</v>
+        <v>0.1543334033865635</v>
       </c>
     </row>
     <row r="19">
@@ -2647,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1132169541253054</v>
+        <v>0.1210111614870003</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2774495710571215</v>
+        <v>0.2775843004204024</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6832272913858297</v>
+        <v>0.6628774877860037</v>
       </c>
     </row>
     <row r="20">
@@ -2663,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2221611794684668</v>
+        <v>0.2255181952666778</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2786852004816464</v>
+        <v>0.2783783956071254</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4253487681357151</v>
+        <v>0.4178747418803492</v>
       </c>
     </row>
     <row r="21">
@@ -2679,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2186935943615172</v>
+        <v>0.2301319673853008</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2670399544657355</v>
+        <v>0.2673309630216595</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4128123266990062</v>
+        <v>0.3893204404921214</v>
       </c>
     </row>
     <row r="22">
@@ -2695,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.03623470789752706</v>
+        <v>0.0464665458385428</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2843907115968473</v>
+        <v>0.2845286078456561</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8986145456843142</v>
+        <v>0.8702738657351082</v>
       </c>
     </row>
     <row r="23">
@@ -2711,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.02820713606357417</v>
+        <v>-0.02162756752909025</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2921362658986958</v>
+        <v>0.2925905475884686</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9230800146895295</v>
+        <v>0.9410760153784389</v>
       </c>
     </row>
     <row r="24">
@@ -2727,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.87713009663581</v>
+        <v>0.8764973807420283</v>
       </c>
       <c r="C24" t="n">
-        <v>0.159855830901508</v>
+        <v>0.1598667289796822</v>
       </c>
       <c r="D24" t="n">
-        <v>4.088004552582586e-08</v>
+        <v>4.189413124540377e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2743,13 +2718,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5917569512165406</v>
+        <v>-0.5923085897232842</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1170694015370464</v>
+        <v>0.1169262828732781</v>
       </c>
       <c r="D25" t="n">
-        <v>4.30947311754086e-07</v>
+        <v>4.069915021574061e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2759,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1379347416692537</v>
+        <v>-0.1386000328216487</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1507585295960442</v>
+        <v>0.1507698258117117</v>
       </c>
       <c r="D26" t="n">
-        <v>0.360224060713374</v>
+        <v>0.3579479313928081</v>
       </c>
     </row>
     <row r="27">
@@ -2775,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08351770317020611</v>
+        <v>-0.08444119781568347</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1575153679928091</v>
+        <v>0.1574438589059061</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5959598250856352</v>
+        <v>0.5917334279738686</v>
       </c>
     </row>
     <row r="28">
@@ -2791,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1104442107318846</v>
+        <v>-0.1114085316198851</v>
       </c>
       <c r="C28" t="n">
-        <v>0.148566215986576</v>
+        <v>0.1483441008175726</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4572391948936911</v>
+        <v>0.4526440879579776</v>
       </c>
     </row>
     <row r="29">
@@ -2807,29 +2782,29 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.318610526492638</v>
+        <v>-0.3220151818496277</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1550508799957422</v>
+        <v>0.1549982402231347</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03989086197612763</v>
+        <v>0.03775166539448369</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>big_span</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1816898713049951</v>
+        <v>-0.01293860122823143</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1675437923427983</v>
+        <v>0.008183645815534176</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2781732450178475</v>
+        <v>0.1138708520154793</v>
       </c>
     </row>
     <row r="31">
@@ -2839,61 +2814,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.03170385269830844</v>
+        <v>-0.03120747680900946</v>
       </c>
       <c r="C31" t="n">
-        <v>0.06006853305094995</v>
+        <v>0.05994942728922969</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5976418440010126</v>
+        <v>0.6026709615967232</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.01482976190572093</v>
+        <v>0.01847772081409666</v>
       </c>
       <c r="C32" t="n">
-        <v>0.007101299600452767</v>
+        <v>0.02286223089800343</v>
       </c>
       <c r="D32" t="n">
-        <v>0.03676928414705806</v>
+        <v>0.4189637308910258</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.01307736032002064</v>
+        <v>0.002580638036074965</v>
       </c>
       <c r="C33" t="n">
-        <v>0.008192979711924618</v>
+        <v>0.00729235368609906</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1104516092929934</v>
+        <v>0.7234267695349461</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.03008506166450895</v>
+        <v>0.01489842147412547</v>
       </c>
       <c r="C34" t="n">
-        <v>0.02331722086972511</v>
+        <v>0.007094501199577954</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1969636114055597</v>
+        <v>0.03572922606502637</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -480,13 +480,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.058</v>
+        <v>-0.055</v>
       </c>
       <c r="D2" t="n">
         <v>-0.028</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03</v>
+        <v>0.027</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.109</v>
+        <v>0.103</v>
       </c>
       <c r="D3" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08499999999999999</v>
+        <v>0.07799999999999999</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.063</v>
+        <v>-0.022</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002</v>
+        <v>-0.021</v>
       </c>
       <c r="E4" t="n">
-        <v>0.061</v>
+        <v>0.0009999999999999974</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.036</v>
+        <v>0.026</v>
       </c>
       <c r="D5" t="n">
-        <v>0.029</v>
+        <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006999999999999996</v>
+        <v>0.016</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.09</v>
+        <v>-0.018</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.029</v>
+        <v>0.006</v>
       </c>
       <c r="E6" t="n">
-        <v>0.061</v>
+        <v>0.012</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.014</v>
+        <v>-0.015</v>
       </c>
       <c r="D7" t="n">
-        <v>0.017</v>
+        <v>0.002</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.003000000000000001</v>
+        <v>0.013</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.185</v>
+        <v>0.024</v>
       </c>
       <c r="D8" t="n">
-        <v>0.013</v>
+        <v>0.004</v>
       </c>
       <c r="E8" t="n">
-        <v>0.172</v>
+        <v>0.02</v>
       </c>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.019</v>
+        <v>0.045</v>
       </c>
       <c r="D9" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="E9" t="n">
-        <v>0.012</v>
+        <v>0.039</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.181</v>
+        <v>0.369</v>
       </c>
       <c r="D10" t="n">
-        <v>0.014</v>
+        <v>0.007</v>
       </c>
       <c r="E10" t="n">
-        <v>0.167</v>
+        <v>0.362</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.013</v>
+        <v>-0.216</v>
       </c>
       <c r="D11" t="n">
-        <v>0.007</v>
+        <v>-0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>0.005999999999999999</v>
+        <v>0.156</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.054</v>
+        <v>-0.183</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.023</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0.031</v>
+        <v>0.174</v>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.012</v>
+        <v>-0.015</v>
       </c>
       <c r="D13" t="n">
-        <v>0.006</v>
+        <v>-0.024</v>
       </c>
       <c r="E13" t="n">
-        <v>0.006</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.351</v>
+        <v>0.075</v>
       </c>
       <c r="D14" t="n">
-        <v>0.016</v>
+        <v>0.008</v>
       </c>
       <c r="E14" t="n">
-        <v>0.335</v>
+        <v>0.067</v>
       </c>
       <c r="F14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.015</v>
+        <v>0.035</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.03</v>
+        <v>0.024</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.015</v>
+        <v>0.011</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.001</v>
+        <v>0.011</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.001</v>
+        <v>0.004</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.008</v>
+        <v>0.015</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.007</v>
+        <v>0.019</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001</v>
+        <v>-0.004</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="D18" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="E18" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.392</v>
+        <v>-0.117</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.027</v>
+        <v>-0.003</v>
       </c>
       <c r="E19" t="n">
-        <v>0.365</v>
+        <v>0.114</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,16 +966,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.095</v>
+        <v>0.19</v>
       </c>
       <c r="D20" t="n">
-        <v>0.005</v>
+        <v>0.024</v>
       </c>
       <c r="E20" t="n">
-        <v>0.09</v>
+        <v>0.166</v>
       </c>
       <c r="F20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -996,10 +996,10 @@
         <v>0.036</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.001</v>
+        <v>0.006</v>
       </c>
       <c r="E21" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.007</v>
+        <v>-0.095</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.006</v>
+        <v>0.015</v>
       </c>
       <c r="E22" t="n">
-        <v>0.001</v>
+        <v>0.08</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.001</v>
+        <v>0.35</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.007</v>
+        <v>0.019</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.006</v>
+        <v>0.331</v>
       </c>
       <c r="F23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.096</v>
+        <v>0.003</v>
       </c>
       <c r="D24" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.079</v>
+        <v>0.003</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.007</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.028</v>
+        <v>-0.029</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.021</v>
+        <v>0.042</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.076</v>
+        <v>0.099</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>0.076</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.368</v>
+        <v>-0.388</v>
       </c>
       <c r="D27" t="n">
-        <v>0.004</v>
+        <v>-0.031</v>
       </c>
       <c r="E27" t="n">
-        <v>0.364</v>
+        <v>0.357</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.215</v>
+        <v>0.036</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.058</v>
+        <v>0.02</v>
       </c>
       <c r="E28" t="n">
-        <v>0.157</v>
+        <v>0.016</v>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.075</v>
+        <v>-0.031</v>
       </c>
       <c r="D29" t="n">
-        <v>0.004</v>
+        <v>-0.005</v>
       </c>
       <c r="E29" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.059</v>
+        <v>-0.008</v>
       </c>
       <c r="D30" t="n">
-        <v>0.021</v>
+        <v>-0.021</v>
       </c>
       <c r="E30" t="n">
-        <v>0.03799999999999999</v>
+        <v>-0.013</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.033</v>
+        <v>0.02</v>
       </c>
       <c r="D31" t="n">
-        <v>0.025</v>
+        <v>0.002</v>
       </c>
       <c r="E31" t="n">
-        <v>0.008</v>
+        <v>0.018</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.044</v>
+        <v>-0.082</v>
       </c>
       <c r="D32" t="n">
-        <v>0.027</v>
+        <v>-0.027</v>
       </c>
       <c r="E32" t="n">
-        <v>0.017</v>
+        <v>0.05500000000000001</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.021</v>
+        <v>-0.025</v>
       </c>
       <c r="D33" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="E33" t="n">
-        <v>0.017</v>
+        <v>0.023</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
@@ -1385,25 +1385,25 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6217</v>
+        <v>6044</v>
       </c>
       <c r="B2" t="n">
-        <v>6054.814949838281</v>
+        <v>5880.843365300834</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9955799696542841</v>
+        <v>0.9949908017929653</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1629543857601319</v>
+        <v>0.1657439023898879</v>
       </c>
       <c r="E2" t="n">
-        <v>1.864929480836644</v>
+        <v>1.853163385476146</v>
       </c>
       <c r="F2" t="n">
-        <v>1.150690388380934</v>
+        <v>1.168712646832276</v>
       </c>
       <c r="G2" t="n">
-        <v>1.864005612713846</v>
+        <v>1.851455159122648</v>
       </c>
     </row>
   </sheetData>
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.493998113457369</v>
+        <v>1.430916292430171</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0915417634209051</v>
+        <v>0.1000831566672885</v>
       </c>
       <c r="D2" t="n">
-        <v>1.314579554071109</v>
+        <v>1.234756909903205</v>
       </c>
       <c r="E2" t="n">
-        <v>1.673416672843629</v>
+        <v>1.627075674957136</v>
       </c>
       <c r="F2" t="n">
-        <v>7.067206153092709e-60</v>
+        <v>2.275503900783856e-46</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01139734884641806</v>
+        <v>0.007543586664148222</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01836912354870617</v>
+        <v>0.01785366274695303</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02460547173661262</v>
+        <v>-0.02744894931200417</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04740016942944873</v>
+        <v>0.04253612264030061</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5349534598931439</v>
+        <v>0.6726431725489894</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.09369904833157609</v>
+        <v>-0.08746276072038488</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04522288491293567</v>
+        <v>0.04650174918954322</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1823342740379298</v>
+        <v>-0.1786045143500042</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.005063822625222397</v>
+        <v>0.003678992909234485</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03827115219154174</v>
+        <v>0.05999248510483759</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01066467357152956</v>
+        <v>-0.01403347829791829</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02981982333274044</v>
+        <v>0.03093697564115754</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06911045332904799</v>
+        <v>-0.07466883634518</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04778110618598887</v>
+        <v>0.04660187974934343</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7206149497742436</v>
+        <v>0.6501059066201329</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.04301492997829071</v>
+        <v>-0.03787901042425926</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03066350771200715</v>
+        <v>0.03200695968536719</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1031143007334909</v>
+        <v>-0.1006114986622044</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01708444077690951</v>
+        <v>0.0248534778136859</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1606749173778477</v>
+        <v>0.2366262230531389</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0009581591331443549</v>
+        <v>0.003790329245909087</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0295414371461689</v>
+        <v>0.02958199160697881</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05694199372490041</v>
+        <v>-0.05418930889473553</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05885831199118913</v>
+        <v>0.0617699673865537</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9741256203875795</v>
+        <v>0.8980463984756383</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.01499471859888909</v>
+        <v>-0.009122079738841245</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03011722069603003</v>
+        <v>0.03193143536141091</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0740233864775523</v>
+        <v>-0.07170654302187535</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04403394927977411</v>
+        <v>0.05346238354419286</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6185696367956148</v>
+        <v>0.7751254483554761</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009760945713619042</v>
+        <v>0.01941788401766658</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02969887927955248</v>
+        <v>0.03154682417714684</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.04844778805550669</v>
+        <v>-0.04241275519615866</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06796967948274478</v>
+        <v>0.08124852323149181</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7424098394948975</v>
+        <v>0.5382075398620452</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.008945036718057832</v>
+        <v>0.01040134955875804</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05227344659369296</v>
+        <v>0.0508899183012224</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.09350903595335835</v>
+        <v>-0.08934105748782363</v>
       </c>
       <c r="E10" t="n">
-        <v>0.111399109389474</v>
+        <v>0.1101437566053397</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8641293418452052</v>
+        <v>0.8380493712142114</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.07294946240716814</v>
+        <v>-0.07164478387083151</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04956147246244857</v>
+        <v>0.04908682432664911</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.170088163454341</v>
+        <v>-0.1678531916665084</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02418923864000472</v>
+        <v>0.02456362392484535</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1410482591329769</v>
+        <v>0.1444131763866517</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.086623422743713</v>
+        <v>-0.0855185319267841</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05089844563154296</v>
+        <v>0.05175895972033006</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1863825430506073</v>
+        <v>-0.1869642288558904</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01313569756318125</v>
+        <v>0.01592716500232216</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08877648025963013</v>
+        <v>0.09848442135817075</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.008024749836484072</v>
+        <v>-0.02014219262295371</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05113295056969706</v>
+        <v>0.04835193024820024</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1082434913763572</v>
+        <v>-0.114910234492419</v>
       </c>
       <c r="E13" t="n">
-        <v>0.092193991703389</v>
+        <v>0.0746258492465116</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8752929892942469</v>
+        <v>0.6769894910276899</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04340557759080335</v>
+        <v>-0.04644002677660911</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05045929460802627</v>
+        <v>0.04771229108737273</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.142303977707831</v>
+        <v>-0.1399543989277511</v>
       </c>
       <c r="E14" t="n">
-        <v>0.05549282252622428</v>
+        <v>0.04707434537453286</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3896734268082835</v>
+        <v>0.330386999999622</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.04574671530427665</v>
+        <v>-0.04379653132756444</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04961392181428276</v>
+        <v>0.04846010907971658</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.142988215192057</v>
+        <v>-0.1387765998106914</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05149478458350369</v>
+        <v>0.05118353715556253</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3565004068554797</v>
+        <v>0.3661202339272874</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.03713592023139946</v>
+        <v>-0.04275936100726026</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05010472347761161</v>
+        <v>0.04831280652572718</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1353393737028567</v>
+        <v>-0.1374507217897372</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06106753324005778</v>
+        <v>0.0519319997752167</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4585927625445312</v>
+        <v>0.3761284191125533</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.01948239245873596</v>
+        <v>-0.01894843278470495</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05062347938805209</v>
+        <v>0.04870450629519182</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1187025888314238</v>
+        <v>-0.1144075110080853</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07973780391395191</v>
+        <v>0.07651064543867536</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7003493364163528</v>
+        <v>0.697240000833819</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.02897547644273375</v>
+        <v>-0.03108663839834799</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05100630816200021</v>
+        <v>0.04980785777074328</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1289460034246055</v>
+        <v>-0.1287082457760983</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07099505053913804</v>
+        <v>0.06653496897940231</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5699831381275109</v>
+        <v>0.5325414206392294</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.04008864287509666</v>
+        <v>-0.0367426440212982</v>
       </c>
       <c r="C19" t="n">
-        <v>0.04996256722766794</v>
+        <v>0.04885158569502032</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.138013475216487</v>
+        <v>-0.1324899925712101</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05783618946629372</v>
+        <v>0.05900470452861373</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4223369033872212</v>
+        <v>0.4519741045461796</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.08980962914662681</v>
+        <v>-0.09057188359527762</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04956030606584796</v>
+        <v>0.04927809434824119</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1869460440984708</v>
+        <v>-0.1871551737445971</v>
       </c>
       <c r="E20" t="n">
-        <v>0.007326785805217173</v>
+        <v>0.006011406554041893</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06996638708640618</v>
+        <v>0.0660661546429757</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.003397924751943016</v>
+        <v>0.006813317291130315</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04891083189773241</v>
+        <v>0.04829245253929013</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.09246554422150537</v>
+        <v>-0.08783815041098823</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0992613937253914</v>
+        <v>0.1014647849932489</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9446140588838092</v>
+        <v>0.8878031757662277</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.005820590202436597</v>
+        <v>-0.006540046937606269</v>
       </c>
       <c r="C22" t="n">
-        <v>0.04992222605418412</v>
+        <v>0.04835474720397568</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1036663552967046</v>
+        <v>-0.1013136099389375</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0920251748918314</v>
+        <v>0.08823351606372495</v>
       </c>
       <c r="F22" t="n">
-        <v>0.907182456498179</v>
+        <v>0.8924131142901446</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06091882540351709</v>
+        <v>-0.06600063754204345</v>
       </c>
       <c r="C23" t="n">
-        <v>0.04983273321557467</v>
+        <v>0.04797515526485327</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1585891877572363</v>
+        <v>-0.160030214013873</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03675153695020213</v>
+        <v>0.02802893892978611</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2215314283124573</v>
+        <v>0.1689066787636249</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.04546552218884722</v>
+        <v>-0.05334327025872953</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04088368473780886</v>
+        <v>0.04069017585118595</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1255960718302425</v>
+        <v>-0.1330945494516554</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03466502745254803</v>
+        <v>0.02640800893419638</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2661080237958381</v>
+        <v>0.18987063592294</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.005855003749821474</v>
+        <v>0.006376847600652717</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02357096913273556</v>
+        <v>0.02353350465813137</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.04034324683104553</v>
+        <v>-0.03974797395929036</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05205325433068848</v>
+        <v>0.0525016691605958</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8038257535625445</v>
+        <v>0.786414960720857</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.02022035479316613</v>
+        <v>0.01943138450268198</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02847209635064418</v>
+        <v>0.02857099835969373</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03558392861845076</v>
+        <v>-0.0365667432846707</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07602463820478303</v>
+        <v>0.07542951229003464</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4775916198870094</v>
+        <v>0.4964356372482078</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.01017504924390031</v>
+        <v>0.01364006778452288</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02920817082181938</v>
+        <v>0.02987010641842526</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.04707191362115934</v>
+        <v>-0.04490426500996934</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06742201210895997</v>
+        <v>0.07218440057901511</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7275675029194189</v>
+        <v>0.6479254338860438</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.03075274291213687</v>
+        <v>0.02905652978827481</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02852520938942744</v>
+        <v>0.02904075610010609</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.02515564014260471</v>
+        <v>-0.02786230625174501</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08666112596687844</v>
+        <v>0.08597536582829464</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2809935950997029</v>
+        <v>0.3170477230932158</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.01431775187402593</v>
+        <v>-0.02046318562776313</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02757795020140893</v>
+        <v>0.02907864115174509</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.06836954103622657</v>
+        <v>-0.07745627500454783</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03973403728817471</v>
+        <v>0.03652990374902157</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6036394802206324</v>
+        <v>0.4816079278891827</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3642249454799705</v>
+        <v>0.3975380272033305</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03859338896492541</v>
+        <v>0.0384345990913346</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2885832930673712</v>
+        <v>0.3222075972240788</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4398665978925699</v>
+        <v>0.4728684571825822</v>
       </c>
       <c r="F30" t="n">
-        <v>3.817947647451369e-21</v>
+        <v>4.491231826565436e-25</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2189,19 +2189,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0002855410455972163</v>
+        <v>0.000476310167395319</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001532410754135807</v>
+        <v>0.001594281744030665</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.002717928842030828</v>
+        <v>-0.002648424632114489</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003289010933225261</v>
+        <v>0.003601044966905127</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8521824265147973</v>
+        <v>0.7651219509252148</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2214,16 +2214,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5808547372361993</v>
+        <v>0.579358867170089</v>
       </c>
       <c r="C32" t="n">
-        <v>0.01060596000933943</v>
+        <v>0.01041510004813046</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5600674375964219</v>
+        <v>0.5589456461803719</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6016420368759767</v>
+        <v>0.5997720881598061</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.003217439514964089</v>
+        <v>-0.0006838861338531119</v>
       </c>
       <c r="C33" t="n">
-        <v>0.003983890433832242</v>
+        <v>0.001270881981302638</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.004590842253700756</v>
+        <v>-0.003174769045807189</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01102572128362894</v>
+        <v>0.001806996778100965</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4193137172191297</v>
+        <v>0.5904946825704036</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.001854532319157675</v>
+        <v>0.007538497370492824</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001243594980252404</v>
+        <v>0.004040326219119685</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.004291933691807186</v>
+        <v>-0.0003803965047746438</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0005828690534918361</v>
+        <v>0.01545739124576029</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1358913747251281</v>
+        <v>0.06206738785507834</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2289,19 +2289,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.002242891807688961</v>
+        <v>0.002452468964350139</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001173661517189244</v>
+        <v>0.001267934449779066</v>
       </c>
       <c r="D35" t="n">
-        <v>-5.744249604259458e-05</v>
+        <v>-3.263689197443957e-05</v>
       </c>
       <c r="E35" t="n">
-        <v>0.004543226111420517</v>
+        <v>0.004937574820674718</v>
       </c>
       <c r="F35" t="n">
-        <v>0.05600188208985798</v>
+        <v>0.05308561981596006</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.427664644175298</v>
+        <v>-2.158962193354868</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5181657220038092</v>
+        <v>0.5271718320278242</v>
       </c>
       <c r="D2" t="n">
-        <v>2.798063509202317e-06</v>
+        <v>4.214999094552947e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04283704187763188</v>
+        <v>0.01238407949467807</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1065056610557124</v>
+        <v>0.1068934331327136</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6875336293530983</v>
+        <v>0.9077678991895134</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3420089197228887</v>
+        <v>0.3240614798744141</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2258273108558932</v>
+        <v>0.2300673427565921</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1299064164023922</v>
+        <v>0.1589681126213356</v>
       </c>
     </row>
     <row r="5">
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7568550919253108</v>
+        <v>0.7742552485596507</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1749116140278904</v>
+        <v>0.1687090407132097</v>
       </c>
       <c r="D5" t="n">
-        <v>1.51104797168333e-05</v>
+        <v>4.447494244187916e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1819727920118003</v>
+        <v>-0.1818685182700858</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2139666880119049</v>
+        <v>0.2082512218159787</v>
       </c>
       <c r="D6" t="n">
-        <v>0.395062422656179</v>
+        <v>0.3824924469491959</v>
       </c>
     </row>
     <row r="7">
@@ -2430,13 +2430,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1330552971690139</v>
+        <v>0.1367270800884084</v>
       </c>
       <c r="C7" t="n">
-        <v>0.195395281947656</v>
+        <v>0.1831182868961762</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4959002791352489</v>
+        <v>0.4552688866476771</v>
       </c>
     </row>
     <row r="8">
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.0972804768982078</v>
+        <v>-0.09668771677203515</v>
       </c>
       <c r="C8" t="n">
-        <v>0.210785304924523</v>
+        <v>0.1943986040042544</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6444295130162212</v>
+        <v>0.618929306423194</v>
       </c>
     </row>
     <row r="9">
@@ -2462,13 +2462,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.068702246714659</v>
+        <v>1.069744038116436</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1704165076539109</v>
+        <v>0.1651181209928365</v>
       </c>
       <c r="D9" t="n">
-        <v>3.584618716992699e-10</v>
+        <v>9.254124082934877e-11</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09164285114131125</v>
+        <v>0.1069802150572807</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2821462910028381</v>
+        <v>0.2832033016714792</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7453277880093364</v>
+        <v>0.7056158800782512</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2093667135385768</v>
+        <v>0.2579745235365334</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2718908402685904</v>
+        <v>0.2778622026713494</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4412764034926278</v>
+        <v>0.353186580600241</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.245816735984436</v>
+        <v>-0.1913836813322333</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3060864204610717</v>
+        <v>0.3052132495597789</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4219193324752625</v>
+        <v>0.5306270765800094</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2480605146834362</v>
+        <v>0.3096324773489049</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2698784026653988</v>
+        <v>0.2734335275906101</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3580136685717242</v>
+        <v>0.257471913364385</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2887265920666398</v>
+        <v>0.2686015457564108</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2797122646585152</v>
+        <v>0.2611524565189026</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3019657220075027</v>
+        <v>0.3037034494888953</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3364569693417747</v>
+        <v>0.2981954526051827</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2683702941076248</v>
+        <v>0.2676697859174169</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2099495347382754</v>
+        <v>0.2652610583887295</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1212332819747698</v>
+        <v>0.1286082242724552</v>
       </c>
       <c r="C16" t="n">
-        <v>0.267949350587076</v>
+        <v>0.2547964366533393</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6509459134758498</v>
+        <v>0.6137352020167333</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1766572982617271</v>
+        <v>0.1872659224740911</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2752350890811211</v>
+        <v>0.2740865337717661</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5209761107851427</v>
+        <v>0.4944574156002215</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3813830960578529</v>
+        <v>0.4792250424143023</v>
       </c>
       <c r="C18" t="n">
-        <v>0.267751744446892</v>
+        <v>0.2542200639096525</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1543334033865635</v>
+        <v>0.05941909921850658</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1210111614870003</v>
+        <v>0.1174287321565227</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2775843004204024</v>
+        <v>0.2802520220184884</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6628774877860037</v>
+        <v>0.6752079572031144</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2255181952666778</v>
+        <v>0.2512390302626729</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2783783956071254</v>
+        <v>0.2805131285650854</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4178747418803492</v>
+        <v>0.3704445854557468</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2301319673853008</v>
+        <v>0.2502097424803264</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2673309630216595</v>
+        <v>0.2766872969776025</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3893204404921214</v>
+        <v>0.3658336265353853</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0464665458385428</v>
+        <v>0.001586873957917817</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2845286078456561</v>
+        <v>0.2917531392941587</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8702738657351082</v>
+        <v>0.9956602489653652</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.02162756752909025</v>
+        <v>-0.08094720439440932</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2925905475884686</v>
+        <v>0.2925914426201546</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9410760153784389</v>
+        <v>0.7820441915709218</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8764973807420283</v>
+        <v>0.8937956915905405</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1598667289796822</v>
+        <v>0.1584442431263436</v>
       </c>
       <c r="D24" t="n">
-        <v>4.189413124540377e-08</v>
+        <v>1.689927615944732e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5923085897232842</v>
+        <v>-0.5765879163508648</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1169262828732781</v>
+        <v>0.1158237616093811</v>
       </c>
       <c r="D25" t="n">
-        <v>4.069915021574061e-07</v>
+        <v>6.419530711296993e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1386000328216487</v>
+        <v>-0.147969958483758</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1507698258117117</v>
+        <v>0.1535174480722674</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3579479313928081</v>
+        <v>0.3351140594754043</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08444119781568347</v>
+        <v>-0.0899482548834898</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1574438589059061</v>
+        <v>0.1506886950402402</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5917334279738686</v>
+        <v>0.5505645198063103</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1114085316198851</v>
+        <v>-0.05574640129887711</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1483441008175726</v>
+        <v>0.1543104955024623</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4526440879579776</v>
+        <v>0.7179041641931156</v>
       </c>
     </row>
     <row r="29">
@@ -2782,13 +2782,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3220151818496277</v>
+        <v>-0.3713220125545123</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1549982402231347</v>
+        <v>0.1614980539979261</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03775166539448369</v>
+        <v>0.02149158647937515</v>
       </c>
     </row>
     <row r="30">
@@ -2798,13 +2798,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.01293860122823143</v>
+        <v>-0.01290875358535705</v>
       </c>
       <c r="C30" t="n">
-        <v>0.008183645815534176</v>
+        <v>0.008406891382953915</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1138708520154793</v>
+        <v>0.1246618784599235</v>
       </c>
     </row>
     <row r="31">
@@ -2814,45 +2814,45 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.03120747680900946</v>
+        <v>-0.03174935848357562</v>
       </c>
       <c r="C31" t="n">
-        <v>0.05994942728922969</v>
+        <v>0.06037936443457634</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6026709615967232</v>
+        <v>0.5990054390834734</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.01847772081409666</v>
+        <v>0.007080910324510744</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02286223089800343</v>
+        <v>0.006267464118519536</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4189637308910258</v>
+        <v>0.2585652583325028</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.002580638036074965</v>
+        <v>-0.01710601584298992</v>
       </c>
       <c r="C33" t="n">
-        <v>0.00729235368609906</v>
+        <v>0.02271992637017727</v>
       </c>
       <c r="D33" t="n">
-        <v>0.7234267695349461</v>
+        <v>0.4515051602521268</v>
       </c>
     </row>
     <row r="34">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.01489842147412547</v>
+        <v>0.01401700440248826</v>
       </c>
       <c r="C34" t="n">
-        <v>0.007094501199577954</v>
+        <v>0.006899535929054969</v>
       </c>
       <c r="D34" t="n">
-        <v>0.03572922606502637</v>
+        <v>0.04219552933797019</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.018</v>
+        <v>0.024</v>
       </c>
       <c r="D6" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="E6" t="n">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.015</v>
+        <v>0.369</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="E7" t="n">
-        <v>0.013</v>
+        <v>0.362</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.024</v>
+        <v>-0.388</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004</v>
+        <v>-0.031</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02</v>
+        <v>0.357</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.045</v>
+        <v>0.003</v>
       </c>
       <c r="D9" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.039</v>
+        <v>0.003</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.369</v>
+        <v>0.036</v>
       </c>
       <c r="D10" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="E10" t="n">
-        <v>0.362</v>
+        <v>0.03</v>
       </c>
       <c r="F10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.216</v>
+        <v>-0.095</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.06</v>
+        <v>0.015</v>
       </c>
       <c r="E11" t="n">
-        <v>0.156</v>
+        <v>0.08</v>
       </c>
       <c r="F11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.183</v>
+        <v>0.008</v>
       </c>
       <c r="D12" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="E12" t="n">
-        <v>0.174</v>
+        <v>0.003</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.015</v>
+        <v>-0.082</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.024</v>
+        <v>-0.027</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.009000000000000001</v>
+        <v>0.05500000000000001</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.075</v>
+        <v>0.035</v>
       </c>
       <c r="D14" t="n">
-        <v>0.008</v>
+        <v>0.024</v>
       </c>
       <c r="E14" t="n">
-        <v>0.067</v>
+        <v>0.011</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.035</v>
+        <v>-0.183</v>
       </c>
       <c r="D15" t="n">
-        <v>0.024</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>0.011</v>
+        <v>0.174</v>
       </c>
       <c r="F15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.011</v>
+        <v>-0.216</v>
       </c>
       <c r="D16" t="n">
-        <v>0.004</v>
+        <v>-0.06</v>
       </c>
       <c r="E16" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.156</v>
       </c>
       <c r="F16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="D17" t="n">
-        <v>0.019</v>
+        <v>0.004</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.004</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.008</v>
+        <v>-0.015</v>
       </c>
       <c r="D18" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="E18" t="n">
-        <v>0.003</v>
+        <v>0.013</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.117</v>
+        <v>-0.015</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.003</v>
+        <v>-0.024</v>
       </c>
       <c r="E19" t="n">
-        <v>0.114</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.19</v>
+        <v>-0.117</v>
       </c>
       <c r="D20" t="n">
-        <v>0.024</v>
+        <v>-0.003</v>
       </c>
       <c r="E20" t="n">
-        <v>0.166</v>
+        <v>0.114</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.036</v>
+        <v>0.045</v>
       </c>
       <c r="D21" t="n">
         <v>0.006</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03</v>
+        <v>0.039</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.095</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>0.015</v>
+        <v>-0.029</v>
       </c>
       <c r="E22" t="n">
-        <v>0.08</v>
+        <v>0.042</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.35</v>
+        <v>-0.031</v>
       </c>
       <c r="D23" t="n">
-        <v>0.019</v>
+        <v>-0.005</v>
       </c>
       <c r="E23" t="n">
-        <v>0.331</v>
+        <v>0.026</v>
       </c>
       <c r="F23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.003</v>
+        <v>0.075</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="E24" t="n">
-        <v>0.003</v>
+        <v>0.067</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.008</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.029</v>
+        <v>-0.021</v>
       </c>
       <c r="E25" t="n">
-        <v>0.042</v>
+        <v>-0.013</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.388</v>
+        <v>0.02</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.031</v>
+        <v>0.002</v>
       </c>
       <c r="E27" t="n">
-        <v>0.357</v>
+        <v>0.018</v>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.036</v>
+        <v>0.19</v>
       </c>
       <c r="D28" t="n">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="E28" t="n">
-        <v>0.016</v>
+        <v>0.166</v>
       </c>
       <c r="F28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.031</v>
+        <v>-0.018</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.005</v>
+        <v>0.006</v>
       </c>
       <c r="E29" t="n">
-        <v>0.026</v>
+        <v>0.012</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.008</v>
+        <v>0.35</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.021</v>
+        <v>0.019</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.013</v>
+        <v>0.331</v>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D31" t="n">
-        <v>0.002</v>
+        <v>0.019</v>
       </c>
       <c r="E31" t="n">
-        <v>0.018</v>
+        <v>-0.004</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.082</v>
+        <v>0.036</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.027</v>
+        <v>0.02</v>
       </c>
       <c r="E32" t="n">
-        <v>0.05500000000000001</v>
+        <v>0.016</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.430916292430171</v>
+        <v>1.43091629243017</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1000831566672885</v>
+        <v>0.1000831566672891</v>
       </c>
       <c r="D2" t="n">
-        <v>1.234756909903205</v>
+        <v>1.234756909903204</v>
       </c>
       <c r="E2" t="n">
-        <v>1.627075674957136</v>
+        <v>1.627075674957137</v>
       </c>
       <c r="F2" t="n">
-        <v>2.275503900783856e-46</v>
+        <v>2.27550390078691e-46</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1492,16 +1492,16 @@
         <v>0.007543586664148222</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01785366274695303</v>
+        <v>0.01785366274695305</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02744894931200417</v>
+        <v>-0.0274489493120042</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04253612264030061</v>
+        <v>0.04253612264030064</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6726431725489894</v>
+        <v>0.6726431725489896</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.08746276072038488</v>
+        <v>-0.08746276072038492</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04650174918954322</v>
+        <v>0.04650174918954324</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1786045143500042</v>
+        <v>-0.1786045143500043</v>
       </c>
       <c r="E4" t="n">
         <v>0.003678992909234485</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01403347829791829</v>
+        <v>-0.01403347829791832</v>
       </c>
       <c r="C5" t="n">
         <v>0.03093697564115754</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.07466883634518</v>
+        <v>-0.07466883634518004</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04660187974934343</v>
+        <v>0.04660187974934341</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6501059066201329</v>
+        <v>0.6501059066201322</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.03787901042425926</v>
+        <v>-0.03787901042425931</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03200695968536719</v>
+        <v>0.0320069596853672</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1006114986622044</v>
+        <v>-0.1006114986622045</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0248534778136859</v>
+        <v>0.02485347781368587</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2366262230531389</v>
+        <v>0.2366262230531381</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003790329245909087</v>
+        <v>0.00379032924590907</v>
       </c>
       <c r="C7" t="n">
         <v>0.02958199160697881</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05418930889473553</v>
+        <v>-0.05418930889473555</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0617699673865537</v>
+        <v>0.06176996738655369</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8980463984756383</v>
+        <v>0.8980463984756387</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.009122079738841245</v>
+        <v>-0.009122079738841242</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03193143536141091</v>
+        <v>0.03193143536141092</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.07170654302187535</v>
+        <v>-0.07170654302187536</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05346238354419286</v>
+        <v>0.05346238354419287</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7751254483554761</v>
+        <v>0.7751254483554763</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01941788401766658</v>
+        <v>0.01941788401766656</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03154682417714684</v>
+        <v>0.03154682417714685</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.04241275519615866</v>
+        <v>-0.0424127551961587</v>
       </c>
       <c r="E9" t="n">
         <v>0.08124852323149181</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5382075398620452</v>
+        <v>0.5382075398620458</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01040134955875804</v>
+        <v>0.0104013495587579</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0508899183012224</v>
+        <v>0.05088991830122247</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.08934105748782363</v>
+        <v>-0.08934105748782391</v>
       </c>
       <c r="E10" t="n">
         <v>0.1101437566053397</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8380493712142114</v>
+        <v>0.8380493712142139</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.07164478387083151</v>
+        <v>-0.0716447838708316</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04908682432664911</v>
+        <v>0.04908682432664914</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1678531916665084</v>
+        <v>-0.1678531916665085</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02456362392484535</v>
+        <v>0.0245636239248453</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1444131763866517</v>
+        <v>0.1444131763866514</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.0855185319267841</v>
+        <v>-0.0855185319267842</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05175895972033006</v>
+        <v>0.05175895972033011</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1869642288558904</v>
+        <v>-0.1869642288558906</v>
       </c>
       <c r="E12" t="n">
         <v>0.01592716500232216</v>
       </c>
       <c r="F12" t="n">
-        <v>0.09848442135817075</v>
+        <v>0.09848442135817068</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.02014219262295371</v>
+        <v>-0.02014219262295376</v>
       </c>
       <c r="C13" t="n">
         <v>0.04835193024820024</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.114910234492419</v>
+        <v>-0.1149102344924191</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0746258492465116</v>
+        <v>0.07462584924651154</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6769894910276899</v>
+        <v>0.6769894910276891</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04644002677660911</v>
+        <v>-0.04644002677660903</v>
       </c>
       <c r="C14" t="n">
-        <v>0.04771229108737273</v>
+        <v>0.04771229108737265</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1399543989277511</v>
+        <v>-0.1399543989277509</v>
       </c>
       <c r="E14" t="n">
-        <v>0.04707434537453286</v>
+        <v>0.04707434537453279</v>
       </c>
       <c r="F14" t="n">
-        <v>0.330386999999622</v>
+        <v>0.3303869999996221</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.04379653132756444</v>
+        <v>-0.04379653132756456</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04846010907971658</v>
+        <v>0.04846010907971655</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1387765998106914</v>
+        <v>-0.1387765998106915</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05118353715556253</v>
+        <v>0.05118353715556234</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3661202339272874</v>
+        <v>0.3661202339272859</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.04275936100726026</v>
+        <v>-0.04275936100726035</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04831280652572718</v>
+        <v>0.04831280652572725</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1374507217897372</v>
+        <v>-0.1374507217897375</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0519319997752167</v>
+        <v>0.05193199977521676</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3761284191125533</v>
+        <v>0.3761284191125531</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.01894843278470495</v>
+        <v>-0.01894843278470501</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04870450629519182</v>
+        <v>0.04870450629519191</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1144075110080853</v>
+        <v>-0.1144075110080855</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07651064543867536</v>
+        <v>0.07651064543867547</v>
       </c>
       <c r="F17" t="n">
-        <v>0.697240000833819</v>
+        <v>0.6972400008338187</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.03108663839834799</v>
+        <v>-0.03108663839834801</v>
       </c>
       <c r="C18" t="n">
-        <v>0.04980785777074328</v>
+        <v>0.0498078577707433</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1287082457760983</v>
+        <v>-0.1287082457760984</v>
       </c>
       <c r="E18" t="n">
         <v>0.06653496897940231</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5325414206392294</v>
+        <v>0.5325414206392292</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.0367426440212982</v>
+        <v>-0.0367426440212983</v>
       </c>
       <c r="C19" t="n">
-        <v>0.04885158569502032</v>
+        <v>0.04885158569502038</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1324899925712101</v>
+        <v>-0.1324899925712104</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05900470452861373</v>
+        <v>0.05900470452861376</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4519741045461796</v>
+        <v>0.4519741045461788</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.09057188359527762</v>
+        <v>-0.09057188359527769</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04927809434824119</v>
+        <v>0.04927809434824124</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1871551737445971</v>
+        <v>-0.1871551737445973</v>
       </c>
       <c r="E20" t="n">
-        <v>0.006011406554041893</v>
+        <v>0.00601140655404192</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0660661546429757</v>
+        <v>0.06606615464297572</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.006813317291130315</v>
+        <v>0.006813317291130208</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04829245253929013</v>
+        <v>0.04829245253929011</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.08783815041098823</v>
+        <v>-0.0878381504109883</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1014647849932489</v>
+        <v>0.1014647849932487</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8878031757662277</v>
+        <v>0.8878031757662295</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.006540046937606269</v>
+        <v>-0.006540046937606426</v>
       </c>
       <c r="C22" t="n">
-        <v>0.04835474720397568</v>
+        <v>0.04835474720397565</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1013136099389375</v>
+        <v>-0.1013136099389376</v>
       </c>
       <c r="E22" t="n">
-        <v>0.08823351606372495</v>
+        <v>0.08823351606372472</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8924131142901446</v>
+        <v>0.8924131142901419</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06600063754204345</v>
+        <v>-0.06600063754204354</v>
       </c>
       <c r="C23" t="n">
-        <v>0.04797515526485327</v>
+        <v>0.04797515526485328</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.160030214013873</v>
+        <v>-0.1600302140138731</v>
       </c>
       <c r="E23" t="n">
-        <v>0.02802893892978611</v>
+        <v>0.02802893892978604</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1689066787636249</v>
+        <v>0.1689066787636244</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.05334327025872953</v>
+        <v>-0.05334327025872957</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04069017585118595</v>
+        <v>0.04069017585118596</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1330945494516554</v>
+        <v>-0.1330945494516555</v>
       </c>
       <c r="E24" t="n">
-        <v>0.02640800893419638</v>
+        <v>0.02640800893419636</v>
       </c>
       <c r="F24" t="n">
-        <v>0.18987063592294</v>
+        <v>0.1898706359229398</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.006376847600652717</v>
+        <v>0.006376847600652707</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02353350465813137</v>
+        <v>0.02353350465813144</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.03974797395929036</v>
+        <v>-0.03974797395929051</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0525016691605958</v>
+        <v>0.05250166916059592</v>
       </c>
       <c r="F25" t="n">
-        <v>0.786414960720857</v>
+        <v>0.7864149607208579</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01943138450268198</v>
+        <v>0.0194313845026819</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02857099835969373</v>
+        <v>0.02857099835969376</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0365667432846707</v>
+        <v>-0.03656674328467083</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07542951229003464</v>
+        <v>0.07542951229003463</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4964356372482078</v>
+        <v>0.49643563724821</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.01364006778452288</v>
+        <v>0.01364006778452283</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02987010641842526</v>
+        <v>0.02987010641842527</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.04490426500996934</v>
+        <v>-0.04490426500996941</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07218440057901511</v>
+        <v>0.07218440057901507</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6479254338860438</v>
+        <v>0.6479254338860452</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.02905652978827481</v>
+        <v>0.02905652978827477</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02904075610010609</v>
+        <v>0.0290407561001061</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.02786230625174501</v>
+        <v>-0.02786230625174507</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08597536582829464</v>
+        <v>0.0859753658282946</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3170477230932158</v>
+        <v>0.3170477230932167</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.02046318562776313</v>
+        <v>-0.02046318562776316</v>
       </c>
       <c r="C29" t="n">
         <v>0.02907864115174509</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.07745627500454783</v>
+        <v>-0.07745627500454785</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03652990374902157</v>
+        <v>0.03652990374902153</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4816079278891827</v>
+        <v>0.4816079278891821</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2167,7 +2167,7 @@
         <v>0.3975380272033305</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0384345990913346</v>
+        <v>0.03843459909133461</v>
       </c>
       <c r="D30" t="n">
         <v>0.3222075972240788</v>
@@ -2176,7 +2176,7 @@
         <v>0.4728684571825822</v>
       </c>
       <c r="F30" t="n">
-        <v>4.491231826565436e-25</v>
+        <v>4.491231826565502e-25</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.000476310167395319</v>
+        <v>0.007538497370492831</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001594281744030665</v>
+        <v>0.004040326219119737</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.002648424632114489</v>
+        <v>-0.0003803965047747392</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003601044966905127</v>
+        <v>0.0154573912457604</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7651219509252148</v>
+        <v>0.06206738785508146</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.579358867170089</v>
+        <v>0.0004763101673953202</v>
       </c>
       <c r="C32" t="n">
-        <v>0.01041510004813046</v>
+        <v>0.001594281744030681</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5589456461803719</v>
+        <v>-0.00264842463211452</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5997720881598061</v>
+        <v>0.00360104496690516</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.7651219509252165</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.0006838861338531119</v>
+        <v>-0.0006838861338531103</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001270881981302638</v>
+        <v>0.001270881981302642</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.003174769045807189</v>
+        <v>-0.003174769045807195</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001806996778100965</v>
+        <v>0.001806996778100974</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5904946825704036</v>
+        <v>0.5904946825704056</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.007538497370492824</v>
+        <v>0.002452468964350136</v>
       </c>
       <c r="C34" t="n">
-        <v>0.004040326219119685</v>
+        <v>0.001267934449779067</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0003803965047746438</v>
+        <v>-3.263689197444478e-05</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01545739124576029</v>
+        <v>0.004937574820674718</v>
       </c>
       <c r="F34" t="n">
-        <v>0.06206738785507834</v>
+        <v>0.05308561981596056</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.002452468964350139</v>
+        <v>0.579358867170089</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001267934449779066</v>
+        <v>0.0104151000481304</v>
       </c>
       <c r="D35" t="n">
-        <v>-3.263689197443957e-05</v>
+        <v>0.558945646180372</v>
       </c>
       <c r="E35" t="n">
-        <v>0.004937574820674718</v>
+        <v>0.599772088159806</v>
       </c>
       <c r="F35" t="n">
-        <v>0.05308561981596006</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.158962193354868</v>
+        <v>-2.158962193354871</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5271718320278242</v>
+        <v>0.5271718320277949</v>
       </c>
       <c r="D2" t="n">
-        <v>4.214999094552947e-05</v>
+        <v>4.21499909454871e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01238407949467807</v>
+        <v>0.0123840794946781</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1068934331327136</v>
+        <v>0.1068934331327134</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9077678991895134</v>
+        <v>0.9077678991895131</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3240614798744141</v>
+        <v>0.324061479874414</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2300673427565921</v>
+        <v>0.230067342756592</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1589681126213356</v>
+        <v>0.1589681126213354</v>
       </c>
     </row>
     <row r="5">
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7742552485596507</v>
+        <v>0.7742552485596506</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1687090407132097</v>
+        <v>0.1687090407132093</v>
       </c>
       <c r="D5" t="n">
-        <v>4.447494244187916e-06</v>
+        <v>4.4474942441877e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1818685182700858</v>
+        <v>-0.1818685182700856</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2082512218159787</v>
+        <v>0.2082512218159782</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3824924469491959</v>
+        <v>0.3824924469491958</v>
       </c>
     </row>
     <row r="7">
@@ -2433,10 +2433,10 @@
         <v>0.1367270800884084</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1831182868961762</v>
+        <v>0.1831182868961759</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4552688866476771</v>
+        <v>0.4552688866476762</v>
       </c>
     </row>
     <row r="8">
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09668771677203515</v>
+        <v>-0.09668771677203519</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1943986040042544</v>
+        <v>0.1943986040042539</v>
       </c>
       <c r="D8" t="n">
-        <v>0.618929306423194</v>
+        <v>0.6189293064231929</v>
       </c>
     </row>
     <row r="9">
@@ -2465,10 +2465,10 @@
         <v>1.069744038116436</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1651181209928365</v>
+        <v>0.1651181209928361</v>
       </c>
       <c r="D9" t="n">
-        <v>9.254124082934877e-11</v>
+        <v>9.254124082933939e-11</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1069802150572807</v>
+        <v>0.1069802150572806</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2832033016714792</v>
+        <v>0.2832033016714789</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7056158800782512</v>
+        <v>0.705615880078251</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2579745235365334</v>
+        <v>0.2579745235365333</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2778622026713494</v>
+        <v>0.2778622026713486</v>
       </c>
       <c r="D11" t="n">
-        <v>0.353186580600241</v>
+        <v>0.3531865806002399</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.1913836813322333</v>
+        <v>-0.1913836813322334</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3052132495597789</v>
+        <v>0.3052132495597783</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5306270765800094</v>
+        <v>0.5306270765800085</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3096324773489049</v>
+        <v>0.3096324773489048</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2734335275906101</v>
+        <v>0.2734335275906097</v>
       </c>
       <c r="D13" t="n">
-        <v>0.257471913364385</v>
+        <v>0.2574719133643846</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2686015457564108</v>
+        <v>0.2686015457564107</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2611524565189026</v>
+        <v>0.2611524565189018</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3037034494888953</v>
+        <v>0.3037034494888941</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2981954526051827</v>
+        <v>0.2981954526051825</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2676697859174169</v>
+        <v>0.2676697859174158</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2652610583887295</v>
+        <v>0.2652610583887277</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1286082242724552</v>
+        <v>0.1286082242724551</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2547964366533393</v>
+        <v>0.2547964366533378</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6137352020167333</v>
+        <v>0.6137352020167315</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1872659224740911</v>
+        <v>0.187265922474091</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2740865337717661</v>
+        <v>0.2740865337717644</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4944574156002215</v>
+        <v>0.4944574156002191</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4792250424143023</v>
+        <v>0.4792250424143022</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2542200639096525</v>
+        <v>0.2542200639096521</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05941909921850658</v>
+        <v>0.05941909921850626</v>
       </c>
     </row>
     <row r="19">
@@ -2625,10 +2625,10 @@
         <v>0.1174287321565227</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2802520220184884</v>
+        <v>0.2802520220184872</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6752079572031144</v>
+        <v>0.6752079572031133</v>
       </c>
     </row>
     <row r="20">
@@ -2641,10 +2641,10 @@
         <v>0.2512390302626729</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2805131285650854</v>
+        <v>0.2805131285650849</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3704445854557468</v>
+        <v>0.370444585455746</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2502097424803264</v>
+        <v>0.2502097424803263</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2766872969776025</v>
+        <v>0.2766872969776014</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3658336265353853</v>
+        <v>0.3658336265353836</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.001586873957917817</v>
+        <v>0.001586873957917993</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2917531392941587</v>
+        <v>0.2917531392941569</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9956602489653652</v>
+        <v>0.9956602489653646</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.08094720439440932</v>
+        <v>-0.08094720439440929</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2925914426201546</v>
+        <v>0.2925914426201531</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7820441915709218</v>
+        <v>0.7820441915709209</v>
       </c>
     </row>
     <row r="24">
@@ -2708,7 +2708,7 @@
         <v>0.1584442431263436</v>
       </c>
       <c r="D24" t="n">
-        <v>1.689927615944732e-08</v>
+        <v>1.689927615944738e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2721,10 +2721,10 @@
         <v>-0.5765879163508648</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1158237616093811</v>
+        <v>0.1158237616093812</v>
       </c>
       <c r="D25" t="n">
-        <v>6.419530711296993e-07</v>
+        <v>6.419530711297054e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.147969958483758</v>
+        <v>-0.1479699584837581</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1535174480722674</v>
+        <v>0.1535174480722673</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3351140594754043</v>
+        <v>0.3351140594754034</v>
       </c>
     </row>
     <row r="27">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.05574640129887711</v>
+        <v>-0.05574640129887709</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1543104955024623</v>
+        <v>0.1543104955024621</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7179041641931156</v>
+        <v>0.7179041641931153</v>
       </c>
     </row>
     <row r="29">
@@ -2782,45 +2782,45 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3713220125545123</v>
+        <v>-0.3713220125545122</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1614980539979261</v>
+        <v>0.1614980539979259</v>
       </c>
       <c r="D29" t="n">
-        <v>0.02149158647937515</v>
+        <v>0.02149158647937501</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.01290875358535705</v>
+        <v>-0.01710601584298984</v>
       </c>
       <c r="C30" t="n">
-        <v>0.008406891382953915</v>
+        <v>0.02271992637017727</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1246618784599235</v>
+        <v>0.4515051602521292</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.03174935848357562</v>
+        <v>-0.01290875358535701</v>
       </c>
       <c r="C31" t="n">
-        <v>0.06037936443457634</v>
+        <v>0.008406891382953788</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5990054390834734</v>
+        <v>0.1246618784599187</v>
       </c>
     </row>
     <row r="32">
@@ -2830,45 +2830,45 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.007080910324510744</v>
+        <v>0.007080910324510749</v>
       </c>
       <c r="C32" t="n">
-        <v>0.006267464118519536</v>
+        <v>0.006267464118519504</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2585652583325028</v>
+        <v>0.2585652583325001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.01710601584298992</v>
+        <v>0.01401700440248826</v>
       </c>
       <c r="C33" t="n">
-        <v>0.02271992637017727</v>
+        <v>0.006899535929054942</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4515051602521268</v>
+        <v>0.04219552933796935</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.01401700440248826</v>
+        <v>-0.03174935848357539</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006899535929054969</v>
+        <v>0.06037936443457578</v>
       </c>
       <c r="D34" t="n">
-        <v>0.04219552933797019</v>
+        <v>0.5990054390834727</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.082</v>
+        <v>0.035</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.027</v>
+        <v>0.024</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05500000000000001</v>
+        <v>0.011</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.045</v>
+        <v>-0.082</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006</v>
+        <v>-0.027</v>
       </c>
       <c r="E7" t="n">
-        <v>0.039</v>
+        <v>0.05500000000000001</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.008</v>
+        <v>0.003</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.021</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.013</v>
+        <v>0.003</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.031</v>
+        <v>0.024</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.005</v>
+        <v>0.004</v>
       </c>
       <c r="E9" t="n">
-        <v>0.026</v>
+        <v>0.02</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.117</v>
+        <v>-0.031</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.003</v>
+        <v>-0.005</v>
       </c>
       <c r="E10" t="n">
-        <v>0.114</v>
+        <v>0.026</v>
       </c>
       <c r="F10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.19</v>
+        <v>0.045</v>
       </c>
       <c r="D11" t="n">
-        <v>0.024</v>
+        <v>0.006</v>
       </c>
       <c r="E11" t="n">
-        <v>0.166</v>
+        <v>0.039</v>
       </c>
       <c r="F11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.183</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.029</v>
       </c>
       <c r="E12" t="n">
-        <v>0.174</v>
+        <v>0.042</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
       <c r="D13" t="n">
-        <v>0.004</v>
+        <v>0.019</v>
       </c>
       <c r="E13" t="n">
-        <v>0.006999999999999999</v>
+        <v>-0.004</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.036</v>
+        <v>-0.018</v>
       </c>
       <c r="D14" t="n">
         <v>0.006</v>
       </c>
       <c r="E14" t="n">
-        <v>0.03</v>
+        <v>0.012</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003</v>
+        <v>-0.008</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0.021</v>
       </c>
       <c r="E15" t="n">
-        <v>0.003</v>
+        <v>-0.013</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.075</v>
+        <v>-0.117</v>
       </c>
       <c r="D16" t="n">
-        <v>0.008</v>
+        <v>-0.003</v>
       </c>
       <c r="E16" t="n">
-        <v>0.067</v>
+        <v>0.114</v>
       </c>
       <c r="F16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.018</v>
+        <v>0.036</v>
       </c>
       <c r="D17" t="n">
         <v>0.006</v>
       </c>
       <c r="E17" t="n">
-        <v>0.012</v>
+        <v>0.03</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.015</v>
+        <v>0.35</v>
       </c>
       <c r="D18" t="n">
         <v>0.019</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.004</v>
+        <v>0.331</v>
       </c>
       <c r="F18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,16 +966,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.35</v>
+        <v>0.011</v>
       </c>
       <c r="D20" t="n">
-        <v>0.019</v>
+        <v>0.004</v>
       </c>
       <c r="E20" t="n">
-        <v>0.331</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.369</v>
+        <v>-0.183</v>
       </c>
       <c r="D21" t="n">
-        <v>0.007</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>0.362</v>
+        <v>0.174</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.099</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.029</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>0.042</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.388</v>
+        <v>0.02</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.031</v>
+        <v>0.002</v>
       </c>
       <c r="E23" t="n">
-        <v>0.357</v>
+        <v>0.018</v>
       </c>
       <c r="F23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1077,10 +1077,10 @@
         <v>-0.015</v>
       </c>
       <c r="D24" t="n">
-        <v>0.002</v>
+        <v>-0.024</v>
       </c>
       <c r="E24" t="n">
-        <v>0.013</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.216</v>
+        <v>0.19</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.06</v>
+        <v>0.024</v>
       </c>
       <c r="E25" t="n">
-        <v>0.156</v>
+        <v>0.166</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.024</v>
+        <v>-0.216</v>
       </c>
       <c r="D26" t="n">
-        <v>0.004</v>
+        <v>-0.06</v>
       </c>
       <c r="E26" t="n">
-        <v>0.02</v>
+        <v>0.156</v>
       </c>
       <c r="F26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.035</v>
+        <v>0.369</v>
       </c>
       <c r="D27" t="n">
-        <v>0.024</v>
+        <v>0.007</v>
       </c>
       <c r="E27" t="n">
-        <v>0.011</v>
+        <v>0.362</v>
       </c>
       <c r="F27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.036</v>
+        <v>-0.095</v>
       </c>
       <c r="D28" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="E28" t="n">
-        <v>0.016</v>
+        <v>0.08</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1212,10 +1212,10 @@
         <v>-0.015</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.024</v>
+        <v>0.002</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.009000000000000001</v>
+        <v>0.013</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.099</v>
+        <v>0.075</v>
       </c>
       <c r="D30" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="E30" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.095</v>
+        <v>-0.388</v>
       </c>
       <c r="D31" t="n">
-        <v>0.015</v>
+        <v>-0.031</v>
       </c>
       <c r="E31" t="n">
-        <v>0.08</v>
+        <v>0.357</v>
       </c>
       <c r="F31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="D32" t="n">
         <v>0.02</v>
       </c>
-      <c r="D32" t="n">
-        <v>0.002</v>
-      </c>
       <c r="E32" t="n">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1394,16 +1394,16 @@
         <v>0.9949908017929653</v>
       </c>
       <c r="D2" t="n">
-        <v>0.165743902389888</v>
+        <v>0.1657439023898879</v>
       </c>
       <c r="E2" t="n">
-        <v>1.853163385476147</v>
+        <v>1.853163385476146</v>
       </c>
       <c r="F2" t="n">
         <v>1.168712646832276</v>
       </c>
       <c r="G2" t="n">
-        <v>1.851455159122649</v>
+        <v>1.851455159122648</v>
       </c>
     </row>
   </sheetData>
@@ -1467,16 +1467,16 @@
         <v>1.43091629243017</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1000831566672886</v>
+        <v>0.1000831566672876</v>
       </c>
       <c r="D2" t="n">
-        <v>1.234756909903205</v>
+        <v>1.234756909903207</v>
       </c>
       <c r="E2" t="n">
-        <v>1.627075674957136</v>
+        <v>1.627075674957134</v>
       </c>
       <c r="F2" t="n">
-        <v>2.275503900784375e-46</v>
+        <v>2.275503900779696e-46</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007543586664148193</v>
+        <v>0.007543586664148217</v>
       </c>
       <c r="C3" t="n">
         <v>0.01785366274695303</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0274489493120042</v>
+        <v>-0.02744894931200416</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04253612264030059</v>
+        <v>0.0425361226403006</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6726431725489905</v>
+        <v>0.6726431725489895</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.08746276072038491</v>
+        <v>-0.08746276072038486</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04650174918954323</v>
+        <v>0.04650174918954322</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1786045143500043</v>
+        <v>-0.1786045143500042</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003678992909234471</v>
+        <v>0.003678992909234499</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05999248510483754</v>
+        <v>0.05999248510483759</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1542,10 +1542,10 @@
         <v>-0.01403347829791828</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03093697564115752</v>
+        <v>0.03093697564115753</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.07466883634517997</v>
+        <v>-0.07466883634517998</v>
       </c>
       <c r="E5" t="n">
         <v>0.04660187974934342</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.03787901042425914</v>
+        <v>-0.03787901042425924</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03200695968536717</v>
+        <v>0.0320069596853672</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1006114986622043</v>
+        <v>-0.1006114986622044</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02485347781368597</v>
+        <v>0.02485347781368592</v>
       </c>
       <c r="F6" t="n">
-        <v>0.23662622305314</v>
+        <v>0.236626223053139</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003790329245909079</v>
+        <v>0.003790329245909062</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0295819916069788</v>
+        <v>0.02958199160697879</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05418930889473552</v>
+        <v>-0.05418930889473553</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06176996738655368</v>
+        <v>0.06176996738655365</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8980463984756384</v>
+        <v>0.8980463984756388</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.009122079738841294</v>
+        <v>-0.009122079738841191</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03193143536141091</v>
+        <v>0.0319314353614109</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0717065430218754</v>
+        <v>-0.07170654302187528</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05346238354419281</v>
+        <v>0.0534623835441929</v>
       </c>
       <c r="F8" t="n">
-        <v>0.775125448355475</v>
+        <v>0.7751254483554774</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1642,16 +1642,16 @@
         <v>0.01941788401766658</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03154682417714684</v>
+        <v>0.03154682417714683</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.04241275519615866</v>
+        <v>-0.04241275519615863</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08124852323149181</v>
+        <v>0.08124852323149179</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5382075398620453</v>
+        <v>0.5382075398620449</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01040134955875789</v>
+        <v>0.01040134955875788</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05088991830122239</v>
+        <v>0.05088991830122242</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.08934105748782377</v>
+        <v>-0.08934105748782384</v>
       </c>
       <c r="E10" t="n">
         <v>0.1101437566053396</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8380493712142139</v>
+        <v>0.8380493712142141</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.0716447838708316</v>
+        <v>-0.07164478387083156</v>
       </c>
       <c r="C11" t="n">
         <v>0.04908682432664915</v>
@@ -1698,10 +1698,10 @@
         <v>-0.1678531916665085</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02456362392484532</v>
+        <v>0.02456362392484536</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1444131763866514</v>
+        <v>0.1444131763866517</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.08551853192678424</v>
+        <v>-0.08551853192678413</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05175895972033008</v>
+        <v>0.05175895972033002</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1869642288558905</v>
+        <v>-0.1869642288558903</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01592716500232207</v>
+        <v>0.01592716500232205</v>
       </c>
       <c r="F12" t="n">
-        <v>0.09848442135817036</v>
+        <v>0.0984844213581704</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.0201421926229538</v>
+        <v>-0.02014219262295372</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04835193024820021</v>
+        <v>0.04835193024820024</v>
       </c>
       <c r="D13" t="n">
         <v>-0.114910234492419</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07462584924651144</v>
+        <v>0.07462584924651158</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6769894910276884</v>
+        <v>0.6769894910276897</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04644002677660908</v>
+        <v>-0.04644002677660902</v>
       </c>
       <c r="C14" t="n">
-        <v>0.04771229108737265</v>
+        <v>0.0477122910873727</v>
       </c>
       <c r="D14" t="n">
         <v>-0.1399543989277509</v>
       </c>
       <c r="E14" t="n">
-        <v>0.04707434537453273</v>
+        <v>0.04707434537453288</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3303869999996215</v>
+        <v>0.3303869999996226</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.04379653132756453</v>
+        <v>-0.04379653132756449</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04846010907971656</v>
+        <v>0.04846010907971661</v>
       </c>
       <c r="D15" t="n">
         <v>-0.1387765998106915</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0511835371555624</v>
+        <v>0.05118353715556252</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3661202339272863</v>
+        <v>0.3661202339272872</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.04275936100726035</v>
+        <v>-0.04275936100726031</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04831280652572715</v>
+        <v>0.04831280652572718</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1374507217897372</v>
+        <v>-0.1374507217897373</v>
       </c>
       <c r="E16" t="n">
-        <v>0.05193199977521656</v>
+        <v>0.05193199977521665</v>
       </c>
       <c r="F16" t="n">
-        <v>0.376128419112552</v>
+        <v>0.3761284191125529</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.01894843278470502</v>
+        <v>-0.01894843278470498</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0487045062951919</v>
+        <v>0.04870450629519183</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1144075110080855</v>
+        <v>-0.1144075110080853</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07651064543867545</v>
+        <v>0.07651064543867535</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6972400008338184</v>
+        <v>0.6972400008338187</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.03108663839834789</v>
+        <v>-0.03108663839834793</v>
       </c>
       <c r="C18" t="n">
-        <v>0.04980785777074326</v>
+        <v>0.04980785777074337</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1287082457760982</v>
+        <v>-0.1287082457760984</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06653496897940236</v>
+        <v>0.06653496897940253</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5325414206392306</v>
+        <v>0.5325414206392309</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.03674264402129831</v>
+        <v>-0.03674264402129822</v>
       </c>
       <c r="C19" t="n">
-        <v>0.04885158569502031</v>
+        <v>0.04885158569502035</v>
       </c>
       <c r="D19" t="n">
         <v>-0.1324899925712102</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0590047045286136</v>
+        <v>0.05900470452861377</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4519741045461781</v>
+        <v>0.4519741045461796</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.09057188359527762</v>
+        <v>-0.0905718835952776</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04927809434824119</v>
+        <v>0.04927809434824114</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1871551737445971</v>
+        <v>-0.187155173744597</v>
       </c>
       <c r="E20" t="n">
-        <v>0.006011406554041893</v>
+        <v>0.006011406554041823</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0660661546429757</v>
+        <v>0.06606615464297544</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.006813317291130233</v>
+        <v>0.006813317291130251</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04829245253929007</v>
+        <v>0.04829245253929018</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.08783815041098819</v>
+        <v>-0.08783815041098839</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1014647849932487</v>
+        <v>0.1014647849932489</v>
       </c>
       <c r="F21" t="n">
-        <v>0.887803175766229</v>
+        <v>0.8878031757662289</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.006540046937606322</v>
+        <v>-0.006540046937606275</v>
       </c>
       <c r="C22" t="n">
         <v>0.04835474720397571</v>
@@ -1973,10 +1973,10 @@
         <v>-0.1013136099389376</v>
       </c>
       <c r="E22" t="n">
-        <v>0.08823351606372495</v>
+        <v>0.088233516063725</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8924131142901438</v>
+        <v>0.8924131142901446</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06600063754204354</v>
+        <v>-0.06600063754204351</v>
       </c>
       <c r="C23" t="n">
-        <v>0.04797515526485324</v>
+        <v>0.04797515526485326</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.160030214013873</v>
+        <v>-0.1600302140138731</v>
       </c>
       <c r="E23" t="n">
-        <v>0.02802893892978596</v>
+        <v>0.02802893892978604</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1689066787636242</v>
+        <v>0.1689066787636245</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.05334327025872958</v>
+        <v>-0.05334327025872955</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04069017585118596</v>
+        <v>0.04069017585118598</v>
       </c>
       <c r="D24" t="n">
         <v>-0.1330945494516555</v>
       </c>
       <c r="E24" t="n">
-        <v>0.02640800893419634</v>
+        <v>0.02640800893419641</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1898706359229396</v>
+        <v>0.1898706359229402</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.006376847600652669</v>
+        <v>0.006376847600652704</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02353350465813141</v>
+        <v>0.02353350465813144</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.03974797395929049</v>
+        <v>-0.03974797395929051</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05250166916059583</v>
+        <v>0.05250166916059593</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7864149607208589</v>
+        <v>0.7864149607208581</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01943138450268204</v>
+        <v>0.019431384502682</v>
       </c>
       <c r="C26" t="n">
         <v>0.02857099835969373</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03656674328467064</v>
+        <v>-0.03656674328467067</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07542951229003472</v>
+        <v>0.07542951229003467</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4964356372482064</v>
+        <v>0.4964356372482073</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.01364006778452286</v>
+        <v>0.01364006778452284</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02987010641842529</v>
+        <v>0.02987010641842527</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.04490426500996941</v>
+        <v>-0.0449042650099694</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07218440057901512</v>
+        <v>0.07218440057901508</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6479254338860447</v>
+        <v>0.647925433886045</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.02905652978827483</v>
+        <v>0.02905652978827478</v>
       </c>
       <c r="C28" t="n">
         <v>0.0290407561001061</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.027862306251745</v>
+        <v>-0.02786230625174507</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08597536582829465</v>
+        <v>0.08597536582829463</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3170477230932155</v>
+        <v>0.3170477230932165</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.02046318562776314</v>
+        <v>-0.02046318562776317</v>
       </c>
       <c r="C29" t="n">
         <v>0.0290786411517451</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.07745627500454785</v>
+        <v>-0.07745627500454789</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03652990374902158</v>
+        <v>0.03652990374902156</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4816079278891827</v>
+        <v>0.4816079278891821</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2176,7 +2176,7 @@
         <v>0.4728684571825822</v>
       </c>
       <c r="F30" t="n">
-        <v>4.491231826565693e-25</v>
+        <v>4.491231826565629e-25</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2189,19 +2189,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0004763101673953236</v>
+        <v>0.0004763101673953227</v>
       </c>
       <c r="C31" t="n">
-        <v>0.00159428174403065</v>
+        <v>0.001594281744030656</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.002648424632114455</v>
+        <v>-0.002648424632114469</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003601044966905102</v>
+        <v>0.003601044966905114</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7651219509252104</v>
+        <v>0.7651219509252118</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2214,19 +2214,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.002452468964350139</v>
+        <v>0.002452468964350137</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001267934449779069</v>
+        <v>0.001267934449779068</v>
       </c>
       <c r="D32" t="n">
-        <v>-3.263689197444738e-05</v>
+        <v>-3.263689197444521e-05</v>
       </c>
       <c r="E32" t="n">
-        <v>0.004937574820674724</v>
+        <v>0.004937574820674719</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0530856198159608</v>
+        <v>0.05308561981596061</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.0006838861338531105</v>
+        <v>0.007538497370492828</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001270881981302639</v>
+        <v>0.004040326219119719</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.003174769045807189</v>
+        <v>-0.0003803965047747089</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001806996778100968</v>
+        <v>0.01545739124576036</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5904946825704045</v>
+        <v>0.06206738785508042</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.007538497370492838</v>
+        <v>-0.0006838861338531119</v>
       </c>
       <c r="C34" t="n">
-        <v>0.004040326219119698</v>
+        <v>0.001270881981302641</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0003803965047746577</v>
+        <v>-0.003174769045807195</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01545739124576033</v>
+        <v>0.001806996778100971</v>
       </c>
       <c r="F34" t="n">
-        <v>0.06206738785507872</v>
+        <v>0.5904946825704045</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2292,13 +2292,13 @@
         <v>0.579358867170089</v>
       </c>
       <c r="C35" t="n">
-        <v>0.01041510004813041</v>
+        <v>0.01041510004813036</v>
       </c>
       <c r="D35" t="n">
-        <v>0.558945646180372</v>
+        <v>0.5589456461803721</v>
       </c>
       <c r="E35" t="n">
-        <v>0.599772088159806</v>
+        <v>0.5997720881598059</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.158962193354867</v>
+        <v>-2.15896219335487</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5271718320278143</v>
+        <v>0.5271718320277861</v>
       </c>
       <c r="D2" t="n">
-        <v>4.21499909455159e-05</v>
+        <v>4.214999094547494e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.012384079494678</v>
+        <v>0.01238407949467809</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1068934331327136</v>
+        <v>0.1068934331327135</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9077678991895139</v>
+        <v>0.9077678991895132</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3240614798744141</v>
+        <v>0.3240614798744142</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2300673427565922</v>
+        <v>0.230067342756592</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1589681126213356</v>
+        <v>0.1589681126213351</v>
       </c>
     </row>
     <row r="5">
@@ -2401,10 +2401,10 @@
         <v>0.7742552485596507</v>
       </c>
       <c r="C5" t="n">
-        <v>0.16870904071321</v>
+        <v>0.1687090407132095</v>
       </c>
       <c r="D5" t="n">
-        <v>4.44749424418808e-06</v>
+        <v>4.447494244187801e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1818685182700857</v>
+        <v>-0.1818685182700856</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2082512218159788</v>
+        <v>0.2082512218159785</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3824924469491967</v>
+        <v>0.3824924469491962</v>
       </c>
     </row>
     <row r="7">
@@ -2433,10 +2433,10 @@
         <v>0.1367270800884084</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1831182868961763</v>
+        <v>0.183118286896176</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4552688866476772</v>
+        <v>0.4552688866476763</v>
       </c>
     </row>
     <row r="8">
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09668771677203515</v>
+        <v>-0.09668771677203514</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1943986040042545</v>
+        <v>0.1943986040042542</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6189293064231942</v>
+        <v>0.6189293064231935</v>
       </c>
     </row>
     <row r="9">
@@ -2465,10 +2465,10 @@
         <v>1.069744038116436</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1651181209928366</v>
+        <v>0.1651181209928362</v>
       </c>
       <c r="D9" t="n">
-        <v>9.254124082935111e-11</v>
+        <v>9.254124082934172e-11</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1069802150572799</v>
+        <v>0.1069802150572809</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2832033016714791</v>
+        <v>0.2832033016714784</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7056158800782533</v>
+        <v>0.7056158800782497</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2579745235365326</v>
+        <v>0.2579745235365334</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2778622026713496</v>
+        <v>0.2778622026713485</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3531865806002431</v>
+        <v>0.3531865806002394</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.1913836813322341</v>
+        <v>-0.1913836813322332</v>
       </c>
       <c r="C12" t="n">
-        <v>0.305213249559779</v>
+        <v>0.3052132495597781</v>
       </c>
       <c r="D12" t="n">
-        <v>0.530627076580008</v>
+        <v>0.5306270765800085</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3096324773489042</v>
+        <v>0.3096324773489051</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2734335275906103</v>
+        <v>0.2734335275906096</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2574719133643865</v>
+        <v>0.2574719133643837</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.26860154575641</v>
+        <v>0.2686015457564109</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2611524565189023</v>
+        <v>0.2611524565189025</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3037034494888962</v>
+        <v>0.303703449488895</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2981954526051819</v>
+        <v>0.2981954526051828</v>
       </c>
       <c r="C15" t="n">
-        <v>0.267669785917417</v>
+        <v>0.2676697859174166</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2652610583887306</v>
+        <v>0.2652610583887288</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1286082242724544</v>
+        <v>0.1286082242724553</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2547964366533386</v>
+        <v>0.2547964366533385</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6137352020167346</v>
+        <v>0.6137352020167318</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1872659224740902</v>
+        <v>0.1872659224740912</v>
       </c>
       <c r="C17" t="n">
-        <v>0.274086533771766</v>
+        <v>0.2740865337717652</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4944574156002235</v>
+        <v>0.4944574156002202</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4792250424143015</v>
+        <v>0.4792250424143023</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2542200639096534</v>
+        <v>0.2542200639096524</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05941909921850794</v>
+        <v>0.05941909921850649</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.117428732156522</v>
+        <v>0.1174287321565228</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2802520220184887</v>
+        <v>0.2802520220184881</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6752079572031167</v>
+        <v>0.6752079572031139</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2512390302626722</v>
+        <v>0.2512390302626729</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2805131285650856</v>
+        <v>0.2805131285650849</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3704445854557485</v>
+        <v>0.3704445854557458</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2502097424803256</v>
+        <v>0.2502097424803267</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2766872969776036</v>
+        <v>0.2766872969776025</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3658336265353888</v>
+        <v>0.3658336265353849</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.001586873957917211</v>
+        <v>0.001586873957917974</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2917531392941581</v>
+        <v>0.2917531392941577</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9956602489653669</v>
+        <v>0.9956602489653648</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.08094720439441005</v>
+        <v>-0.08094720439440917</v>
       </c>
       <c r="C23" t="n">
         <v>0.2925914426201542</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7820441915709195</v>
+        <v>0.7820441915709219</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8937956915905404</v>
+        <v>0.8937956915905405</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1584442431263438</v>
+        <v>0.1584442431263437</v>
       </c>
       <c r="D24" t="n">
-        <v>1.689927615944812e-08</v>
+        <v>1.689927615944756e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2721,10 +2721,10 @@
         <v>-0.5765879163508649</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1158237616093812</v>
+        <v>0.1158237616093811</v>
       </c>
       <c r="D25" t="n">
-        <v>6.419530711297091e-07</v>
+        <v>6.419530711296951e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.147969958483758</v>
+        <v>-0.1479699584837578</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1535174480722673</v>
+        <v>0.1535174480722672</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3351140594754038</v>
+        <v>0.3351140594754043</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08994825488348994</v>
+        <v>-0.0899482548834898</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1506886950402403</v>
+        <v>0.1506886950402402</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5505645198063098</v>
+        <v>0.5505645198063103</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.05574640129887724</v>
+        <v>-0.05574640129887703</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1543104955024623</v>
+        <v>0.1543104955024621</v>
       </c>
       <c r="D28" t="n">
-        <v>0.717904164193115</v>
+        <v>0.7179041641931156</v>
       </c>
     </row>
     <row r="29">
@@ -2782,13 +2782,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3713220125545125</v>
+        <v>-0.3713220125545122</v>
       </c>
       <c r="C29" t="n">
         <v>0.1614980539979262</v>
       </c>
       <c r="D29" t="n">
-        <v>0.02149158647937515</v>
+        <v>0.02149158647937521</v>
       </c>
     </row>
     <row r="30">
@@ -2798,13 +2798,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.01290875358535705</v>
+        <v>-0.01290875358535703</v>
       </c>
       <c r="C30" t="n">
-        <v>0.008406891382953939</v>
+        <v>0.008406891382953568</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1246618784599245</v>
+        <v>0.1246618784599083</v>
       </c>
     </row>
     <row r="31">
@@ -2814,45 +2814,45 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.01401700440248824</v>
+        <v>0.01401700440248826</v>
       </c>
       <c r="C31" t="n">
-        <v>0.006899535929054974</v>
+        <v>0.006899535929054955</v>
       </c>
       <c r="D31" t="n">
-        <v>0.04219552933797057</v>
+        <v>0.0421955293379698</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.00708091032451073</v>
+        <v>-0.01710601584298989</v>
       </c>
       <c r="C32" t="n">
-        <v>0.006267464118519533</v>
+        <v>0.02271992637017735</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2585652583325037</v>
+        <v>0.4515051602521295</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.01710601584298991</v>
+        <v>0.007080910324510753</v>
       </c>
       <c r="C33" t="n">
-        <v>0.02271992637017733</v>
+        <v>0.006267464118519491</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4515051602521285</v>
+        <v>0.2585652583324989</v>
       </c>
     </row>
     <row r="34">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.03174935848357557</v>
+        <v>-0.03174935848357548</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0603793644345766</v>
+        <v>0.06037936443457703</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5990054390834756</v>
+        <v>0.5990054390834793</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.035</v>
+        <v>-0.095</v>
       </c>
       <c r="D6" t="n">
-        <v>0.024</v>
+        <v>0.015</v>
       </c>
       <c r="E6" t="n">
-        <v>0.011</v>
+        <v>0.08</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.082</v>
+        <v>0.02</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.027</v>
+        <v>0.002</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05500000000000001</v>
+        <v>0.018</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.003</v>
+        <v>0.024</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003</v>
+        <v>0.02</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.024</v>
+        <v>-0.216</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004</v>
+        <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02</v>
+        <v>0.156</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.031</v>
+        <v>-0.008</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.005</v>
+        <v>-0.021</v>
       </c>
       <c r="E10" t="n">
-        <v>0.026</v>
+        <v>-0.013</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.045</v>
+        <v>0.036</v>
       </c>
       <c r="D11" t="n">
-        <v>0.006</v>
+        <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>0.039</v>
+        <v>0.016</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.082</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.029</v>
+        <v>-0.027</v>
       </c>
       <c r="E12" t="n">
-        <v>0.042</v>
+        <v>0.05500000000000001</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.015</v>
+        <v>-0.117</v>
       </c>
       <c r="D13" t="n">
-        <v>0.019</v>
+        <v>-0.003</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.004</v>
+        <v>0.114</v>
       </c>
       <c r="F13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.018</v>
+        <v>-0.015</v>
       </c>
       <c r="D14" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="E14" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.008</v>
+        <v>-0.015</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.021</v>
+        <v>-0.024</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.013</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.117</v>
+        <v>-0.031</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.003</v>
+        <v>-0.005</v>
       </c>
       <c r="E16" t="n">
-        <v>0.114</v>
+        <v>0.026</v>
       </c>
       <c r="F16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.036</v>
+        <v>0.035</v>
       </c>
       <c r="D17" t="n">
-        <v>0.006</v>
+        <v>0.024</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03</v>
+        <v>0.011</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.35</v>
+        <v>0.008</v>
       </c>
       <c r="D18" t="n">
-        <v>0.019</v>
+        <v>0.005</v>
       </c>
       <c r="E18" t="n">
-        <v>0.331</v>
+        <v>0.003</v>
       </c>
       <c r="F18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.008</v>
+        <v>0.099</v>
       </c>
       <c r="D19" t="n">
-        <v>0.005</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.003</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,16 +966,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.011</v>
+        <v>0.35</v>
       </c>
       <c r="D20" t="n">
-        <v>0.004</v>
+        <v>0.019</v>
       </c>
       <c r="E20" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.331</v>
       </c>
       <c r="F20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.183</v>
+        <v>0.036</v>
       </c>
       <c r="D21" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="E21" t="n">
-        <v>0.174</v>
+        <v>0.03</v>
       </c>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.099</v>
+        <v>0.045</v>
       </c>
       <c r="D22" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="E22" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02</v>
+        <v>-0.388</v>
       </c>
       <c r="D23" t="n">
-        <v>0.002</v>
+        <v>-0.031</v>
       </c>
       <c r="E23" t="n">
-        <v>0.018</v>
+        <v>0.357</v>
       </c>
       <c r="F23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.015</v>
+        <v>-0.183</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.024</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.009000000000000001</v>
+        <v>0.174</v>
       </c>
       <c r="F24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.19</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.024</v>
+        <v>-0.029</v>
       </c>
       <c r="E25" t="n">
-        <v>0.166</v>
+        <v>0.042</v>
       </c>
       <c r="F25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.216</v>
+        <v>0.369</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.06</v>
+        <v>0.007</v>
       </c>
       <c r="E26" t="n">
-        <v>0.156</v>
+        <v>0.362</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.369</v>
+        <v>0.011</v>
       </c>
       <c r="D27" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="E27" t="n">
-        <v>0.362</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.095</v>
+        <v>0.003</v>
       </c>
       <c r="D28" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08</v>
+        <v>0.003</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.015</v>
+        <v>0.015</v>
       </c>
       <c r="D29" t="n">
-        <v>0.002</v>
+        <v>0.019</v>
       </c>
       <c r="E29" t="n">
-        <v>0.013</v>
+        <v>-0.004</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.075</v>
+        <v>-0.018</v>
       </c>
       <c r="D30" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="E30" t="n">
-        <v>0.067</v>
+        <v>0.012</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.388</v>
+        <v>0.19</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.031</v>
+        <v>0.024</v>
       </c>
       <c r="E31" t="n">
-        <v>0.357</v>
+        <v>0.166</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.036</v>
+        <v>0.075</v>
       </c>
       <c r="D32" t="n">
-        <v>0.02</v>
+        <v>0.008</v>
       </c>
       <c r="E32" t="n">
-        <v>0.016</v>
+        <v>0.067</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1394,7 +1394,7 @@
         <v>0.9949908017929653</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1657439023898879</v>
+        <v>0.165743902389888</v>
       </c>
       <c r="E2" t="n">
         <v>1.853163385476146</v>
@@ -1403,7 +1403,7 @@
         <v>1.168712646832276</v>
       </c>
       <c r="G2" t="n">
-        <v>1.851455159122648</v>
+        <v>1.851455159122649</v>
       </c>
     </row>
   </sheetData>
@@ -1467,16 +1467,16 @@
         <v>1.43091629243017</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1000831566672876</v>
+        <v>0.1000831566672887</v>
       </c>
       <c r="D2" t="n">
-        <v>1.234756909903207</v>
+        <v>1.234756909903204</v>
       </c>
       <c r="E2" t="n">
-        <v>1.627075674957134</v>
+        <v>1.627075674957136</v>
       </c>
       <c r="F2" t="n">
-        <v>2.275503900779696e-46</v>
+        <v>2.275503900784928e-46</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007543586664148217</v>
+        <v>0.007543586664148233</v>
       </c>
       <c r="C3" t="n">
         <v>0.01785366274695303</v>
@@ -1498,10 +1498,10 @@
         <v>-0.02744894931200416</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0425361226403006</v>
+        <v>0.04253612264030063</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6726431725489895</v>
+        <v>0.672643172548989</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.08746276072038486</v>
+        <v>-0.08746276072038491</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04650174918954322</v>
+        <v>0.04650174918954324</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1786045143500042</v>
+        <v>-0.1786045143500043</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003678992909234499</v>
+        <v>0.003678992909234485</v>
       </c>
       <c r="F4" t="n">
         <v>0.05999248510483759</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01403347829791828</v>
+        <v>-0.01403347829791827</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03093697564115753</v>
+        <v>0.03093697564115752</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.07466883634517998</v>
+        <v>-0.07466883634517996</v>
       </c>
       <c r="E5" t="n">
         <v>0.04660187974934342</v>
       </c>
       <c r="F5" t="n">
-        <v>0.650105906620133</v>
+        <v>0.6501059066201332</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.03787901042425924</v>
+        <v>-0.03787901042425911</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0320069596853672</v>
+        <v>0.03200695968536717</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1006114986622044</v>
+        <v>-0.1006114986622042</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02485347781368592</v>
+        <v>0.024853477813686</v>
       </c>
       <c r="F6" t="n">
-        <v>0.236626223053139</v>
+        <v>0.2366262230531401</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003790329245909062</v>
+        <v>0.003790329245909075</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02958199160697879</v>
+        <v>0.02958199160697878</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05418930889473553</v>
+        <v>-0.05418930889473549</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06176996738655365</v>
+        <v>0.06176996738655364</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8980463984756388</v>
+        <v>0.8980463984756385</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.009122079738841191</v>
+        <v>-0.009122079738841243</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0319314353614109</v>
+        <v>0.03193143536141089</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.07170654302187528</v>
+        <v>-0.0717065430218753</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0534623835441929</v>
+        <v>0.05346238354419282</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7751254483554774</v>
+        <v>0.7751254483554759</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01941788401766658</v>
+        <v>0.01941788401766657</v>
       </c>
       <c r="C9" t="n">
         <v>0.03154682417714683</v>
@@ -1651,7 +1651,7 @@
         <v>0.08124852323149179</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5382075398620449</v>
+        <v>0.5382075398620452</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01040134955875788</v>
+        <v>0.01040134955875787</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05088991830122242</v>
+        <v>0.05088991830122237</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.08934105748782384</v>
+        <v>-0.08934105748782373</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1101437566053396</v>
+        <v>0.1101437566053395</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8380493712142141</v>
+        <v>0.8380493712142139</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.07164478387083156</v>
+        <v>-0.07164478387083152</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04908682432664915</v>
+        <v>0.04908682432664907</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1678531916665085</v>
+        <v>-0.1678531916665083</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02456362392484536</v>
+        <v>0.02456362392484525</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1444131763866517</v>
+        <v>0.1444131763866513</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1717,16 +1717,16 @@
         <v>-0.08551853192678413</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05175895972033002</v>
+        <v>0.05175895972032998</v>
       </c>
       <c r="D12" t="n">
         <v>-0.1869642288558903</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01592716500232205</v>
+        <v>0.01592716500232198</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0984844213581704</v>
+        <v>0.09848442135817009</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.02014219262295372</v>
+        <v>-0.02014219262295373</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04835193024820024</v>
+        <v>0.04835193024820026</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.114910234492419</v>
+        <v>-0.1149102344924191</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07462584924651158</v>
+        <v>0.07462584924651161</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6769894910276897</v>
+        <v>0.6769894910276896</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04644002677660902</v>
+        <v>-0.04644002677660915</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0477122910873727</v>
+        <v>0.04771229108737265</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1399543989277509</v>
+        <v>-0.139954398927751</v>
       </c>
       <c r="E14" t="n">
-        <v>0.04707434537453288</v>
+        <v>0.04707434537453267</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3303869999996226</v>
+        <v>0.3303869999996208</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.04379653132756449</v>
+        <v>-0.04379653132756453</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04846010907971661</v>
+        <v>0.04846010907971652</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1387765998106915</v>
+        <v>-0.1387765998106914</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05118353715556252</v>
+        <v>0.05118353715556231</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3661202339272872</v>
+        <v>0.3661202339272859</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,16 +1814,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.04275936100726031</v>
+        <v>-0.0427593610072603</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04831280652572718</v>
+        <v>0.04831280652572716</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1374507217897373</v>
+        <v>-0.1374507217897372</v>
       </c>
       <c r="E16" t="n">
-        <v>0.05193199977521665</v>
+        <v>0.05193199977521663</v>
       </c>
       <c r="F16" t="n">
         <v>0.3761284191125529</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.01894843278470498</v>
+        <v>-0.01894843278470496</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04870450629519183</v>
+        <v>0.0487045062951918</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1144075110080853</v>
+        <v>-0.1144075110080852</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07651064543867535</v>
+        <v>0.07651064543867532</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6972400008338187</v>
+        <v>0.6972400008338189</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.03108663839834793</v>
+        <v>-0.03108663839834802</v>
       </c>
       <c r="C18" t="n">
-        <v>0.04980785777074337</v>
+        <v>0.04980785777074322</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1287082457760984</v>
+        <v>-0.1287082457760982</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06653496897940253</v>
+        <v>0.06653496897940214</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5325414206392309</v>
+        <v>0.5325414206392285</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.03674264402129822</v>
+        <v>-0.03674264402129819</v>
       </c>
       <c r="C19" t="n">
-        <v>0.04885158569502035</v>
+        <v>0.04885158569502028</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1324899925712102</v>
+        <v>-0.13248999257121</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05900470452861377</v>
+        <v>0.05900470452861366</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4519741045461796</v>
+        <v>0.4519741045461791</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0905718835952776</v>
+        <v>-0.09057188359527761</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04927809434824114</v>
+        <v>0.04927809434824119</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.187155173744597</v>
+        <v>-0.1871551737445971</v>
       </c>
       <c r="E20" t="n">
-        <v>0.006011406554041823</v>
+        <v>0.006011406554041906</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06606615464297544</v>
+        <v>0.0660661546429757</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.006813317291130251</v>
+        <v>0.006813317291130298</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04829245253929018</v>
+        <v>0.04829245253929003</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.08783815041098839</v>
+        <v>-0.08783815041098804</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1014647849932489</v>
+        <v>0.1014647849932486</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8878031757662289</v>
+        <v>0.8878031757662278</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.006540046937606275</v>
+        <v>-0.006540046937606202</v>
       </c>
       <c r="C22" t="n">
-        <v>0.04835474720397571</v>
+        <v>0.0483547472039756</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1013136099389376</v>
+        <v>-0.1013136099389373</v>
       </c>
       <c r="E22" t="n">
-        <v>0.088233516063725</v>
+        <v>0.08823351606372487</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8924131142901446</v>
+        <v>0.8924131142901455</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06600063754204351</v>
+        <v>-0.06600063754204349</v>
       </c>
       <c r="C23" t="n">
-        <v>0.04797515526485326</v>
+        <v>0.04797515526485321</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1600302140138731</v>
+        <v>-0.1600302140138729</v>
       </c>
       <c r="E23" t="n">
-        <v>0.02802893892978604</v>
+        <v>0.02802893892978595</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1689066787636245</v>
+        <v>0.1689066787636242</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.05334327025872955</v>
+        <v>-0.05334327025872956</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04069017585118598</v>
+        <v>0.04069017585118595</v>
       </c>
       <c r="D24" t="n">
         <v>-0.1330945494516555</v>
       </c>
       <c r="E24" t="n">
-        <v>0.02640800893419641</v>
+        <v>0.02640800893419635</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1898706359229402</v>
+        <v>0.1898706359229397</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.006376847600652704</v>
+        <v>0.006376847600652705</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02353350465813144</v>
+        <v>0.02353350465813138</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.03974797395929051</v>
+        <v>-0.0397479739592904</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05250166916059593</v>
+        <v>0.05250166916059582</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7864149607208581</v>
+        <v>0.7864149607208575</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.019431384502682</v>
+        <v>0.01943138450268201</v>
       </c>
       <c r="C26" t="n">
         <v>0.02857099835969373</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03656674328467067</v>
+        <v>-0.03656674328467065</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07542951229003467</v>
+        <v>0.07542951229003468</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4964356372482073</v>
+        <v>0.4964356372482069</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2092,16 +2092,16 @@
         <v>0.01364006778452284</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02987010641842527</v>
+        <v>0.02987010641842526</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0449042650099694</v>
+        <v>-0.04490426500996937</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07218440057901508</v>
+        <v>0.07218440057901505</v>
       </c>
       <c r="F27" t="n">
-        <v>0.647925433886045</v>
+        <v>0.6479254338860448</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.02905652978827478</v>
+        <v>0.02905652978827489</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0290407561001061</v>
+        <v>0.02904075610010612</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.02786230625174507</v>
+        <v>-0.02786230625174499</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08597536582829463</v>
+        <v>0.08597536582829476</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3170477230932165</v>
+        <v>0.3170477230932151</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.02046318562776317</v>
+        <v>-0.02046318562776315</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0290786411517451</v>
+        <v>0.02907864115174509</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.07745627500454789</v>
+        <v>-0.07745627500454785</v>
       </c>
       <c r="E29" t="n">
         <v>0.03652990374902156</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4816079278891821</v>
+        <v>0.4816079278891824</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2167,16 +2167,16 @@
         <v>0.3975380272033305</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03843459909133461</v>
+        <v>0.03843459909133462</v>
       </c>
       <c r="D30" t="n">
         <v>0.3222075972240788</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4728684571825822</v>
+        <v>0.4728684571825823</v>
       </c>
       <c r="F30" t="n">
-        <v>4.491231826565629e-25</v>
+        <v>4.491231826565693e-25</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0004763101673953227</v>
+        <v>0.579358867170089</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001594281744030656</v>
+        <v>0.01041510004813033</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.002648424632114469</v>
+        <v>0.5589456461803721</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003601044966905114</v>
+        <v>0.5997720881598059</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7651219509252118</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2214,19 +2214,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.002452468964350137</v>
+        <v>0.002452468964350139</v>
       </c>
       <c r="C32" t="n">
         <v>0.001267934449779068</v>
       </c>
       <c r="D32" t="n">
-        <v>-3.263689197444521e-05</v>
+        <v>-3.263689197444434e-05</v>
       </c>
       <c r="E32" t="n">
-        <v>0.004937574820674719</v>
+        <v>0.004937574820674721</v>
       </c>
       <c r="F32" t="n">
-        <v>0.05308561981596061</v>
+        <v>0.05308561981596054</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.007538497370492828</v>
+        <v>0.00753849737049284</v>
       </c>
       <c r="C33" t="n">
-        <v>0.004040326219119719</v>
+        <v>0.004040326219119724</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0003803965047747089</v>
+        <v>-0.0003803965047747071</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01545739124576036</v>
+        <v>0.01545739124576039</v>
       </c>
       <c r="F33" t="n">
-        <v>0.06206738785508042</v>
+        <v>0.06206738785508031</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.0006838861338531119</v>
+        <v>0.0004763101673953283</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001270881981302641</v>
+        <v>0.001594281744030654</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.003174769045807195</v>
+        <v>-0.002648424632114459</v>
       </c>
       <c r="E34" t="n">
-        <v>0.001806996778100971</v>
+        <v>0.003601044966905116</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5904946825704045</v>
+        <v>0.765121950925209</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.579358867170089</v>
+        <v>-0.0006838861338531097</v>
       </c>
       <c r="C35" t="n">
-        <v>0.01041510004813036</v>
+        <v>0.00127088198130264</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5589456461803721</v>
+        <v>-0.003174769045807191</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5997720881598059</v>
+        <v>0.001806996778100972</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.5904946825704056</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.15896219335487</v>
+        <v>-2.158962193354869</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5271718320277861</v>
+        <v>0.5271718320278008</v>
       </c>
       <c r="D2" t="n">
-        <v>4.214999094547494e-05</v>
+        <v>4.21499909454961e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01238407949467809</v>
+        <v>0.0123840794946781</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1068934331327135</v>
+        <v>0.1068934331327136</v>
       </c>
       <c r="D3" t="n">
         <v>0.9077678991895132</v>
@@ -2385,10 +2385,10 @@
         <v>0.3240614798744142</v>
       </c>
       <c r="C4" t="n">
-        <v>0.230067342756592</v>
+        <v>0.2300673427565921</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1589681126213351</v>
+        <v>0.1589681126213355</v>
       </c>
     </row>
     <row r="5">
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7742552485596507</v>
+        <v>0.7742552485596508</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1687090407132095</v>
+        <v>0.1687090407132096</v>
       </c>
       <c r="D5" t="n">
-        <v>4.447494244187801e-06</v>
+        <v>4.447494244187851e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1818685182700856</v>
+        <v>-0.1818685182700855</v>
       </c>
       <c r="C6" t="n">
         <v>0.2082512218159785</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3824924469491962</v>
+        <v>0.3824924469491968</v>
       </c>
     </row>
     <row r="7">
@@ -2433,7 +2433,7 @@
         <v>0.1367270800884084</v>
       </c>
       <c r="C7" t="n">
-        <v>0.183118286896176</v>
+        <v>0.1831182868961761</v>
       </c>
       <c r="D7" t="n">
         <v>0.4552688866476763</v>
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09668771677203514</v>
+        <v>-0.09668771677203518</v>
       </c>
       <c r="C8" t="n">
         <v>0.1943986040042542</v>
@@ -2465,10 +2465,10 @@
         <v>1.069744038116436</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1651181209928362</v>
+        <v>0.1651181209928363</v>
       </c>
       <c r="D9" t="n">
-        <v>9.254124082934172e-11</v>
+        <v>9.254124082934272e-11</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1069802150572809</v>
+        <v>0.1069802150572807</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2832033016714784</v>
+        <v>0.2832033016714788</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7056158800782497</v>
+        <v>0.7056158800782508</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2579745235365334</v>
+        <v>0.2579745235365333</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2778622026713485</v>
+        <v>0.2778622026713496</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3531865806002394</v>
+        <v>0.3531865806002417</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.1913836813322332</v>
+        <v>-0.1913836813322334</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3052132495597781</v>
+        <v>0.3052132495597789</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5306270765800085</v>
+        <v>0.5306270765800092</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3096324773489051</v>
+        <v>0.3096324773489049</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2734335275906096</v>
+        <v>0.2734335275906097</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2574719133643837</v>
+        <v>0.2574719133643845</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2686015457564109</v>
+        <v>0.2686015457564107</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2611524565189025</v>
+        <v>0.2611524565189028</v>
       </c>
       <c r="D14" t="n">
-        <v>0.303703449488895</v>
+        <v>0.3037034494888959</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2981954526051828</v>
+        <v>0.2981954526051826</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2676697859174166</v>
+        <v>0.2676697859174169</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2652610583887288</v>
+        <v>0.2652610583887295</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1286082242724553</v>
+        <v>0.1286082242724551</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2547964366533385</v>
+        <v>0.2547964366533388</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6137352020167318</v>
+        <v>0.6137352020167328</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1872659224740912</v>
+        <v>0.1872659224740909</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2740865337717652</v>
+        <v>0.2740865337717657</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4944574156002202</v>
+        <v>0.4944574156002216</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4792250424143023</v>
+        <v>0.4792250424143021</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2542200639096524</v>
+        <v>0.2542200639096531</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05941909921850649</v>
+        <v>0.05941909921850728</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1174287321565228</v>
+        <v>0.1174287321565226</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2802520220184881</v>
+        <v>0.2802520220184888</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6752079572031139</v>
+        <v>0.6752079572031152</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2512390302626729</v>
+        <v>0.2512390302626727</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2805131285650849</v>
+        <v>0.2805131285650854</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3704445854557458</v>
+        <v>0.3704445854557469</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2502097424803267</v>
+        <v>0.2502097424803263</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2766872969776025</v>
+        <v>0.2766872969776032</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3658336265353849</v>
+        <v>0.3658336265353869</v>
       </c>
     </row>
     <row r="22">
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.001586873957917974</v>
+        <v>0.001586873957917985</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2917531392941577</v>
+        <v>0.2917531392941587</v>
       </c>
       <c r="D22" t="n">
         <v>0.9956602489653648</v>
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.08094720439440917</v>
+        <v>-0.08094720439440953</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2925914426201542</v>
+        <v>0.2925914426201544</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7820441915709219</v>
+        <v>0.7820441915709211</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8937956915905405</v>
+        <v>0.8937956915905404</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1584442431263437</v>
+        <v>0.1584442431263438</v>
       </c>
       <c r="D24" t="n">
-        <v>1.689927615944756e-08</v>
+        <v>1.689927615944801e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2724,7 +2724,7 @@
         <v>0.1158237616093811</v>
       </c>
       <c r="D25" t="n">
-        <v>6.419530711296951e-07</v>
+        <v>6.419530711296864e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1479699584837578</v>
+        <v>-0.147969958483758</v>
       </c>
       <c r="C26" t="n">
         <v>0.1535174480722672</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3351140594754043</v>
+        <v>0.3351140594754038</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0899482548834898</v>
+        <v>-0.08994825488348984</v>
       </c>
       <c r="C27" t="n">
         <v>0.1506886950402402</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5505645198063103</v>
+        <v>0.55056451980631</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.05574640129887703</v>
+        <v>-0.0557464012988771</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1543104955024621</v>
+        <v>0.1543104955024624</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7179041641931156</v>
+        <v>0.7179041641931159</v>
       </c>
     </row>
     <row r="29">
@@ -2782,29 +2782,29 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3713220125545122</v>
+        <v>-0.3713220125545124</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1614980539979262</v>
+        <v>0.1614980539979261</v>
       </c>
       <c r="D29" t="n">
-        <v>0.02149158647937521</v>
+        <v>0.02149158647937512</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.01290875358535703</v>
+        <v>-0.03174935848357564</v>
       </c>
       <c r="C30" t="n">
-        <v>0.008406891382953568</v>
+        <v>0.06037936443457633</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1246618784599083</v>
+        <v>0.5990054390834731</v>
       </c>
     </row>
     <row r="31">
@@ -2814,13 +2814,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.01401700440248826</v>
+        <v>0.01401700440248825</v>
       </c>
       <c r="C31" t="n">
         <v>0.006899535929054955</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0421955293379698</v>
+        <v>0.0421955293379699</v>
       </c>
     </row>
     <row r="32">
@@ -2830,45 +2830,45 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.01710601584298989</v>
+        <v>-0.01710601584298987</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02271992637017735</v>
+        <v>0.02271992637017747</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4515051602521295</v>
+        <v>0.4515051602521324</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.007080910324510753</v>
+        <v>-0.01290875358535703</v>
       </c>
       <c r="C33" t="n">
-        <v>0.006267464118519491</v>
+        <v>0.008406891382953762</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2585652583324989</v>
+        <v>0.124661878459917</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.03174935848357548</v>
+        <v>0.007080910324510735</v>
       </c>
       <c r="C34" t="n">
-        <v>0.06037936443457703</v>
+        <v>0.006267464118519493</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5990054390834793</v>
+        <v>0.2585652583325003</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.029</v>
+        <v>0.004</v>
       </c>
       <c r="E6" t="n">
-        <v>0.042</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.095</v>
+        <v>-0.008</v>
       </c>
       <c r="D7" t="n">
-        <v>0.015</v>
+        <v>-0.021</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08</v>
+        <v>-0.013</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.369</v>
+        <v>-0.082</v>
       </c>
       <c r="D8" t="n">
-        <v>0.007</v>
+        <v>-0.027</v>
       </c>
       <c r="E8" t="n">
-        <v>0.362</v>
+        <v>0.05500000000000001</v>
       </c>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.183</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.029</v>
       </c>
       <c r="E9" t="n">
-        <v>0.174</v>
+        <v>0.042</v>
       </c>
       <c r="F9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D10" t="n">
-        <v>0.002</v>
+        <v>0.019</v>
       </c>
       <c r="E10" t="n">
-        <v>0.018</v>
+        <v>-0.004</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.036</v>
+        <v>0.045</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02</v>
+        <v>0.006</v>
       </c>
       <c r="E11" t="n">
-        <v>0.016</v>
+        <v>0.039</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="D12" t="n">
-        <v>0.019</v>
+        <v>0.002</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.004</v>
+        <v>0.018</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.008</v>
+        <v>-0.216</v>
       </c>
       <c r="D13" t="n">
-        <v>0.005</v>
+        <v>-0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>0.003</v>
+        <v>0.156</v>
       </c>
       <c r="F13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.216</v>
+        <v>-0.183</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.06</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>0.156</v>
+        <v>0.174</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.35</v>
+        <v>-0.015</v>
       </c>
       <c r="D15" t="n">
-        <v>0.019</v>
+        <v>-0.024</v>
       </c>
       <c r="E15" t="n">
-        <v>0.331</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.082</v>
+        <v>0.003</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.027</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.05500000000000001</v>
+        <v>0.003</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.117</v>
+        <v>0.075</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.003</v>
+        <v>0.008</v>
       </c>
       <c r="E17" t="n">
-        <v>0.114</v>
+        <v>0.067</v>
       </c>
       <c r="F17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="E18" t="n">
         <v>0.011</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.006999999999999999</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.19</v>
+        <v>0.008</v>
       </c>
       <c r="D19" t="n">
-        <v>0.024</v>
+        <v>0.005</v>
       </c>
       <c r="E19" t="n">
-        <v>0.166</v>
+        <v>0.003</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.024</v>
+        <v>0.036</v>
       </c>
       <c r="D20" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="E20" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.099</v>
+        <v>-0.031</v>
       </c>
       <c r="D21" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.005</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.026</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.008</v>
+        <v>0.036</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.021</v>
+        <v>0.02</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.013</v>
+        <v>0.016</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.388</v>
+        <v>0.19</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.031</v>
+        <v>0.024</v>
       </c>
       <c r="E23" t="n">
-        <v>0.357</v>
+        <v>0.166</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="C25" t="n">
+        <v>-0.388</v>
+      </c>
+      <c r="D25" t="n">
         <v>-0.031</v>
       </c>
-      <c r="D25" t="n">
-        <v>-0.005</v>
-      </c>
       <c r="E25" t="n">
-        <v>0.026</v>
+        <v>0.357</v>
       </c>
       <c r="F25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.003</v>
+        <v>0.369</v>
       </c>
       <c r="D26" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="F26" t="b">
         <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="F26" t="b">
-        <v>1</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.035</v>
+        <v>-0.015</v>
       </c>
       <c r="D27" t="n">
-        <v>0.024</v>
+        <v>0.002</v>
       </c>
       <c r="E27" t="n">
-        <v>0.011</v>
+        <v>0.013</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.015</v>
+        <v>0.024</v>
       </c>
       <c r="D28" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="E28" t="n">
-        <v>0.013</v>
+        <v>0.02</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.036</v>
+        <v>-0.095</v>
       </c>
       <c r="D29" t="n">
-        <v>0.006</v>
+        <v>0.015</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.045</v>
+        <v>0.099</v>
       </c>
       <c r="D30" t="n">
-        <v>0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>0.039</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.015</v>
+        <v>-0.117</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.024</v>
+        <v>-0.003</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.009000000000000001</v>
+        <v>0.114</v>
       </c>
       <c r="F31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,16 +1290,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.075</v>
+        <v>0.35</v>
       </c>
       <c r="D32" t="n">
-        <v>0.008</v>
+        <v>0.019</v>
       </c>
       <c r="E32" t="n">
-        <v>0.067</v>
+        <v>0.331</v>
       </c>
       <c r="F32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
@@ -1394,16 +1394,16 @@
         <v>0.9949908017929653</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1657439023898879</v>
+        <v>0.165743902389888</v>
       </c>
       <c r="E2" t="n">
-        <v>1.853163385476145</v>
+        <v>1.853163385476147</v>
       </c>
       <c r="F2" t="n">
         <v>1.168712646832276</v>
       </c>
       <c r="G2" t="n">
-        <v>1.851455159122647</v>
+        <v>1.851455159122649</v>
       </c>
     </row>
   </sheetData>
@@ -1467,16 +1467,16 @@
         <v>1.43091629243017</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1000831566672874</v>
+        <v>0.1000831566672855</v>
       </c>
       <c r="D2" t="n">
-        <v>1.234756909903207</v>
+        <v>1.234756909903211</v>
       </c>
       <c r="E2" t="n">
-        <v>1.627075674957133</v>
+        <v>1.627075674957129</v>
       </c>
       <c r="F2" t="n">
-        <v>2.275503900779111e-46</v>
+        <v>2.275503900770078e-46</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007543586664148225</v>
+        <v>0.007543586664148232</v>
       </c>
       <c r="C3" t="n">
         <v>0.01785366274695304</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02744894931200418</v>
+        <v>-0.02744894931200417</v>
       </c>
       <c r="E3" t="n">
         <v>0.04253612264030063</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6726431725489894</v>
+        <v>0.6726431725489891</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.08746276072038493</v>
+        <v>-0.08746276072038486</v>
       </c>
       <c r="C4" t="n">
         <v>0.04650174918954324</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1786045143500043</v>
+        <v>-0.1786045143500042</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003678992909234458</v>
+        <v>0.003678992909234527</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05999248510483754</v>
+        <v>0.05999248510483772</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.0140334782979183</v>
+        <v>-0.01403347829791829</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03093697564115752</v>
+        <v>0.03093697564115748</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.07466883634518</v>
+        <v>-0.0746688363451799</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04660187974934339</v>
+        <v>0.04660187974934332</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6501059066201325</v>
+        <v>0.6501059066201323</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.03787901042425924</v>
+        <v>-0.03787901042425926</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03200695968536719</v>
+        <v>0.03200695968536715</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1006114986622044</v>
+        <v>-0.1006114986622043</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02485347781368591</v>
+        <v>0.02485347781368581</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2366262230531389</v>
+        <v>0.236626223053138</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003790329245909049</v>
+        <v>0.003790329245909098</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0295819916069788</v>
+        <v>0.02958199160697877</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05418930889473556</v>
+        <v>-0.05418930889473545</v>
       </c>
       <c r="E7" t="n">
         <v>0.06176996738655365</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8980463984756393</v>
+        <v>0.8980463984756378</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,16 +1614,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.009122079738841252</v>
+        <v>-0.009122079738841243</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03193143536141092</v>
+        <v>0.03193143536141087</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.07170654302187537</v>
+        <v>-0.07170654302187526</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05346238354419287</v>
+        <v>0.05346238354419278</v>
       </c>
       <c r="F8" t="n">
         <v>0.7751254483554759</v>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01941788401766658</v>
+        <v>0.01941788401766657</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03154682417714684</v>
+        <v>0.03154682417714682</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.04241275519615866</v>
+        <v>-0.04241275519615862</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08124852323149181</v>
+        <v>0.08124852323149176</v>
       </c>
       <c r="F9" t="n">
         <v>0.5382075398620452</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01040134955875788</v>
+        <v>0.01040134955875802</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0508899183012223</v>
+        <v>0.05088991830122228</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.08934105748782359</v>
+        <v>-0.08934105748782342</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1101437566053393</v>
+        <v>0.1101437566053395</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8380493712142136</v>
+        <v>0.8380493712142114</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.07164478387083155</v>
+        <v>-0.07164478387083152</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04908682432664901</v>
+        <v>0.049086824326649</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1678531916665082</v>
+        <v>-0.1678531916665081</v>
       </c>
       <c r="E11" t="n">
         <v>0.02456362392484511</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1444131763866507</v>
+        <v>0.1444131763866508</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.08551853192678412</v>
+        <v>-0.08551853192678413</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05175895972032988</v>
+        <v>0.05175895972032996</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.18696422885589</v>
+        <v>-0.1869642288558902</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01592716500232179</v>
+        <v>0.01592716500232194</v>
       </c>
       <c r="F12" t="n">
-        <v>0.09848442135816948</v>
+        <v>0.09848442135817</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1742,7 +1742,7 @@
         <v>-0.0201421926229537</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04835193024820014</v>
+        <v>0.04835193024820015</v>
       </c>
       <c r="D13" t="n">
         <v>-0.1149102344924188</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04644002677660895</v>
+        <v>-0.04644002677660904</v>
       </c>
       <c r="C14" t="n">
-        <v>0.04771229108737251</v>
+        <v>0.04771229108737256</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1399543989277505</v>
+        <v>-0.1399543989277507</v>
       </c>
       <c r="E14" t="n">
-        <v>0.04707434537453258</v>
+        <v>0.0470743453745326</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3303869999996214</v>
+        <v>0.3303869999996211</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.0437965313275645</v>
+        <v>-0.04379653132756447</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04846010907971653</v>
+        <v>0.04846010907971644</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1387765998106913</v>
+        <v>-0.1387765998106912</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05118353715556236</v>
+        <v>0.05118353715556221</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3661202339272863</v>
+        <v>0.3661202339272858</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.04275936100726032</v>
+        <v>-0.04275936100726025</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04831280652572709</v>
+        <v>0.04831280652572706</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1374507217897371</v>
+        <v>-0.137450721789737</v>
       </c>
       <c r="E16" t="n">
-        <v>0.05193199977521647</v>
+        <v>0.05193199977521649</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3761284191125518</v>
+        <v>0.3761284191125523</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1842,16 +1842,16 @@
         <v>-0.01894843278470496</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04870450629519173</v>
+        <v>0.04870450629519177</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1144075110080851</v>
+        <v>-0.1144075110080852</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07651064543867517</v>
+        <v>0.07651064543867525</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6972400008338184</v>
+        <v>0.6972400008338187</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.03108663839834786</v>
+        <v>-0.03108663839834789</v>
       </c>
       <c r="C18" t="n">
-        <v>0.04980785777074329</v>
+        <v>0.04980785777074315</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1287082457760982</v>
+        <v>-0.1287082457760979</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06653496897940245</v>
+        <v>0.06653496897940214</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5325414206392313</v>
+        <v>0.5325414206392297</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.03674264402129824</v>
+        <v>-0.03674264402129822</v>
       </c>
       <c r="C19" t="n">
         <v>0.04885158569502022</v>
@@ -1898,7 +1898,7 @@
         <v>-0.13248999257121</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05900470452861351</v>
+        <v>0.05900470452861353</v>
       </c>
       <c r="F19" t="n">
         <v>0.4519741045461783</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.09057188359527761</v>
+        <v>-0.09057188359527758</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0492780943482411</v>
+        <v>0.04927809434824103</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1871551737445969</v>
+        <v>-0.1871551737445968</v>
       </c>
       <c r="E20" t="n">
-        <v>0.006011406554041726</v>
+        <v>0.006011406554041615</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0660661546429752</v>
+        <v>0.06606615464297488</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.006813317291130285</v>
+        <v>0.006813317291130278</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04829245253928997</v>
+        <v>0.04829245253929001</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.08783815041098794</v>
+        <v>-0.08783815041098803</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1014647849932485</v>
+        <v>0.1014647849932486</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8878031757662279</v>
+        <v>0.887803175766228</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.00654004693760626</v>
+        <v>-0.006540046937606295</v>
       </c>
       <c r="C22" t="n">
-        <v>0.04835474720397558</v>
+        <v>0.04835474720397549</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1013136099389373</v>
+        <v>-0.1013136099389371</v>
       </c>
       <c r="E22" t="n">
-        <v>0.08823351606372475</v>
+        <v>0.08823351606372455</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8924131142901445</v>
+        <v>0.8924131142901437</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06600063754204347</v>
+        <v>-0.06600063754204345</v>
       </c>
       <c r="C23" t="n">
         <v>0.04797515526485312</v>
@@ -1998,7 +1998,7 @@
         <v>-0.1600302140138727</v>
       </c>
       <c r="E23" t="n">
-        <v>0.02802893892978581</v>
+        <v>0.02802893892978583</v>
       </c>
       <c r="F23" t="n">
         <v>0.1689066787636234</v>
@@ -2017,16 +2017,16 @@
         <v>-0.05334327025872958</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04069017585118598</v>
+        <v>0.04069017585118596</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1330945494516556</v>
+        <v>-0.1330945494516555</v>
       </c>
       <c r="E24" t="n">
-        <v>0.02640800893419638</v>
+        <v>0.02640800893419636</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1898706359229398</v>
+        <v>0.1898706359229397</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.006376847600652682</v>
+        <v>0.006376847600652712</v>
       </c>
       <c r="C25" t="n">
         <v>0.02353350465813141</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.03974797395929049</v>
+        <v>-0.03974797395929044</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05250166916059584</v>
+        <v>0.05250166916059587</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7864149607208586</v>
+        <v>0.7864149607208575</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01943138450268189</v>
+        <v>0.019431384502682</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02857099835969373</v>
+        <v>0.0285709983596937</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03656674328467079</v>
+        <v>-0.03656674328467061</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07542951229003457</v>
+        <v>0.07542951229003461</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4964356372482097</v>
+        <v>0.4964356372482068</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2092,16 +2092,16 @@
         <v>0.01364006778452285</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02987010641842526</v>
+        <v>0.02987010641842523</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.04490426500996937</v>
+        <v>-0.04490426500996932</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07218440057901507</v>
+        <v>0.07218440057901501</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6479254338860445</v>
+        <v>0.6479254338860444</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.02905652978827478</v>
+        <v>0.0290565297882748</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0290407561001061</v>
+        <v>0.02904075610010608</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.02786230625174506</v>
+        <v>-0.02786230625174498</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08597536582829461</v>
+        <v>0.0859753658282946</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3170477230932165</v>
+        <v>0.3170477230932157</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.02046318562776314</v>
+        <v>-0.02046318562776315</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02907864115174506</v>
+        <v>0.02907864115174507</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.07745627500454777</v>
+        <v>-0.0774562750045478</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03652990374902149</v>
+        <v>0.0365299037490215</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4816079278891819</v>
+        <v>0.4816079278891821</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3975380272033306</v>
+        <v>0.3975380272033305</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03843459909133459</v>
+        <v>0.03843459909133462</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3222075972240789</v>
+        <v>0.3222075972240788</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4728684571825823</v>
+        <v>0.4728684571825822</v>
       </c>
       <c r="F30" t="n">
-        <v>4.491231826565276e-25</v>
+        <v>4.491231826565724e-25</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.579358867170089</v>
+        <v>-0.0006838861338531102</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01041510004813034</v>
+        <v>0.001270881981302643</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5589456461803721</v>
+        <v>-0.003174769045807196</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5997720881598059</v>
+        <v>0.001806996778100976</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.5904946825704058</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.0006838861338531079</v>
+        <v>0.0004763101673953282</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001270881981302642</v>
+        <v>0.001594281744030631</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.003174769045807191</v>
+        <v>-0.002648424632114415</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001806996778100976</v>
+        <v>0.003601044966905071</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5904946825704067</v>
+        <v>0.7651219509252056</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.007538497370492823</v>
+        <v>0.007538497370492839</v>
       </c>
       <c r="C33" t="n">
-        <v>0.004040326219119732</v>
+        <v>0.004040326219119695</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0003803965047747384</v>
+        <v>-0.0003803965047746499</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01545739124576039</v>
+        <v>0.01545739124576033</v>
       </c>
       <c r="F33" t="n">
-        <v>0.06206738785508146</v>
+        <v>0.0620673878550785</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0004763101673953255</v>
+        <v>0.002452468964350136</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001594281744030625</v>
+        <v>0.001267934449779068</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.002648424632114404</v>
+        <v>-3.263689197444694e-05</v>
       </c>
       <c r="E34" t="n">
-        <v>0.003601044966905055</v>
+        <v>0.004937574820674719</v>
       </c>
       <c r="F34" t="n">
-        <v>0.765121950925206</v>
+        <v>0.05308561981596077</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.002452468964350139</v>
+        <v>0.5793588671700891</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001267934449779069</v>
+        <v>0.01041510004813033</v>
       </c>
       <c r="D35" t="n">
-        <v>-3.263689197444651e-05</v>
+        <v>0.5589456461803722</v>
       </c>
       <c r="E35" t="n">
-        <v>0.004937574820674724</v>
+        <v>0.599772088159806</v>
       </c>
       <c r="F35" t="n">
-        <v>0.05308561981596073</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.158962193354871</v>
+        <v>-2.15896219335487</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5271718320277896</v>
+        <v>0.527171832027808</v>
       </c>
       <c r="D2" t="n">
-        <v>4.214999094547929e-05</v>
+        <v>4.214999094550605e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01238407949467822</v>
+        <v>0.01238407949467813</v>
       </c>
       <c r="C3" t="n">
         <v>0.1068934331327135</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9077678991895122</v>
+        <v>0.907767899189513</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3240614798744142</v>
+        <v>0.3240614798744141</v>
       </c>
       <c r="C4" t="n">
         <v>0.2300673427565921</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1589681126213353</v>
+        <v>0.1589681126213354</v>
       </c>
     </row>
     <row r="5">
@@ -2404,7 +2404,7 @@
         <v>0.1687090407132095</v>
       </c>
       <c r="D5" t="n">
-        <v>4.447494244187784e-06</v>
+        <v>4.447494244187808e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2417,10 +2417,10 @@
         <v>-0.1818685182700855</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2082512218159784</v>
+        <v>0.2082512218159786</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3824924469491962</v>
+        <v>0.3824924469491968</v>
       </c>
     </row>
     <row r="7">
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1367270800884084</v>
+        <v>0.1367270800884085</v>
       </c>
       <c r="C7" t="n">
         <v>0.183118286896176</v>
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.0966877167720351</v>
+        <v>-0.09668771677203504</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1943986040042541</v>
+        <v>0.1943986040042542</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6189293064231935</v>
+        <v>0.618929306423194</v>
       </c>
     </row>
     <row r="9">
@@ -2468,7 +2468,7 @@
         <v>0.1651181209928362</v>
       </c>
       <c r="D9" t="n">
-        <v>9.254124082934172e-11</v>
+        <v>9.254124082934036e-11</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1069802150572807</v>
+        <v>0.1069802150572806</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2832033016714787</v>
+        <v>0.2832033016714791</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7056158800782508</v>
+        <v>0.7056158800782513</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2579745235365336</v>
+        <v>0.2579745235365334</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2778622026713491</v>
+        <v>0.2778622026713499</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3531865806002403</v>
+        <v>0.353186580600242</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.191383681332233</v>
+        <v>-0.1913836813322333</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3052132495597792</v>
+        <v>0.3052132495597794</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5306270765800105</v>
+        <v>0.5306270765800101</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3096324773489051</v>
+        <v>0.309632477348905</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2734335275906108</v>
+        <v>0.27343352759061</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2574719133643859</v>
+        <v>0.2574719133643847</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.268601545756411</v>
+        <v>0.2686015457564108</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2611524565189025</v>
+        <v>0.2611524565189027</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3037034494888947</v>
+        <v>0.3037034494888956</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2981954526051829</v>
+        <v>0.2981954526051827</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2676697859174172</v>
+        <v>0.2676697859174167</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2652610583887295</v>
+        <v>0.2652610583887292</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1286082242724556</v>
+        <v>0.1286082242724552</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2547964366533388</v>
+        <v>0.2547964366533391</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6137352020167317</v>
+        <v>0.6137352020167328</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1872659224740912</v>
+        <v>0.187265922474091</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2740865337717647</v>
+        <v>0.2740865337717658</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4944574156002191</v>
+        <v>0.4944574156002214</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4792250424143028</v>
+        <v>0.4792250424143024</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2542200639096532</v>
+        <v>0.2542200639096529</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05941909921850706</v>
+        <v>0.05941909921850695</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1174287321565229</v>
+        <v>0.1174287321565227</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2802520220184874</v>
+        <v>0.280252022018488</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6752079572031128</v>
+        <v>0.6752079572031141</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2512390302626731</v>
+        <v>0.2512390302626729</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2805131285650848</v>
+        <v>0.2805131285650851</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3704445854557453</v>
+        <v>0.3704445854557462</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2502097424803267</v>
+        <v>0.2502097424803265</v>
       </c>
       <c r="C21" t="n">
         <v>0.2766872969776031</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3658336265353858</v>
+        <v>0.3658336265353863</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.001586873957918478</v>
+        <v>0.001586873957917937</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2917531392941579</v>
+        <v>0.2917531392941574</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9956602489653633</v>
+        <v>0.9956602489653649</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.08094720439440919</v>
+        <v>-0.08094720439440939</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2925914426201544</v>
+        <v>0.2925914426201541</v>
       </c>
       <c r="D23" t="n">
-        <v>0.782044191570922</v>
+        <v>0.7820441915709212</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8937956915905406</v>
+        <v>0.8937956915905405</v>
       </c>
       <c r="C24" t="n">
         <v>0.1584442431263437</v>
       </c>
       <c r="D24" t="n">
-        <v>1.68992761594477e-08</v>
+        <v>1.689927615944775e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5765879163508647</v>
+        <v>-0.5765879163508648</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1158237616093811</v>
+        <v>0.1158237616093813</v>
       </c>
       <c r="D25" t="n">
-        <v>6.419530711297008e-07</v>
+        <v>6.419530711297162e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.147969958483758</v>
+        <v>-0.1479699584837578</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1535174480722675</v>
+        <v>0.1535174480722673</v>
       </c>
       <c r="D26" t="n">
         <v>0.3351140594754047</v>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08994825488348961</v>
+        <v>-0.08994825488348966</v>
       </c>
       <c r="C27" t="n">
         <v>0.1506886950402403</v>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.05574640129887686</v>
+        <v>-0.05574640129887695</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1543104955024622</v>
+        <v>0.1543104955024624</v>
       </c>
       <c r="D28" t="n">
         <v>0.7179041641931165</v>
@@ -2782,45 +2782,45 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3713220125545121</v>
+        <v>-0.3713220125545122</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1614980539979262</v>
+        <v>0.1614980539979261</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0214915864793753</v>
+        <v>0.02149158647937518</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.03174935848357546</v>
+        <v>0.007080910324510732</v>
       </c>
       <c r="C30" t="n">
-        <v>0.06037936443457656</v>
+        <v>0.006267464118519532</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5990054390834767</v>
+        <v>0.2585652583325034</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.007080910324510751</v>
+        <v>-0.01290875358535702</v>
       </c>
       <c r="C31" t="n">
-        <v>0.006267464118519483</v>
+        <v>0.008406891382953764</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2585652583324984</v>
+        <v>0.1246618784599174</v>
       </c>
     </row>
     <row r="32">
@@ -2833,42 +2833,42 @@
         <v>-0.01710601584298988</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02271992637017742</v>
+        <v>0.02271992637017744</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4515051602521311</v>
+        <v>0.4515051602521313</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.012908753585357</v>
+        <v>0.01401700440248826</v>
       </c>
       <c r="C33" t="n">
-        <v>0.008406891382953684</v>
+        <v>0.006899535929054955</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1246618784599146</v>
+        <v>0.04219552933796985</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.01401700440248826</v>
+        <v>-0.03174935848357562</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006899535929054983</v>
+        <v>0.06037936443457572</v>
       </c>
       <c r="D34" t="n">
-        <v>0.04219552933797059</v>
+        <v>0.5990054390834698</v>
       </c>
     </row>
   </sheetData>
